--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,19 +8,99 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB46163A-B2B9-4382-8DFB-0683998D0ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E627771-0161-402E-9E77-45D4CEA4F452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="1950" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1140" yWindow="180" windowWidth="35640" windowHeight="18855" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
     <sheet name="Results" sheetId="13" r:id="rId2"/>
+    <sheet name="Input - Site" sheetId="75" r:id="rId3"/>
+    <sheet name="Input - Enterprise" sheetId="72" r:id="rId4"/>
+    <sheet name="Constants - Common" sheetId="74" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{CH4} \times GWP_{CH4}")</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Title">_xlfn.LAMBDA("Convert methane emissions to carbon dioxide equivalent emissions")</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
+    <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Variable">_xlfn.LAMBDA("ECH4 CO2e")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e">_xlfn.LAMBDA(_xlpm.E_N2O,_xlpm.GWP_N2O, _xlpm.E_N2O * _xlpm.GWP_N2O)</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EN2O","Nitrous oxide emissions (t N2O)";"GWPN2O","Global warming potential for nitrous oxide (t CO2-e / t N2O)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_LatexEquation">_xlfn.LAMBDA("CO2_e = E_{N2O} \times GWP_{N2O}")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
+    <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
     <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), _xlpm.rows, IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag)), _xlpm.rows))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ConvertStateCommonNameToAbbreviation">_xlfn.LAMBDA(_xlpm.StateCommonName,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.XLOOKUP(_xlpm.StateCommonName, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_1_2">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 1, 2))</definedName>
     <definedName name="Common_InputFunctions.Utility_DisplayArguments_3_4">_xlfn.LAMBDA(_xlpm.ArgumentsArray, _xlfn.CHOOSECOLS(_xlpm.ArgumentsArray, 3, 4))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayArrayInTable">_xlfn.LAMBDA(_xlpm.ArrayData,_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray,_xlop.ColumnsBetweenHeaderAndArray, IFERROR(INDEX(_xlfn.UNIQUE(_xlpm.ArrayData), ROW() - Common_InputFunctions.Utility_GetArrayTableRowStartNumber(_xlpm.TableheaderCell, _xlpm.RowsBetweenHeaderandArray), COLUMN() - Common_InputFunctions.Utility_GetArrayTableColumnStartNumber(_xlpm.TableheaderCell) + IF(_xlfn.ISOMITTED(_xlpm.ColumnsBetweenHeaderAndArray), 1, _xlpm.ColumnsBetweenHeaderAndArray)), ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_DisplayFunctionName">_xlfn.LAMBDA(_xlpm.Function, _xlfn.TEXTBEFORE(_xlfn.FORMULATEXT(_xlpm.Function), "("))</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetArrayTableColumnStartNumber">_xlfn.LAMBDA(_xlpm.TableHeaderCell, COLUMN(_xlpm.TableHeaderCell))</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetArrayTableRowStartNumber">_xlfn.LAMBDA(_xlpm.TableheaderCell,_xlpm.RowsBetweenHeaderandArray, ROW(_xlpm.TableheaderCell) + _xlpm.RowsBetweenHeaderandArray - 1)</definedName>
+    <definedName name="Common_InputFunctions.Utility_GetClimateZone">_xlfn.LAMBDA(_xlpm.avgTemp,_xlpm.avgRain,_xlpm.frostDays,_xlpm.elev,_xlpm.map_pet,_xlpm.minTempArray,_xlpm.maxTempArray,_xlpm.minRainfallArray,_xlpm.maxRainfallArray,_xlpm.minFrostArray,_xlpm.maxFrostArray,_xlpm.minElevationArray,_xlpm.maxElevationArray,_xlpm.minPETArray,_xlpm.maxPETArray,_xlpm.climateZoneArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.minTempArray) &lt;= _xlpm.avgTemp) * (VALUE(_xlpm.maxTempArray) &gt;= _xlpm.avgTemp) * (VALUE(_xlpm.minRainfallArray) &lt;= _xlpm.avgRain) * (VALUE(_xlpm.maxRainfallArray) &gt;= _xlpm.avgRain) * (VALUE(_xlpm.minFrostArray) &lt;= _xlpm.frostDays) * (VALUE(_xlpm.maxFrostArray) &gt;= _xlpm.frostDays) * (VALUE(_xlpm.minElevationArray) &lt;= _xlpm.elev) * (VALUE(_xlpm.maxElevationArray) &gt;= _xlpm.elev) * (VALUE(_xlpm.minPETArray) &lt;= _xlpm.map_pet) * (VALUE(_xlpm.maxPETArray) &gt;= _xlpm.map_pet), _xlfn.TAKE(_xlfn._xlws.FILTER(_xlpm.climateZoneArray, _xlpm.mask, "No match"), 1)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupItemFromMinMax">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.MinArray,_xlpm.MaxArray,_xlpm.ItemArray, _xlfn.LET(_xlpm.mask, (VALUE(_xlpm.MinArray) &lt;= _xlpm.LookupValue) * (VALUE(_xlpm.MaxArray) &gt;= _xlpm.LookupValue), _xlfn._xlws.FILTER(_xlpm.ItemArray, _xlpm.mask, "No match")))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse, IFERROR(_xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)), IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse)))</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell, SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) - 1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Source">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title">_xlfn.LAMBDA("Australian states and territories")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Appendices">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Note:";"MAT = mean annual temperature";"MAP = mean annual precipitation";"PET = potential evapotranspiration"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","MAT","MAP","Frost days per year","Elevation","MAP:PET","Min temp","Max temp","Min rainfall","Max rainfall","Min frost days","Max frost days","Min elevation","Max elevation","Min MAP:PET","Min MAP:PET";"Tropical montane","&gt; 18 C","Any","≤ 7","&gt; 1000 m","Any",18.001,999999,-999999,999999,-999999,7,1000,999999,-999999,999999;"Tropical wet","&gt; 18 C","&gt; 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,2000.001,999999,-999999,7,-999999,999.999,-999999,999999;"Tropical moist","&gt; 18 C","&gt; 1000 mm - ≤ 2000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,1000.001,2000,-999999,7,-999999,999.999,-999999,999999;"Tropical dry","&gt; 18 C","≤ 1000 mm","≤ 7","≤ 1000 m","Any",18.001,999999,-999999,1000,-999999,7,-999999,999.999,-999999,999999;"Warm temperate moist","&gt; 10 C","Any","Any","Any","&gt; 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Warm temperate dry","&gt; 10 C","Any","Any","Any","≤ 1",10.001,999999,-999999,999999,-999999,999999,-999999,999999,-999999,1;"Cool temperate moist","&gt; 0 C - ≤ 10 C","Any","Any","Any","&gt; 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,1.001,999999;"Cool temperate dry","&gt; 0 C - ≤ 10 C","Any","Any","Any","≤ 1",-999999,10,-999999,999999,-999999,999999,-999999,999999,-999999,1}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Title">_xlfn.LAMBDA("VEERG Australian climate zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ClimateZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo in MAT value for warm temperate dry - changed 10 to 11.";"Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.";"GAF accepts rainfall as a proxy for precipitation."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","Conversion factor","Conversion factor 1","Conversion factor 2";"CO2","44/12",44,12;"CH4","16/12",16,12;"N2O","44/28",44,28;"Nox","46/14",46,14;"CO","28/12",28,12;"CO2 Lime","44/12",44,12;"NMVOC","14/12",14,12}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title">_xlfn.LAMBDA("Factor to convert elemental mass of gas to molecular mass")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Unit">_xlfn.LAMBDA("factor")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Variable">_xlfn.LAMBDA("Cg")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Data">_xlfn.LAMBDA(44 / 28)</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Title">_xlfn.LAMBDA("Factor to convert elemental mass of N2O to molecular mass")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Unit">_xlfn.LAMBDA("factor")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_ConvertN2oElementalToMolecularCg_Variable">_xlfn.LAMBDA("CgN2O")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Data source","Data score";"International scope 3 database",1;"Australian scope 3 database",2;"State or regional scope 3 database",3;"Emissions intensity calculated from approved method",4;"Verified credential matching ISO14067",5}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Source">_xlfn.LAMBDA("VEERG 2026: XXXXXXXX")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Title">_xlfn.LAMBDA("Australian data scores for scope 3")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DataScores_Scope3_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Data">_xlfn.LAMBDA(0.6784)</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Title">_xlfn.LAMBDA("p = density of methane")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_DensityOfMethane_Unit">_xlfn.LAMBDA("kg/m3")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"EFleach",0.011}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Equation 3.D.B_10")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Removed duplicate 'Aquaculture' row.";"Removed asterisks to aid lookup.";"Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.";"Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup."}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFNi &amp; EFN2O";"Wet climate zone",0.006;"Dry climate zone",0.005}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.1.4")</definedName>
@@ -28,11 +108,79 @@
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable">_xlfn.LAMBDA("EFNi &amp; EFN2Oi")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate zone","EFPRP";"Wet climate zone",0.006;"Dry climate zone",0.002}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.2")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Emission factor for urine and dung deposited on pasture, range or paddock")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N2O - N / kg N")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"FracLEACH",0.24}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_NIRReference">_xlfn.LAMBDA("National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracLEACH_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Is in leaching zone","FracWET";"Yes - in leaching zone",1;"No - not in leaching zone",0}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Source">_xlfn.LAMBDA("VEERG 2026:5.5.2.3 Constant Parameters")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Title">_xlfn.LAMBDA("Fraction of N that is available for leaching and runoff")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Unit">_xlfn.LAMBDA("(Dimensionless")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWET_Variation">_xlfn.LAMBDA((""))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Irrigation type ir","FracWET";"Not irrigated",0;"Drip irrigation",0;"Sprinkler irrigation",1;"Surface irrigation",1;"Other irrigation",1}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4: Chapter 11: N2O Emissions from Managed Soils, and CO2 Emissions from Lime and Urea Application")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Source">_xlfn.LAMBDA("VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Title">_xlfn.LAMBDA("FracWET for irrigation types")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Unit">_xlfn.LAMBDA("dimensionless")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_FracWETIrrigation_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Gas","CO2-e factor";"CO2",1;"CH4",28;"N2O",265;"CF4",6630;"C2F6",12200;"SF6",22800;"NF3",17200}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Source">_xlfn.LAMBDA("XXXXXXX")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation">_xlfn.LAMBDA("VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Month","Season";"January","Summer";"February","Summer";"March","Autumn";"April","Autumn";"May","Autumn";"June","Winter";"July","Winter";"August","Winter";"September","Spring";"October","Spring";"November","Spring";"December","Summer"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Source">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Title">_xlfn.LAMBDA("Months to Seasons Mapping")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MonthsToSeasons_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Rainfall Zone","Annual rainfall","Rainfall min","Rainfall max";"High rainfall","Annual rainfall &gt; 600mm",600.001,999999;"Low rainfall","Annual rainfall ≤ 600mm",-999999,600}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Title">_xlfn.LAMBDA("VEERG Australian rainfall zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_RainfallZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature Zone","Median Annual Temperature (MAT)","Min MAT","Max MAT";"Warm","≥ 26 C",26,999999;"Temperate","15 - 25 C",15,25.999;"Cool","≤ 14 C",-999999,14.999}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Title">_xlfn.LAMBDA("VEERG Australian temperature zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_TemperatureZones_Variation">_xlfn.LAMBDA("VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(11, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"SA 4 Name";"Bunbury";"Mandurah";"Perth - Inner";"Perth - North East";"Perth - North West";"Perth - South East";"Perth - South West";"Western Australia - Wheat Belt";"Western Australia - Outback (North)";"Western Australia - Outback (South)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Source">_xlfn.LAMBDA("Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Title">_xlfn.LAMBDA("ABS Statistcal Areas Level 4 - Western Australia")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WASA4Areas_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Climate Zone","Wet or Dry Zone";"Tropical montane","Wet climate zone";"Tropical wet","Wet climate zone";"Tropical moist","Wet climate zone";"Tropical dry","Dry climate zone";"Warm temperate moist","Wet climate zone";"Warm temperate dry","Dry climate zone";"Cool temperate moist","Wet climate zone";"Cool temperate dry","Dry climate zone";"Warm temperate moist - low frost","Wet climate zone";"Warm temperate dry - low frost","Dry climate zone";"Warm temperate moist - high temp","Wet climate zone";"Warm temperate dry - high temp","Dry climate zone";"Cool temperate moist - low frost","Wet climate zone";"Cool temperate dry - low frost","Dry climate zone"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Title">_xlfn.LAMBDA("VEERG Australian wet and dry zones")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateFractionResidueRemoved">_xlfn.LAMBDA(_xlpm.TotalResidue,_xlpm.AmountRemoved, (_xlpm.AmountRemoved * 10 ^ 3) / (_xlpm.TotalResidue * 10 ^ 3))</definedName>
+    <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateHarvestIndex">_xlfn.LAMBDA(_xlpm.CropType,_xlpm.CropTypeArray,_xlpm.ResidueCropRatioArray, 1 / (1 + [0]!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.CropType, _xlpm.CropTypeArray, _xlpm.ResidueCropRatioArray)))</definedName>
+    <definedName name="CommonCropping_InputFunctions.CommonCropping_CalculateResidueCropRatio">_xlfn.LAMBDA(_xlpm.HarvestIndex, (1 - _xlpm.HarvestIndex) / _xlpm.HarvestIndex)</definedName>
+    <definedName name="CommonCropping_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, [0]!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, [0]!Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.Livestock_LookupMCFState">_xlfn.LAMBDA(_xlpm.MMS,_xlpm.MMSArray,_xlpm.State,_xlpm.StateArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
@@ -53,6 +201,80 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracLEACH_MS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system","Emission factor";"Irrigated pasture",0.0059;"Irrigated crop",0.007;"Non-irrigated pasture",0.0018;"Non-irrigated crop",0.0041;"Sugar cane",0.0199;"Cotton",0.0053;"Horticulture",0.0064}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracLEACH_MS_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.5a_3, 3.B.5c_3, 3.B.5d_3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracLEACH_MS_Title">_xlfn.LAMBDA("Fraction of N lost through leaching and runoff")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracLEACH_MS_Unit">_xlfn.LAMBDA("Fraction")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracWETMMS_Data">_xlfn.LAMBDA(1)</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracWETMMS_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Equations 3.B.5a_3, 3.B.5c_3, 3.B.5d_3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracWETMMS_Title">_xlfn.LAMBDA("Fraction of N available for leaching and runoff")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_FracWETMMS_Unit">_xlfn.LAMBDA("Fraction")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Source">_xlfn.LAMBDA("National Inventory Report 2023 Volume 1: Table 5.12")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Title">_xlfn.LAMBDA("Table 5.12 Additional symbols used in algorithms for manure related emissions")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Vairable">_xlfn.LAMBDA("MMS")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Cattle, for manufacturing beef","Australia";"Cattle, for prime beef","NSW";"Cattle, weaners","NT";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Title">_xlfn.LAMBDA("Beef cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Chickens","Australia"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Title">_xlfn.LAMBDA("Chickens products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Dairy cows","VIC"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Title">_xlfn.LAMBDA("Dairy cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Pigs","Australia"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Title">_xlfn.LAMBDA("Pigs products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(8, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Product","Source region";"Sheep, for mutton","Australia";"Sheep, for prime lamb","NSW";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Title">_xlfn.LAMBDA("Sheep products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation">_xlfn.LAMBDA(_xlpm.D_j,_xlpm.M_jkl,_xlpm.N_jkl, (_xlpm.D_j * _xlpm.M_jkl * _xlpm.N_jkl) * 10 ^ -3)</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"D_j","number of days the animal is on the farm in each time-period","days","Input";"M_jkl","daily production of enteric methane in each time-period, class and subclass","kg CH4/head/day","Calculated from 3.2.1.1, (2)";"N_jkl","number of beef cattle in each time-period, class and subclass","head","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_LatexEquation">_xlfn.LAMBDA("E_{enteric}=\sum_{j}\sum_{k}\sum_{l}(D_j\times M_{jkl}\times N_{jkl})\times 10^{-3}")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Source">_xlfn.LAMBDA("VEERG 2026: 3.2.1.1, Equation (1)")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Title">_xlfn.LAMBDA("Total annual methane production from enteric fermentation in grazing beef cattle")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Unit">_xlfn.LAMBDA("t CH4")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Variable">_xlfn.LAMBDA("E_enteric")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction">_xlfn.LAMBDA(_xlpm.I_jkl, 20.7 * _xlpm.I_jkl * 10 ^ -3)</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(1, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_jkl","dry matter intake","kg DM/head/day","Calculated from 3.2.1.1, (3)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_LatexEquation">_xlfn.LAMBDA("M_{jkl}=20.7\times I_{jkl}\times 10^{-3}")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_NIRReference">_xlfn.LAMBDA("Charmley et al. (2015)")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_Source">_xlfn.LAMBDA("VEERG 2026: 3.2.1.1, Equation (2)")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_Title">_xlfn.LAMBDA("Daily production of enteric methane")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_Unit">_xlfn.LAMBDA("kg CH4/head/day")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__2_DailyEntericMethaneProduction_Variable">_xlfn.LAMBDA("M_jkl")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef">_xlfn.LAMBDA(_xlpm.W_jkl,_xlpm.LWG_jkl,_xlpm.MA_jk45, (1.185 + 0.00454 * _xlpm.W_jkl - 0.0000026 * _xlpm.W_jkl ^ 2 + 0.315 * _xlpm.LWG_jkl) ^ 2 * _xlpm.MA_jk45)</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"W_jkl","liveweight (kg)","kg","Input";"LWG_jkl","live weight gain (kg/head/day)","kg/head/day","Input";"MA_jk45","additional intake for milk production in cows greater than 2 years","kg/head/day","Calculated from 3.2.1.1, (4)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_LatexEquation">_xlfn.LAMBDA("I_{jkl}=(1.185+0.00454\times W_{jkl}-0.0000026\times W_{jkl}^{2}+0.315\times LWG_{jkl})^2\times MA_{jk=4,5}")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_NIRReference">_xlfn.LAMBDA("Minson and McDonald (1987)")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_Source">_xlfn.LAMBDA("VEERG 2026: 3.2.1.1, Equation (3)")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_Title">_xlfn.LAMBDA("Feed intake for grazing beef cattle")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_Unit">_xlfn.LAMBDA("kg DM/head/day")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__3_FeedIntakeForGrazingBeef_Variable">_xlfn.LAMBDA("I_jkl")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction">_xlfn.LAMBDA(_xlpm.LC_jk45,_xlpm.FA_jk45, (_xlpm.LC_jk45 * _xlpm.FA_jk45) + (1 - _xlpm.LC_jk45))</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"LC_jk45","proportion of cows greater than 1 year in calf in the season of calving expressed as a fraction","fraction","Input";"FA_jk45","feed adjustment value for lactating cows in the season of calving and the season immediately after calving expressed as a fraction","fraction","Constant";"b","breed of cattle","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_ArgumentsVariation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"LC_jk45","proportion of cows greater than 1 year in calf in the season of calving expressed as a fraction","fraction","Input";"FA_jk45calv","feed adjustment value for lactating cows in the season of calving expressed as a fraction","fraction","Constant";"FA_jk45after","feed adjustment value for lactating cows in the season immediately after calving expressed as a fraction","fraction","Constant";"b","breed of cattle","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_LatexEquation">_xlfn.LAMBDA("MA_{jk=4,5}=(LC_{jk=4,5}\times FA_{jk=4,5})+(1-LC_{jk=4,5})")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_LatexEquationVariation">_xlfn.LAMBDA("MA_{jk=4,5}=((LC_{jk=4,5,calv}\times FA_{jk=4,5,calv})+(LC_{jk=4,5,prev}\times FA_{jk=4,5,after}))+(1-(LC_{jk=4,5,calv}+LC_{jk=4,5,prev}))")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Source">_xlfn.LAMBDA("VEERG 2026: 3.2.1.1, Equation (4)")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Title">_xlfn.LAMBDA("Additional intake for milk production in the season of calving and the season after calving")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Variable">_xlfn.LAMBDA("MA_jk45")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Expanded equation to account for season after calving, rather than doing the same equation twice for both seasons")</definedName>
+    <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProductionVariation">_xlfn.LAMBDA(_xlpm.LC_jk45calv,_xlpm.LC_jk45prev,_xlpm.FA_jk45calv,_xlpm.FA_jk45after, ((_xlpm.LC_jk45calv * _xlpm.FA_jk45calv) + (_xlpm.LC_jk45prev * _xlpm.FA_jk45after)) + (1 - (_xlpm.LC_jk45calv + _xlpm.LC_jk45prev)))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
     <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
@@ -67,7 +289,219 @@
     <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
     <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
     <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="M1_Table_I_j_k_l">#REF!</definedName>
+    <definedName name="M1_Table_MA_j_k45">#REF!</definedName>
+    <definedName name="M1_Table_VS_j_k_l">#REF!</definedName>
+    <definedName name="M2_Table_I_j_k_l">#REF!</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement">_xlfn.LAMBDA(_xlpm.N_jkl,_xlpm.M_jklm,_xlpm.D_j, (_xlpm.N_jkl * _xlpm.M_jklm * _xlpm.D_j) * 10 ^ -3)</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"N_jkl","number of beef cattle in each time-period, class and subclass","head","Input";"M_jklm","methane production from manure in each time-period, class, subclass and MMS","kg/head/day","Calculated from 4.2.1.1 (2)";"D_j","number of days in each time-period for each input class","days","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_LatexEquation">_xlfn.LAMBDA("E_{CH4}=\sum_{j}\sum_{k}\sum_{l}\sum_{m}(N_{jkl}\times M_{jklm}\times D_j)\times 10^{-3}")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.1, Equation (1)")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Title">_xlfn.LAMBDA("Total annual methane production from manure management for grazing beef cattle")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Unit">_xlfn.LAMBDA("t CH4")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Variable">_xlfn.LAMBDA("E_CH4")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure">_xlfn.LAMBDA(_xlpm.VS_jkl,_xlpm.B_o,_xlpm.MMS_m,_xlpm.MCF_im,_xlpm.rho, _xlpm.VS_jkl * _xlpm.B_o * _xlpm.MMS_m * _xlpm.MCF_im * _xlpm.rho)</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(7, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VS_jkl","volatile solid production","kg/day","Calculated from 4.2.1.1 (3)";"B_o","emissions potential","m3 CH4/kg VS","Constant";"MMS_m","fraction of waste in each manure management system","fraction","Input";"MCF_im","methane conversion factor for temperature zone and MMS","fraction","Constant";"rho","density of methane","kg/m3","Constant";"i","state","","Input";"i","region","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_Arguments_Method2">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VS_jkl","volatile solid production","kg/day","Calculated from 4.2.1.1 (3)";"B_o","emissions potential","m3 CH4/kg VS","Constant";"MMS_m","fraction of waste in each manure management system","fraction","Input";"MCF_im","methane conversion factor for temperature zone and MMS","fraction","Constant";"rho","density of methane","kg/m3","Constant";"MAT","Mean annual temperature","°C","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_LatexEquation">_xlfn.LAMBDA("M_{jklm}=VS_{jkl}\times B_o\times MMS_m\times MCF_{im}\times \rho")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.1, Equation (2)")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_Title">_xlfn.LAMBDA("Methane production from the manure of grazing beef cattle")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_Unit">_xlfn.LAMBDA("kg CH4/head/day")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__2_MethaneProductionFromManure_Variable">_xlfn.LAMBDA("M_jklm")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef">_xlfn.LAMBDA(_xlpm.I_jkl,_xlpm.DMD_jkl,_xlpm.A, (_xlpm.I_jkl * (1 - _xlpm.DMD_jkl) + (0.04 * _xlpm.I_jkl)) * (1 - _xlpm.A))</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_jkl","dry matter intake as calculated in Chapter 3 Section 3.2.1","kg/head/day","Calculated from 3.2.1.1, (3)";"DMD_jkl","dry matter digestibility expressed as a fraction","fraction","Input";"A","ash content of feed intake expressed as a fraction","fraction","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_LatexEquation">_xlfn.LAMBDA("VS_{jkl}=(I_{jkl}\times (1-DMD_{jkl})+(0.04\times I_{jkl}))\times (1-A)")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.1, Equation (3)")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_Title">_xlfn.LAMBDA("Volatile solid production from grazing beef")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_Unit">_xlfn.LAMBDA("kg/head/day")</definedName>
+    <definedName name="MMS_PastureBeef_Methane_Equations.VEERG_4_2_1_1__3_VolatileSolidProductionFromGrazingBeef_Variable">_xlfn.LAMBDA("VS_jkl")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture">_xlfn.LAMBDA(_xlpm.M_vol,_xlpm.EF_N2O,_xlpm.C_N2O, _xlpm.M_vol * _xlpm.EF_N2O * _xlpm.C_N2O * 10 ^ -3)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"M_vol","mass of nitrogen volatilised from urine and faeces deposited on pasture","kg N","Calculated from 4.2.1.5 (2)";"EF_N2O","nitrous oxide emission factor for atmospheric deposition","kg N2O-N/kg N","Constant";"C_N2O","factor to convert elemental mass of N2O to molecular mass","","Constant";"j","production system","","Input";"i","irrigation method","","Input";"r","rainfall zone","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_LatexEquation">_xlfn.LAMBDA("E_{N2O,ad}=M_{vol}\times EF_{N2O}\times C_{N2O}\times 10^{-3}")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.5, Equation (1)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Title">_xlfn.LAMBDA("Atmospheric deposition emissions from urine and dung deposited on pasture")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Unit">_xlfn.LAMBDA("t N2O")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Variable">_xlfn.LAMBDA("E_N2Oad")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture">_xlfn.LAMBDA(_xlpm.AE,_xlpm.FracGASMsoil, _xlpm.AE * _xlpm.FracGASMsoil)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"AE","total mass of nitrogen excreted on PRP for beef cattle","kg N","Calculated from 4.2.1.3 (2)";"FracGASMsoil","fraction of nitrogen volatilised from urine and faeces deposited on pasture ((kg NH3-N + NOx-N)/kg N)","fraction","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_LatexEquation">_xlfn.LAMBDA("M_{vol}=AE\times FracGASMsoil")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.5, Equation (2)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_Title">_xlfn.LAMBDA("Mass of nitrogen volatilised")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_Unit">_xlfn.LAMBDA("kg N")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_AtmosphericDeposition_Equations.VEERG_4_2_1_5__2_MassOfNitrogenVolatilisedOnPasture_Variable">_xlfn.LAMBDA("M_vol")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture">_xlfn.LAMBDA(_xlpm.M_leach,_xlpm.EF_leach,_xlpm.C_N2O, _xlpm.M_leach * _xlpm.EF_leach * _xlpm.C_N2O * 10 ^ -3)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"M_leach","mass of nitrogen lost to leaching and runoff","kg N","Calculated from 4.2.1.7 (2)";"EF_leach","emission factor for leaching and runoff","kg N2O-N/kg N","Constant";"C_N2O","factor to convert elemental mass of N2O to molecular mass","","Constant"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_LatexEquation">_xlfn.LAMBDA("E_{N2O,leach}=M_{leach}\times EF_{leach}\times C_{N2O}\times 10^{-3}")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.7, Equation (1)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Title">_xlfn.LAMBDA("Leaching and runoff emissions from urine and dung deposited on pasture")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Unit">_xlfn.LAMBDA("t N2O")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Variable">_xlfn.LAMBDA("E_N2Oleach")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture">_xlfn.LAMBDA(_xlpm.AE,_xlpm.FracWet,_xlpm.FracLEACH, _xlpm.AE * _xlpm.FracWet * _xlpm.FracLEACH)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"AE","total mass of nitrogen excreted on PRP for beef cattle","kg N","Calculated from 4.2.1.3 (2)";"FracWet","fraction of N available for leaching and runoff","fraction","Constant";"FracLEACH","fraction of all N that is lost through leaching and runoff","fraction","Constant";"z","location in leaching zone","","Input";"j","production system","","Input";"ir","irrigation method","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_LatexEquation">_xlfn.LAMBDA("M_{leach}=AE\times FracWet\times FracLEACH")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.7, Equation (2)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_Title">_xlfn.LAMBDA("Mass of nitrogen lost to leaching and runoff")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_Unit">_xlfn.LAMBDA("kg N")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_LeachingAndRunoff.VEERG_4_2_1_7__2_MassOfNitrogenLostToLeachingAndRunoffOnPasture_Variable">_xlfn.LAMBDA("M_leach")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture">_xlfn.LAMBDA(_xlpm.AE,_xlpm.EF_PRP,_xlpm.C_N2O, _xlpm.AE * _xlpm.EF_PRP * _xlpm.C_N2O * 10 ^ -3)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"AE","total mass of nitrogen excreted on PRP for beef cattle","kg N","Calculated from 4.2.1.3 (2)";"EF_PRP","emission factor for nitrous oxide from urine and dung deposited to soil","kg N2O-N/kg N deposited","Constant";"C_N2O","factor to convert elemental mass of nitrous oxide to molecular mass","","Constant";"z","wet or dry climate zone","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_LatexEquation">_xlfn.LAMBDA("E_{N2O,dir}=AE\times EF_{PRP}\times C_{N2O}\times 10^{-3}")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (1)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Title">_xlfn.LAMBDA("Total annual direct nitrous oxide emissions from agricultural soils from deposition of urine and dung")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Unit">_xlfn.LAMBDA("t N2O")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Variable">_xlfn.LAMBDA("E_N2Odir")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock">_xlfn.LAMBDA(_xlpm.N_jkl,_xlpm.NE_jkl,_xlpm.D_j, SUM((_xlpm.N_jkl * _xlpm.NE_jkl) * _xlpm.D_j))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"N_jkl","number of beef cattle by time-period, class and subclass","head","Input";"NE_jkl","nitrogen excreted in each time-period, by each class and subclass","kg N/head/day","Calculated from 4.2.1.3 (3)";"D_j","number of days in each time-period (days)","days","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_LatexEquation">_xlfn.LAMBDA("AE=\sum_{j}\sum_{k}\sum_{l}(N_{jkl}\times NE_{jkl}\times D_j)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (2)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_Title">_xlfn.LAMBDA("Total nitrogen excreted to pasture, range and paddock")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_Unit">_xlfn.LAMBDA("kg N")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__2_TotalNitrogenExcretedToPastureRangeAndPaddock_Variable">_xlfn.LAMBDA("AE")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted">_xlfn.LAMBDA(_xlpm.I_jkl,_xlpm.CP_j,_xlpm.MC_jk136,_xlpm.NR_jkl,_xlpm.W_jkl, ((_xlpm.I_jkl * _xlpm.CP_j) / 6.25) + ((0.032 * _xlpm.MC_jk136) / 6.38) - _xlpm.NR_jkl - ((1.1 * 10 ^ -4 * _xlpm.W_jkl ^ 0.75) / 6.25))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(7, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_jkl","dry matter intake as calculated in Chapter 3 Section 3.2.1 (kg DM/head/day)","kg DM/head/day","Calculated from 3.2.1.1 (3)";"CP_j","crude protein content of dry matter intake","fraction","Input";"MC_jk136","milk intake (kg/head/day)","kg/head/day","Constant";"NR_jkl","the amount of nitrogen retained by the body (kg N/head/day)","kg N/head/day","Calculated from 4.2.1.3 (4)";"W_jkl","liveweight (kg/head)","kg/head","Input";"b","breed of cattle","","Input";"s","Calving season","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_LatexEquation">_xlfn.LAMBDA("NE_{jkl}= (I_{jkl}\times CP_j \div 6.25)  + (0.032\times MC_{jk=1,3,6} \div 6.38)  - NR_{jkl} - \left[ (1.1\times 10^{-4}\times W_{jkl}^{0.75}) \div  6.25 \right]")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (3)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_Title">_xlfn.LAMBDA("Nitrogen excreted")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_Unit">_xlfn.LAMBDA("kg N/head/day")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__3_NitrogenExcreted_Variable">_xlfn.LAMBDA("NE_jkl")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody">_xlfn.LAMBDA(_xlpm.MP_jk5,_xlpm.L_jkl,_xlpm.Z_jkl,_xlpm.LWG_jkl, ((0.032 * _xlpm.MP_jk5) / 6.38) + (((0.212 - 0.008 * (_xlpm.L_jkl - 2) - ((0.14 - 0.008 * (_xlpm.L_jkl - 2)) / (1 + EXP(-6 * (_xlpm.Z_jkl - 0.4))))) * (_xlpm.LWG_jkl * 0.92)) / 6.25))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"MP_jk5","milk production (kg/head/day)","kg/head/day","Calculated from 4.2.1.3 (5)";"L_jkl","intake relative to that needed for maintenance","","Calculated from 4.2.1.3 (6)";"Z_jkl","relative size","","Calculated from 4.2.1.3 (7)";"LWG_jkl","liveweight gain (kg/head/day)","kg/head/day","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_LatexEquation">_xlfn.LAMBDA("NR_{jkl}=(0.032 \times MP_{jk=5} \div 6.38) + \left { \left { 0.212 - 0.008 \times (L_{jkl} -2) - \left[ \frac{0.140-0.008 \times (L_{jkl} - 2)}{1+e^{(-6 \times (Z_{jkl}-0.4))}} \right] \right} \times (LWG_{jkl} \times 0.92) \right} \div 6.25")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (4)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_Title">_xlfn.LAMBDA("Amount of nitrogen retained by the body")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_Unit">_xlfn.LAMBDA("kg N/head/day")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__4_NitrogenRetainedByBody_Variable">_xlfn.LAMBDA("NR_jkl")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason">_xlfn.LAMBDA(_xlpm.LC_jk5,_xlpm.DMP_jk5, _xlpm.LC_jk5 * _xlpm.DMP_jk5)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"LC_jk5","proportion of cows greater than 2 years lactating for the season of calving and season after calving expressed as a fraction","fraction","Input";"DMP_jk5","daily milk production (kg/head/day)","kg/head/day","Constant";"b","breed of cattle","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_ArgumentsVariation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"LC_jk5curr","proportion of cows greater than 2 years lactating for the season of calving","fraction","Input";"LC_jk5prev","proportion of cows greater than 2 years lactating for the season after calving","fraction","Input";"DMP_jk5calv","daily milk production for the season of calving (kg/head/day)","kg/head/day","Constant";"DMP_jk5after","daily milk production for the season after calving (kg/head/day)","kg/head/day","Constant";"b","breed of cattle","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_LatexEquation">_xlfn.LAMBDA("MP_{jk=5}=LC_{jk=5}\times DMP_{jk=5}")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_LatexEquationVariation">_xlfn.LAMBDA("MP_{jk=5}=(LC_{jk=5,current}\times DMP_{jk=5,calv})+(LC_{jk=5,prev}\times DMP_{jk=5,after})")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (5)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_Title">_xlfn.LAMBDA("Milk production for the season of calving and season after calving")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_Unit">_xlfn.LAMBDA("kg/head/day")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_Variable">_xlfn.LAMBDA("MP_jk5")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeason_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Split LC and DMP into calving season and after calving season values.")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__5_MilkProductionForCalvingSeasonVariation">_xlfn.LAMBDA(_xlpm.LC_jk5curr,_xlpm.LC_jk5prev,_xlpm.DMP_jk5calv,_xlpm.DMP_jk5after, (_xlpm.LC_jk5curr * _xlpm.DMP_jk5calv) + (_xlpm.LC_jk5prev * _xlpm.DMP_jk5after))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance">_xlfn.LAMBDA(_xlpm.I_jkl,_xlpm.W_jkl, _xlpm.I_jkl / ((1.185 + 0.00454 * _xlpm.W_jkl - 0.0000026 * _xlpm.W_jkl ^ 2) ^ 2))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_jkl","dry matter intake as calculated in Chapter 3 Section 3.2.1 (kg DM/head/day)","kg DM/head/day","Calculated from 3.2.1.1 (3)";"W_jkl","liveweight (kg/head)","kg/head","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_LatexEquation">_xlfn.LAMBDA("L_{jkl}=\frac{I_{jkl}}{(1.185+0.00454\times W_{jkl}-0.0000026\times W_{jkl}^{2})^{2}}")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (6)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_Title">_xlfn.LAMBDA("Intake relative to that needed for maintenance")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_Unit">_xlfn.LAMBDA("ratio")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__6_IntakeRelativeToMaintenance_Variable">_xlfn.LAMBDA("L_jkl")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize">_xlfn.LAMBDA(_xlpm.W_jkl,_xlpm.SRW_k, _xlpm.W_jkl / _xlpm.SRW_k)</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"W_jkl","liveweight (kg)","kg","Input";"SRW_k","standard reference weight (kg)","kg","Constant";"i","state","","Input"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_LatexEquation">_xlfn.LAMBDA("Z_{jkl}=\frac{W_{jkl}}{SRW_k}")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_NIRReference">_xlfn.LAMBDA("")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.1.3, Equation (7)")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Title">_xlfn.LAMBDA("Relative size of the cattle")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Unit">_xlfn.LAMBDA("ratio")</definedName>
+    <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Variable">_xlfn.LAMBDA("Z_jkl")</definedName>
     <definedName name="Range_LivestockStartingValues">#REF!</definedName>
+    <definedName name="Result_Enterprise_Method1">Results!$H$28</definedName>
+    <definedName name="Result_Enterprise_Method2">Results!$I$28</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Data">_xlfn.LAMBDA(0.08)</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.2.3 CONSTANTS")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Title">_xlfn.LAMBDA("Ash content of feed intake")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Variable">_xlfn.LAMBDA("A")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_CrudeProteinContent_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(16, 6, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Spring","Summer","Autumn","Winter";"ACT","n/a",0.07,0.13,0.1,0.06;"NSW","n/a",0.07,0.13,0.1,0.06;"NT","Alice Springs",0.058,0.092,0.075,0.053;"NT","Barkly",0.058,0.092,0.075,0.053;"NT","Northern",0.058,0.092,0.075,0.053;"QLD","High",0.072,0.099,0.078,0.059;"QLD","Moderate/High",0.072,0.099,0.078,0.059;"QLD","Moderate/Low",0.072,0.099,0.078,0.059;"QLD","Low",0.072,0.099,0.078,0.059;"SA","n/a",0.16,0.07,0.09,0.2;"TAS","n/a",0.2,0.1,0.16,0.2;"VIC","n/a",0.25,0.07,0.1,0.21;"WA","South West",0.2,0.09,0.06,0.2;"WA","Pilbara",0.04,0.12,0.09,0.06;"WA","Kimberley",0.04,0.12,0.09,0.06}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_CrudeProteinContent_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.6")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_CrudeProteinContent_Title">_xlfn.LAMBDA("Beef pasture cattle - Crude protein content of feed intake (fraction) (CPj)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_CrudeProteinContent_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_CrudeProteinContent_Variable">_xlfn.LAMBDA("CPj")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_CrudeProteinContent_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Split ACT and NSW into separate rows. Duplicated QLD and NT rows with regions from table A.1.2.2 to aid lookup")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_DryMatterDigestibility_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(16, 6, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Spring","Summer","Autumn","Winter";"ACT","n/a",0.55,0.65,0.6,0.5;"NSW","n/a",0.55,0.65,0.6,0.5;"NT","Alice Springs",0.55,0.61,0.57,0.54;"NT","Barkly",0.55,0.61,0.57,0.54;"NT","Northern",0.55,0.61,0.57,0.54;"QLD","High",0.53,0.57,0.55,0.51;"QLD","Moderate/High",0.53,0.57,0.55,0.51;"QLD","Moderate/Low",0.53,0.57,0.55,0.51;"QLD","Low",0.53,0.57,0.55,0.51;"SA","n/a",0.7,0.55,0.55,0.75;"TAS","n/a",0.75,0.6,0.7,0.75;"VIC","n/a",0.8,0.55,0.6,0.76;"WA","South West",0.8,0.58,0.5,0.75;"WA","Pilbara",0.4,0.65,0.55,0.45;"WA","Kimberley",0.4,0.65,0.55,0.45}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_DryMatterDigestibility_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.5")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_DryMatterDigestibility_Title">_xlfn.LAMBDA("Beef pasture cattle - Dry matter digestibility of feed intake (fraction) (DMDj)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_DryMatterDigestibility_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_DryMatterDigestibility_Variable">_xlfn.LAMBDA("DMDj")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_DryMatterDigestibility_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Split ACT and NSW into separate rows. Duplicated QLD and NT rows with regions from table A.1.2.2 to aid lookup")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FeedAdjustmentAndMilkProduction_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Breed","Season","Feed adjustment (MCjk=1,3,6)","Milk intake / production (DMPjk=5)";"Hereford or Shorthorn breeds","Spring",1.3,6;"Hereford or Shorthorn breeds","Summer",1.1,4;"Hereford or Shorthorn breeds","Autumn",0,0;"Hereford or Shorthorn breeds","Winter",0,0;"Northern Brahman cross breed","Spring",0,0;"Northern Brahman cross breed","Summer",1.3,4;"Northern Brahman cross breed","Autumn",1.1,3;"Northern Brahman cross breed","Winter",0,0}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FeedAdjustmentAndMilkProduction_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.7")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FeedAdjustmentAndMilkProduction_Title">_xlfn.LAMBDA("Beef pasture cattle - Feed intake adjustment and milk production (kg/head/day)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FeedAdjustmentAndMilkProduction_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FeedAdjustmentAndMilkProduction_Variable">_xlfn.LAMBDA("MCjk=1,3,6; DMPjk=5")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FeedAdjustmentAndMilkProduction_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracGASMSoil_Data">_xlfn.LAMBDA(0.21)</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracGASMSoil_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.2.3 CONSTANTS")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracGASMSoil_Title">_xlfn.LAMBDA("Fraction of nitrogen volatilised from urine and faeces deposited on pasture")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracGASMSoil_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracGASMSoil_Variable">_xlfn.LAMBDA("FracGASMSoil")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracGASMSoil_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracLEACH_Data">_xlfn.LAMBDA(0.24)</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracLEACH_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.2.3 CONSTANTS")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracLEACH_Title">_xlfn.LAMBDA("Default fraction of N that is lost through leaching and runoff")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracLEACH_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracLEACH_Variable">_xlfn.LAMBDA("FracLEACH")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FracLEACH_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FractionOfManureToMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(16, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT","n/a",99.192,0.808;"NSW","n/a",99.452,0.548;"SA","n/a",99.759,0.241;"TAS","n/a",99.122,0.878;"VIC","n/a",98.894,1.106;"WA","South West",99.622,0.378;"WA","Pilbara",99.999,0.001;"WA","Kimberley",99.999,0.001;"NT","Alice Springs",99.999,0.001;"NT","Barkly",99.994,0.006;"NT","Northern",99.999,0.001;"QLD","High",99.773,0.227;"QLD","Moderate/High",99.898,0.102;"QLD","Moderate/Low",99.979,0.021;"QLD","Low",99.977,0.023}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FractionOfManureToMMS_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.9")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FractionOfManureToMMS_Title">_xlfn.LAMBDA("Beef pasture cattle - Fraction of manure to each manure management system (fraction) (MMSm)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FractionOfManureToMMS_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FractionOfManureToMMS_Variable">_xlfn.LAMBDA("MMSm")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_FractionOfManureToMMS_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Removed comma from 'Pasture range and paddock' to aid lookup")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_Liveweight_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(29, 10, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Season","Bull &lt; 1","Bull &gt; 1","Cow &lt; 1","Cow 1-2","Cow &gt; 2","Steer &lt; 1","Steer &gt; 1";"ACT/NSW","n/a","Spring",80,480,75,300,440,75,380;"ACT/NSW","n/a","Summer",170,520,160,360,470,160,420;"ACT/NSW","n/a","Autumn",240,550,220,390,490,220,450;"ACT/NSW","n/a","Winter",280,560,260,410,500,260,460;"South Australia","n/a","Spring",250,800,220,400,500,230,420;"South Australia","n/a","Summer",320,800,280,420,500,290,420;"South Australia","n/a","Autumn",80,700,70,300,450,75,400;"South Australia","n/a","Winter",160,700,140,350,450,150,400;"Tasmania","n/a","Spring",105,700,85,300,490,90,480;"Tasmania","n/a","Summer",480,750,150,350,530,160,460;"Tasmania","n/a","Autumn",250,725,200,360,500,215,490;"Tasmania","n/a","Winter",260,700,210,380,460,230,470;"Victoria","n/a","Spring",250,820,240,410,560,240,510;"Victoria","n/a","Summer",280,850,260,440,550,270,520;"Victoria","n/a","Autumn",100,700,95,300,450,95,410;"Victoria","n/a","Winter",150,720,140,320,470,140,440;"Western Australia","South West","Spring",340,800,260,420,550,300,480;"Western Australia","South West","Summer",380,780,300,450,530,340,470;"Western Australia","South West","Autumn",100,680,80,320,480,100,340;"Western Australia","South West","Winter",190,700,150,330,490,170,360;"Western Australia","Pilbara","Spring",80,450,70,260,340,80,370;"Western Australia","Pilbara","Summer",150,500,140,310,360,150,400;"Western Australia","Pilbara","Autumn",230,550,220,330,380,230,420;"Western Australia","Pilbara","Winter",250,500,240,340,360,250,390;"Western Australia","Kimberley","Spring",220,500,180,300,320,210,340;"Western Australia","Kimberley","Summer",110,550,90,220,380,100,390;"Western Australia","Kimberley","Autumn",170,600,140,270,390,160,430;"Western Australia","Kimberley","Winter",200,550,150,280,350,190,400}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_Liveweight_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.1")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_Liveweight_Title">_xlfn.LAMBDA("Beef pasture cattle - Liveweight (kg) (Wjkl)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_Liveweight_Unit">_xlfn.LAMBDA("kg")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_Liveweight_Variable">_xlfn.LAMBDA("Wjkl")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_Liveweight_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGain_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(29, 10, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Season","Bull &lt;1","Bull &gt;1","Cow &lt;1","Cow 1-2","Cow &gt;2","Steer &lt;1","Steer &gt;1";"ACT/NSW","n/a","Spring",0.5,0.2,0.5,0.4,0.3,0.5,0.4;"ACT/NSW","n/a","Summer",1,0.4,0.9,0.7,0.3,0.9,0.4;"ACT/NSW","n/a","Autumn",0.8,0.3,0.7,0.3,0.2,0.7,0.3;"ACT/NSW","n/a","Winter",0.4,0.1,0.4,0.2,0.1,0.4,0.1;"South Australia","n/a","Spring",0.99,1.1,0.88,0.55,0.55,0.88,0.22;"South Australia","n/a","Summer",0.77,0,0.66,0.22,0,0.66,0;"South Australia","n/a","Autumn",0.9,-1.1,0.7,0.22,-0.55,0.8,-0.22;"South Australia","n/a","Winter",0.88,0,0.77,0.55,0,0.82,0;"Tasmania","n/a","Spring",1,0.5,1,1,-0.44,1,0.5;"Tasmania","n/a","Summer",0.82,0.55,0.71,0.55,0.99,0.77,0.5;"Tasmania","n/a","Autumn",0.77,0.5,0.55,0.11,-0.33,0.6,0.33;"Tasmania","n/a","Winter",0.11,-0.27,0.11,0.22,-0.44,0.16,-0.22;"Victoria","n/a","Spring",1.1,1.1,1.1,0.99,0.99,1.1,0.77;"Victoria","n/a","Summer",0.33,0.33,0.22,0.33,-0.1,0.33,0.11;"Victoria","n/a","Autumn",0.5,0.2,0.55,0.44,0.2,0.55,0.2;"Victoria","n/a","Winter",0.55,0.22,0.49,0.22,0.22,0.49,0.33;"Western Australia","South West","Spring",1.64,1.1,1.21,0.99,0.66,1.42,1.1;"Western Australia","South West","Summer",0.44,-0.22,0.44,0.33,-0.22,0.44,-0.11;"Western Australia","South West","Autumn",0.6,0,0.6,0.22,-0.55,0.6,0;"Western Australia","South West","Winter",0.99,0.22,0.77,0.11,0.11,0.77,0.44;"Western Australia","Pilbara","Spring",0.7,-0.55,0.7,0.22,-0.22,0.7,-0.22;"Western Australia","Pilbara","Summer",0.77,0.55,0.77,0.66,0.55,0.77,0.33;"Western Australia","Pilbara","Autumn",0.88,0.55,0.88,0.22,0.22,0.88,0.22;"Western Australia","Pilbara","Winter",0.22,-0.55,0.22,0.11,-0.22,0.22,-0.33;"Western Australia","Kimberley","Spring",0.22,-0.55,0.33,0.22,-0.33,0.22,-0.55;"Western Australia","Kimberley","Summer",0.8,0.55,0.7,0.44,0.66,0.8,0.55;"Western Australia","Kimberley","Autumn",0.66,0.55,0.55,0.55,0.11,0.66,0.55;"Western Australia","Kimberley","Winter",0.33,-0.55,0.11,0.11,-0.44,0.33,-0.55}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGain_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.3")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGain_Title">_xlfn.LAMBDA("Beef pasture cattle - Liveweight gain (kg) (LWGjkl)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGain_Unit">_xlfn.LAMBDA("kg")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGain_Variable">_xlfn.LAMBDA("LWGjkl")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGain_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Replaced 'n/a' with 'South West' for first four rows of Western Australia to be consistent with table A.1.2.1")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGainNTQLD_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(29, 13, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Season","Bull &lt;1","Bull &gt;1","Cow &lt;1","Cow 1-2","Cow 2-3","Cow &gt;3","Steer &lt;1","Steer 1-2","Steer 2-3","Steer &gt;3";"Northern Territory","Alice Springs","Spring",0.22,-0.23,0.25,0.17,0.18,-0.28,0.32,0.24,0.25,-0.05;"Northern Territory","Alice Springs","Summer",0.66,0.2,0.62,0.54,0.38,0.27,0.75,0.64,0.55,0.48;"Northern Territory","Alice Springs","Autumn",0.49,0.13,0.54,0.45,0.35,0.15,0.63,0.54,0.42,0.26;"Northern Territory","Alice Springs","Winter",0.27,-0.8,0.22,0.09,0.12,0.02,0.25,0.18,0.12,0.03;"Northern Territory","Barkly","Spring",0.22,-0.44,0.2,0.21,0.18,0.01,0.12,0.09,"NO","NO";"Northern Territory","Barkly","Summer",0.66,0.22,0.68,0.22,0.24,0.25,0.64,0.37,"NO","NO";"Northern Territory","Barkly","Autumn",0.49,0.05,0.64,0.25,0.29,0.12,0.57,0.49,"NO","NO";"Northern Territory","Barkly","Winter",0.27,-0.27,0.31,0.29,0.19,0.04,0.26,0.28,"NO","NO";"Northern Territory","Northern","Spring",0.22,-0.44,0,0.15,0.08,0.17,0.06,0.02,-0.14,"NO";"Northern Territory","Northern","Summer",0.66,0.22,0.79,0.4,0.38,0.27,0.8,0.16,0.3,"NO";"Northern Territory","Northern","Autumn",0.49,0.05,0.55,0.38,0.36,0.06,0.58,0.23,0.4,"NO";"Northern Territory","Northern","Winter",0.27,-0.27,0.02,0.09,0.16,-0.04,0.21,0.03,0.11,"NO";"Queensland","High","Spring",0.27,-0.19,0.38,0.25,0.07,0.05,0.52,0.55,0.19,0.6;"Queensland","High","Summer",0.16,0.16,0.8,0.57,0.76,0.49,0.84,0.51,0.36,0.17;"Queensland","High","Autumn",0.45,0.1,0.49,0.41,0.4,0.17,0.54,0.64,-0.05,0.32;"Queensland","High","Winter",0.51,-0.07,0.13,-0.09,-0.13,0.07,0.25,0.71,0.17,0.43;"Queensland","Moderate/High","Spring",-0.12,-0.19,0.41,0.09,0.41,-0.19,0.07,1.07,-0.08,0;"Queensland","Moderate/High","Summer",0.65,0.19,0.65,0.51,0.18,0.63,1.3,0.48,1.12,0.38;"Queensland","Moderate/High","Autumn",0.7,0.13,0.52,0.34,0.02,0.04,0.77,0.42,0.12,0.74;"Queensland","Moderate/High","Winter",0.32,-0.06,0.25,0.19,-0.1,-0.02,0.02,0.23,-0.13,0;"Queensland","Moderate/Low","Spring",0.62,-0.19,0.37,0.41,0.06,-0.02,0.47,0.44,0.3,0.13;"Queensland","Moderate/Low","Summer",0.05,0.19,0.31,0.54,0.53,0.15,0.28,0.57,0.42,0.4;"Queensland","Moderate/Low","Autumn",0.33,0.13,0.39,0.36,0.26,0.11,0.4,0.44,0.37,-0.01;"Queensland","Moderate/Low","Winter",0.61,-0.06,0.21,0.18,0.12,0.06,0.29,0.41,0.41,-0.15;"Queensland","Low","Spring",-0.2,0.02,0.24,0.3,0.23,-0.05,0.34,0.3,0.57,0.52;"Queensland","Low","Summer",0.62,0.21,0.25,0.32,0.47,0.31,0.14,0.4,0.26,0.43;"Queensland","Low","Autumn",0.4,0.13,0.12,0.27,0.3,0.08,0.13,0.24,0.15,0.21;"Queensland","Low","Winter",0.08,0.04,0.06,0.18,0.11,-0.07,0.13,0.16,0.4,0.33}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGainNTQLD_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.4")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGainNTQLD_Title">_xlfn.LAMBDA("Beef pasture cattle - Liveweight gain (kg) (LWGjkl) for NT and QLD")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGainNTQLD_Unit">_xlfn.LAMBDA("kg")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGainNTQLD_Variable">_xlfn.LAMBDA("LWGjkl")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightGainNTQLD_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightNTQLD_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(29, 13, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Season","Bull &lt;1","Bull &gt;1","Cows &lt;1","Cows 1-2","Cows 2-3","Cows &gt;3","Steer &lt;1","Steer 1-2","Steer 2-3","Steer &gt;3";"Northern Territory","Alice Springs","Spring",220,706,208,323,415,467,223,371,493,585;"Northern Territory","Alice Springs","Summer",110,703,112,256,368,465,108,280,421,543;"Northern Territory","Alice Springs","Autumn",170,721,169,306,392,464,176,339,470,580;"Northern Territory","Alice Springs","Winter",200,727,211,338,432,492,222,377,498,590;"Northern Territory","Barkly","Spring",220,620,227,319,398,452,216,334,"NO","NO";"Northern Territory","Barkly","Summer",110,650,108,262,346,430,111,236,"NO","NO";"Northern Territory","Barkly","Autumn",170,670,170,266,363,444,169,282,"NO","NO";"Northern Territory","Barkly","Winter",200,660,225,307,398,452,214,326,"NO","NO";"Northern Territory","Northern","Spring",220,620,177,267,365,406,231,249,324,"NO";"Northern Territory","Northern","Summer",110,650,102,203,299,380,102,218,263,"NO";"Northern Territory","Northern","Autumn",170,670,173,250,336,414,175,243,304,"NO";"Northern Territory","Northern","Winter",200,660,202,272,365,390,208,260,337,"NO";"Queensland","High","Spring",260,705,215,302,416,519,234,455,551,660;"Queensland","High","Summer",153,703,118,277,397,483,111,304,521,547;"Queensland","High","Autumn",168,718,191,319,440,506,188,326,520,582;"Queensland","High","Winter",235,722,207,352,470,514,209,421,512,605;"Queensland","Moderate/High","Spring",230,674,217,344,357,467,242,370,550,620;"Queensland","Moderate/High","Summer",113,669,113,283,361,477,120,273,545,553;"Queensland","Moderate/High","Autumn",172,685,172,309,376,471,238,329,573,620;"Queensland","Moderate/High","Winter",241,692,208,344,364,484,260,350,567,620;"Queensland","Moderate/Low","Spring",236,674,178,310,428,466,193,370,519,565;"Queensland","Moderate/Low","Summer",120,669,112,250,390,448,115,273,433,556;"Queensland","Moderate/Low","Autumn",125,685,140,277,407,455,141,296,445,593;"Queensland","Moderate/Low","Winter",180,692,183,316,438,468,189,354,500,553;"Queensland","Low","Spring",190,617,174,265,371,415,170,272,392,531;"Queensland","Low","Summer",119,591,140,205,310,405,133,218,315,445;"Queensland","Low","Autumn",175,610,163,232,351,427,146,242,320,471;"Queensland","Low","Winter",192,615,162,255,364,420,157,261,342,484}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightNTQLD_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.2")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightNTQLD_Title">_xlfn.LAMBDA("Beef pasture cattle - Liveweight (kg) (Wjkl) for NT and QLD")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightNTQLD_Unit">_xlfn.LAMBDA("kg")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightNTQLD_Variable">_xlfn.LAMBDA("Wjkl")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_LiveweightNTQLD_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneConversionFactorPerRegion_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(16, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Region","Pasture range and paddock","Uncovered Anaerobic lagoon";"ACT","n/a",0.0047,0.71;"NSW","n/a",0.0047,0.75;"SA","n/a",0.0047,0.74;"TAS","n/a",0.0047,0.7;"VIC","n/a",0.0047,0.74;"WA","South West",0.0047,0.76;"WA","Pilbara",0.0047,0.76;"WA","Kimberley",0.0047,0.76;"NT","Alice Springs",0.0047,0.8;"NT","Barkly",0.0047,0.8;"NT","Northern",0.0047,0.8;"QLD","High",0.0047,0.78;"QLD","Moderate/High",0.0047,0.78;"QLD","Moderate/Low",0.0047,0.78;"QLD","Low",0.0047,0.78}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneConversionFactorPerRegion_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.10")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneConversionFactorPerRegion_Title">_xlfn.LAMBDA("Beef pasture cattle - Methane conversion factor per region (fraction) (MCFim)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneConversionFactorPerRegion_Unit">_xlfn.LAMBDA("fraction")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneConversionFactorPerRegion_Variable">_xlfn.LAMBDA("MCFim")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneConversionFactorPerRegion_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Removed comma from 'Pasture range and paddock' to aid lookup")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneEmissionsPotential_Data">_xlfn.LAMBDA(0.19)</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneEmissionsPotential_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.2.3 CONSTANTS")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneEmissionsPotential_Title">_xlfn.LAMBDA("Methane emissions potential")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneEmissionsPotential_Unit">_xlfn.LAMBDA("m3 CH4 / kg VS")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneEmissionsPotential_Variable">_xlfn.LAMBDA("B0")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_MethaneEmissionsPotential_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 9, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State","Bulls &lt;1","Bulls &gt;1","Cows &lt;1","Cows 1-2","Cows &gt;2","Steer &lt;1","Steer &gt;1","State abbreviation";"ACT",700,700,500,500,500,600,600,"ACT";"NSW",700,700,500,500,500,600,600,"NSW";"Northern Territory",770,770,550,550,550,660,660,"NT";"Queensland",770,770,550,550,550,660,660,"QLD";"South Australia",770,770,550,550,550,660,660,"SA";"Tasmania",770,770,550,550,550,660,660,"TAS";"Victoria",770,770,550,550,550,660,660,"VIC";"Western Australia",770,770,550,550,550,660,660,"WA"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.2.8")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Title">_xlfn.LAMBDA("Beef pasture cattle - Standard reference weights (kg) (SRWk)")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Unit">_xlfn.LAMBDA("kg")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Variable">_xlfn.LAMBDA("SRWk")</definedName>
+    <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Split ACT and NSW into separate rows. Added 'State abbreviation' column to aid lookup.")</definedName>
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
@@ -79,27 +513,29 @@
     <definedName name="VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method2">#REF!</definedName>
     <definedName name="VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method1">#REF!</definedName>
     <definedName name="VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method2">#REF!</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'Input - Enterprise'!$E$19</definedName>
+    <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'Input - Enterprise'!$E$18</definedName>
     <definedName name="X_Cell_PastureBeef_Breed">#REF!</definedName>
     <definedName name="X_Cell_PastureBeef_FencedWater">#REF!</definedName>
     <definedName name="X_Cell_PastureBeef_GrazingIrrigationMethod">#REF!</definedName>
     <definedName name="X_Cell_PastureBeef_GrazingProductionSystem">#REF!</definedName>
     <definedName name="X_Cell_PastureBeef_ProductionRegion">#REF!</definedName>
-    <definedName name="X_Cell_Site_AverageTemperature">#REF!</definedName>
-    <definedName name="X_Cell_Site_ClimateZone">#REF!</definedName>
-    <definedName name="X_Cell_Site_Elevation">#REF!</definedName>
-    <definedName name="X_Cell_Site_FarmName">#REF!</definedName>
-    <definedName name="X_Cell_Site_FrostDays">#REF!</definedName>
-    <definedName name="X_Cell_Site_LeachingZone">#REF!</definedName>
-    <definedName name="X_Cell_Site_MapPetRatio">#REF!</definedName>
-    <definedName name="X_Cell_Site_PotentialEvapotranspiration">#REF!</definedName>
-    <definedName name="X_Cell_Site_RainfallZone">#REF!</definedName>
-    <definedName name="X_Cell_Site_Region">#REF!</definedName>
-    <definedName name="X_Cell_Site_ReportingEntityName">#REF!</definedName>
-    <definedName name="X_Cell_Site_StartDate">#REF!</definedName>
-    <definedName name="X_Cell_Site_State">#REF!</definedName>
-    <definedName name="X_Cell_Site_TemperatureZone">#REF!</definedName>
-    <definedName name="X_Cell_Site_TotalRainfall">#REF!</definedName>
-    <definedName name="X_Cell_Site_WetOrDryClimateZone">#REF!</definedName>
+    <definedName name="X_Cell_Site_AverageTemperature">'Input - Site'!$E$14</definedName>
+    <definedName name="X_Cell_Site_ClimateZone">'Input - Site'!$E$20</definedName>
+    <definedName name="X_Cell_Site_Elevation">'Input - Site'!$E$13</definedName>
+    <definedName name="X_Cell_Site_FarmName">'Input - Enterprise'!$E$7</definedName>
+    <definedName name="X_Cell_Site_FrostDays">'Input - Site'!$E$17</definedName>
+    <definedName name="X_Cell_Site_LeachingZone">'Input - Site'!$E$12</definedName>
+    <definedName name="X_Cell_Site_MapPetRatio">'Input - Site'!$E$18</definedName>
+    <definedName name="X_Cell_Site_PotentialEvapotranspiration">'Input - Site'!$E$16</definedName>
+    <definedName name="X_Cell_Site_RainfallZone">'Input - Site'!$E$19</definedName>
+    <definedName name="X_Cell_Site_Region">'Input - Site'!$E$11</definedName>
+    <definedName name="X_Cell_Site_ReportingEntityName">'Input - Enterprise'!$E$8</definedName>
+    <definedName name="X_Cell_Site_StartDate">'Input - Enterprise'!$E$12</definedName>
+    <definedName name="X_Cell_Site_State">'Input - Site'!$E$10</definedName>
+    <definedName name="X_Cell_Site_TemperatureZone">'Input - Site'!$E$22</definedName>
+    <definedName name="X_Cell_Site_TotalRainfall">'Input - Site'!$E$15</definedName>
+    <definedName name="X_Cell_Site_WetOrDryClimateZone">'Input - Site'!$E$21</definedName>
     <definedName name="X_Table_PastureBeef_CrudeProtein_Method1">#REF!</definedName>
     <definedName name="X_Table_PastureBeef_CrudeProtein_Method2">#REF!</definedName>
     <definedName name="X_Table_PastureBeef_DryMatterDigestibility_Method1">#REF!</definedName>
@@ -134,9 +570,10 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
@@ -147,6 +584,20 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </cellMetadata>
   <valueMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
@@ -156,7 +607,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="187">
   <si>
     <t>Home</t>
   </si>
@@ -182,9 +633,6 @@
     <t>GHG Unit</t>
   </si>
   <si>
-    <t>CO2-e unit</t>
-  </si>
-  <si>
     <t>t CH4</t>
   </si>
   <si>
@@ -219,20 +667,577 @@
   </si>
   <si>
     <t>4.2.1.7-8 Soil leaching and runoff</t>
+  </si>
+  <si>
+    <t>Production timeframe start</t>
+  </si>
+  <si>
+    <t>Production timeframe end</t>
+  </si>
+  <si>
+    <t>Production timeframe length</t>
+  </si>
+  <si>
+    <t>Emissions calculation period start date</t>
+  </si>
+  <si>
+    <t>Emissions calculation period end date</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Liveweight sold</t>
+  </si>
+  <si>
+    <t>Liveweight grown - method 1</t>
+  </si>
+  <si>
+    <t>Liveweight grown - method 2</t>
+  </si>
+  <si>
+    <t>Manure produced</t>
+  </si>
+  <si>
+    <t>Percent manure sold</t>
+  </si>
+  <si>
+    <t>Percent manure applied as fertiliser on own farm</t>
+  </si>
+  <si>
+    <t>Percent manure applied to soil with no purpose (as waste)</t>
+  </si>
+  <si>
+    <t>Livestock sales</t>
+  </si>
+  <si>
+    <t>⚠️ Livestock sales are not automatically reflected in the herd movement data - you will need to manually adjust head count and average liveweight</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Sale date</t>
+  </si>
+  <si>
+    <t>Head sold</t>
+  </si>
+  <si>
+    <t>Average weight per head (kg)</t>
+  </si>
+  <si>
+    <t>Total liveweight sold</t>
+  </si>
+  <si>
+    <t>Bulls &gt; 1 year</t>
+  </si>
+  <si>
+    <t>tonnes</t>
+  </si>
+  <si>
+    <t>Constants - Common</t>
+  </si>
+  <si>
+    <t>State/Territory</t>
+  </si>
+  <si>
+    <t>Common Name</t>
+  </si>
+  <si>
+    <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>SA 4 Name</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>CO2-e factor</t>
+  </si>
+  <si>
+    <t>Conversion factor</t>
+  </si>
+  <si>
+    <t>Conversion factor 1</t>
+  </si>
+  <si>
+    <t>Conversion factor 2</t>
+  </si>
+  <si>
+    <t>Conversion factor combined</t>
+  </si>
+  <si>
+    <t>Climate zone</t>
+  </si>
+  <si>
+    <t>Wet or Dry Zone</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>MAP</t>
+  </si>
+  <si>
+    <t>Frost days per year</t>
+  </si>
+  <si>
+    <t>Elevation</t>
+  </si>
+  <si>
+    <t>MAP:PET</t>
+  </si>
+  <si>
+    <t>Min temp</t>
+  </si>
+  <si>
+    <t>Max temp</t>
+  </si>
+  <si>
+    <t>Min rainfall</t>
+  </si>
+  <si>
+    <t>Max rainfall</t>
+  </si>
+  <si>
+    <t>Min frost days</t>
+  </si>
+  <si>
+    <t>Max frost days</t>
+  </si>
+  <si>
+    <t>Min elevation</t>
+  </si>
+  <si>
+    <t>Max elevation</t>
+  </si>
+  <si>
+    <t>Min MAP:PET</t>
+  </si>
+  <si>
+    <t>Max MAP:PET</t>
+  </si>
+  <si>
+    <t>Temperature Zone</t>
+  </si>
+  <si>
+    <t>Min MAT</t>
+  </si>
+  <si>
+    <t>Max MAT</t>
+  </si>
+  <si>
+    <t>Rainfall Zone</t>
+  </si>
+  <si>
+    <t>Annual rainfall</t>
+  </si>
+  <si>
+    <t>Leaching Zone</t>
+  </si>
+  <si>
+    <t>Leaching criteria</t>
+  </si>
+  <si>
+    <t>Is in leaching zone</t>
+  </si>
+  <si>
+    <t>FracWET</t>
+  </si>
+  <si>
+    <t>Irrigation type i</t>
+  </si>
+  <si>
+    <t>Data source</t>
+  </si>
+  <si>
+    <t>Data score</t>
+  </si>
+  <si>
+    <t>Production system j</t>
+  </si>
+  <si>
+    <t>EFN2O</t>
+  </si>
+  <si>
+    <t>Production system only</t>
+  </si>
+  <si>
+    <t>Irrigation method</t>
+  </si>
+  <si>
+    <t>Rainfall zone</t>
+  </si>
+  <si>
+    <t>EFPRP</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Season</t>
+  </si>
+  <si>
+    <t>Temperature zone</t>
+  </si>
+  <si>
+    <t>MAT (ºC)</t>
+  </si>
+  <si>
+    <t>Anaerobic lagoon</t>
+  </si>
+  <si>
+    <t>Digester / covered lagoons</t>
+  </si>
+  <si>
+    <t>Liquid systems</t>
+  </si>
+  <si>
+    <t>Daily spread</t>
+  </si>
+  <si>
+    <t>Composting (passive windrow)</t>
+  </si>
+  <si>
+    <t>Solid storage</t>
+  </si>
+  <si>
+    <t>Pit storage</t>
+  </si>
+  <si>
+    <t>Deep litter</t>
+  </si>
+  <si>
+    <t>Poultry manure with bedding</t>
+  </si>
+  <si>
+    <t>Poultry manure without bedding</t>
+  </si>
+  <si>
+    <t>Direct processing</t>
+  </si>
+  <si>
+    <t>Direct application</t>
+  </si>
+  <si>
+    <t>Pasture range and paddock</t>
+  </si>
+  <si>
+    <t>MAT raw</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>EFNi &amp; EFN2Oi</t>
+  </si>
+  <si>
+    <t>Input - Site</t>
+  </si>
+  <si>
+    <t>Your business</t>
+  </si>
+  <si>
+    <t>Farm name</t>
+  </si>
+  <si>
+    <t>Test Farms</t>
+  </si>
+  <si>
+    <t>Reporting entity name</t>
+  </si>
+  <si>
+    <t>Test Farms Pty Ltd</t>
+  </si>
+  <si>
+    <t>💡An 'Emissions accounting period' is a 12 month period where the business can report on the emissions, and is typically the same as the business' financial accounting period.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">← </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DD/MM/YYYY or DD Month YYYY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">← </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Automatically calculated, 12 months after start date</t>
+    </r>
+  </si>
+  <si>
+    <t>Location and climate</t>
+  </si>
+  <si>
+    <t>Location information is used to reference some region and climate-specific emission factors</t>
+  </si>
+  <si>
+    <t>Tip: Use the web-based GAF Location Helper tool to easily get region and climate information. You will need an internet connection to use the GAF Location Helper.</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Western Australia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">← </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Please select</t>
+    </r>
+  </si>
+  <si>
+    <t>Region (ABS Statistical area level 4) if state is WA</t>
+  </si>
+  <si>
+    <t>Western Australia - Outback (South)</t>
+  </si>
+  <si>
+    <t>Leaching zone</t>
+  </si>
+  <si>
+    <t>NO - Not in leaching zone</t>
+  </si>
+  <si>
+    <t>Meters</t>
+  </si>
+  <si>
+    <t>Average temperature for reporting period</t>
+  </si>
+  <si>
+    <t>Degrees celsius</t>
+  </si>
+  <si>
+    <t>Total rainfall for reporting period</t>
+  </si>
+  <si>
+    <t>Millimetres</t>
+  </si>
+  <si>
+    <t>Potential evapotranspiration for reporting period</t>
+  </si>
+  <si>
+    <t>Number of frost days for reporting period</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>MAP:PET ratio</t>
+  </si>
+  <si>
+    <t>Wet or dry climate zone</t>
+  </si>
+  <si>
+    <t>Emissions for whole production cycle</t>
+  </si>
+  <si>
+    <t>Emissions calculation cycle</t>
+  </si>
+  <si>
+    <t>Enter the method 1 and 2 CO2e emissions from prevoius emissions calculation periods if applicable.</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Product emissions</t>
+  </si>
+  <si>
+    <t>Amount (tonnnes)</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Emissions allocation (mass)</t>
+  </si>
+  <si>
+    <t>Manure sold</t>
+  </si>
+  <si>
+    <t>t co2e/t liveweight sold</t>
+  </si>
+  <si>
+    <t>t co2e/t manure</t>
+  </si>
+  <si>
+    <t>Emissions intensity (Method 1)</t>
+  </si>
+  <si>
+    <t>Emissions intensity (Method 2)</t>
+  </si>
+  <si>
+    <t>Product type</t>
+  </si>
+  <si>
+    <t>Main product</t>
+  </si>
+  <si>
+    <t>Co-product</t>
+  </si>
+  <si>
+    <t>Manure used as fertiliser on own farm</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Residual product</t>
+  </si>
+  <si>
+    <t>Carbon removals from plantings</t>
+  </si>
+  <si>
+    <t>CO2 removed attributed to this enterprise</t>
+  </si>
+  <si>
+    <t>t CO2</t>
+  </si>
+  <si>
+    <t>Total emissions for production cycle</t>
+  </si>
+  <si>
+    <t>Total carbon removals for production cycle</t>
+  </si>
+  <si>
+    <t>Net emissions</t>
+  </si>
+  <si>
+    <t>Method 1</t>
+  </si>
+  <si>
+    <t>Method 2</t>
+  </si>
+  <si>
+    <t>Liveweight grown - Method 1</t>
+  </si>
+  <si>
+    <t>Liveweight grown - Method 2</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>t co2e/t liveweight grown</t>
+  </si>
+  <si>
+    <t>3.2.1.1-2 Enteric methane</t>
+  </si>
+  <si>
+    <t>5.1.1.1-2 Inorganic fert N2O</t>
+  </si>
+  <si>
+    <t>5.1.1.3-4 Inorganic fert CO2</t>
+  </si>
+  <si>
+    <t>5.2.1.1-2 Organic fert N2O</t>
+  </si>
+  <si>
+    <t>5.3.1.1-2 Lime CO2</t>
+  </si>
+  <si>
+    <t>5.4.1.1-4 Atmos. deposition</t>
+  </si>
+  <si>
+    <t>5.5.1.1-2 Leaching &amp; runoff</t>
+  </si>
+  <si>
+    <t>6.2.1.1-2 Pasture residue N2O</t>
+  </si>
+  <si>
+    <t>6.3.1.1-2 Leach &amp; runoff (pasture)</t>
+  </si>
+  <si>
+    <t>8.1.1.1-2 Transport fuel CO2</t>
+  </si>
+  <si>
+    <t>8.1.1.1-2 Transport fuel N2O</t>
+  </si>
+  <si>
+    <t>8.1.1.1-2 Transport fuel CH4</t>
+  </si>
+  <si>
+    <t>8.2.1.1-2 Stationary fuel CO2</t>
+  </si>
+  <si>
+    <t>8.2.1.1-2 Stationary fuel CH4</t>
+  </si>
+  <si>
+    <t>8.2.1.1-2 Stationary fuel N2O</t>
+  </si>
+  <si>
+    <t>14.1.1-2 Purchased electricity (Location-based)</t>
+  </si>
+  <si>
+    <t>14.1.1-2 Purchased electricity (Market-based)</t>
+  </si>
+  <si>
+    <t>Enter value</t>
+  </si>
+  <si>
+    <t>Input - Enterprise</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="5">
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="d/mm/yyyy;@"/>
     <numFmt numFmtId="167" formatCode="[$-C09]dd\-mmmm\-yyyy;@"/>
     <numFmt numFmtId="168" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +1517,80 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -609,7 +1688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -674,8 +1753,127 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.749961851863155"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="66">
+  <cellStyleXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -862,8 +2060,11 @@
     <xf numFmtId="0" fontId="41" fillId="15" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -899,20 +2100,11 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="12" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="8" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="53">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="32"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="53" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="4" borderId="0" xfId="11">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -926,14 +2118,208 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="7" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="15">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="0" xfId="59">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="41">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="52">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="12">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="16">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="4" borderId="2" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="7">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="54">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="7" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="5" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="14">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="8" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="7" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="8" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="9" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="10" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="2" xfId="40" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="11" xfId="39" applyFont="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="12" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="13" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="14" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="15" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="16" xfId="39" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="17" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="29" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="47" fillId="0" borderId="0" xfId="17" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="26" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="47" fillId="4" borderId="0" xfId="17" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="47" fillId="4" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="4" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="50" fillId="4" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="7" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="5" xfId="39">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="0" xfId="66" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="18" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="4" borderId="0" xfId="67" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="7" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="56">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="4" borderId="0" xfId="8" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="0" xfId="8" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="66">
+  <cellStyles count="69">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
     <cellStyle name="Arguments" xfId="63" xr:uid="{D74147AB-B374-43DE-928A-C20FDAA7023A}"/>
     <cellStyle name="Arguments hyperlink" xfId="62" xr:uid="{E9A63CA8-EB4E-4FD6-930A-AD1711340AFB}"/>
     <cellStyle name="Block heading" xfId="5" xr:uid="{74527274-3B4A-494A-B37C-EA50686E114C}"/>
     <cellStyle name="Block subheading" xfId="47" xr:uid="{34E62905-A3E0-4883-B81A-BDB58FC88DA7}"/>
     <cellStyle name="Code" xfId="24" xr:uid="{99B3520F-01DD-4F8E-A8D0-24EAA04E90EB}"/>
+    <cellStyle name="Comma" xfId="67" builtinId="3"/>
     <cellStyle name="Content bold" xfId="7" xr:uid="{468A1381-682E-4BF1-945B-DF2E2BCA4419}"/>
     <cellStyle name="Content bold total" xfId="27" xr:uid="{17159E75-EF9F-42B8-8195-E83583796F67}"/>
     <cellStyle name="Content hidden" xfId="50" xr:uid="{8E56D08F-467A-4F3D-ADA8-ECA27B2FFCD3}"/>
@@ -942,6 +2328,7 @@
     <cellStyle name="Equation source" xfId="6" xr:uid="{348FC12D-3392-478F-B0B3-D4FA4BBA59E4}"/>
     <cellStyle name="Equation table header" xfId="1" xr:uid="{11780056-D3CA-48D4-90AF-8DF1A50E1B13}"/>
     <cellStyle name="Euqation table row 2" xfId="13" xr:uid="{2CAEAB93-BC87-4606-B5A1-3C2F7B5C52A1}"/>
+    <cellStyle name="Hyperlink" xfId="66" builtinId="8"/>
     <cellStyle name="Information tip" xfId="39" xr:uid="{7D200D09-32E3-4546-9822-1B93AD118A74}"/>
     <cellStyle name="Information variation" xfId="54" xr:uid="{205494A3-14DD-4E6A-BDD3-5C5A864D6FA7}"/>
     <cellStyle name="Input block subheading" xfId="30" xr:uid="{A9FEBDB0-0992-4E30-96E5-9F9CAE92E3FB}"/>
@@ -986,6 +2373,7 @@
     <cellStyle name="Page heading" xfId="2" xr:uid="{255E304E-A5AB-40F0-8E3A-91C132147F10}"/>
     <cellStyle name="Page section heading" xfId="4" xr:uid="{B654AFF3-28A2-43B8-AE91-E7D2C159A294}"/>
     <cellStyle name="Page source" xfId="3" xr:uid="{35DF92BD-4909-4EA7-B1E6-C0EDAAEB1713}"/>
+    <cellStyle name="Percent" xfId="68" builtinId="5"/>
     <cellStyle name="Results table column header" xfId="60" xr:uid="{A846043F-10AE-4BED-BAA6-90407C977915}"/>
     <cellStyle name="Table description" xfId="58" xr:uid="{8BD2F353-2E3C-42FF-89E9-616E85DC18C5}"/>
     <cellStyle name="Table name" xfId="57" xr:uid="{D56F17A4-9740-44B6-BDDB-150E2C950B8B}"/>
@@ -995,7 +2383,871 @@
     <cellStyle name="Variable type input" xfId="65" xr:uid="{69904D21-1566-4CAB-9A42-C86AC6535120}"/>
     <cellStyle name="Variable type other" xfId="64" xr:uid="{105BD9DE-B567-4DA0-87E6-C60A0ECC1C65}"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="48">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1" tint="0.24994659260841701"/>
@@ -1198,20 +3450,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="11"/>
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstColumn" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="wholeTable" dxfId="47"/>
+      <tableStyleElement type="headerRow" dxfId="46"/>
+      <tableStyleElement type="totalRow" dxfId="45"/>
+      <tableStyleElement type="firstColumn" dxfId="44"/>
+      <tableStyleElement type="firstRowStripe" dxfId="43"/>
+      <tableStyleElement type="secondRowStripe" dxfId="42"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="totalRow" dxfId="3"/>
-      <tableStyleElement type="firstColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="41"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="totalRow" dxfId="39"/>
+      <tableStyleElement type="firstColumn" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="secondRowStripe" dxfId="36"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -2043,6 +4295,486 @@
 </richValueRels>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CBCD503-838A-4523-932C-9BA527D1C34C}" name="Table_Input_LivestockSales3" displayName="Table_Input_LivestockSales3" ref="D33:H35" totalsRowShown="0">
+  <autoFilter ref="D33:H35" xr:uid="{6CBCD503-838A-4523-932C-9BA527D1C34C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{10611EAE-C98A-4772-A79C-DBC0DEE0D909}" name="Class"/>
+    <tableColumn id="2" xr3:uid="{C72E6C94-BA4D-4748-84FC-BCCF1BBBA7D6}" name="Sale date"/>
+    <tableColumn id="3" xr3:uid="{BC87B559-6411-49E0-9FED-D9EC6CFBBD83}" name="Head sold"/>
+    <tableColumn id="4" xr3:uid="{F08DE3C5-21CB-42C6-A868-7EFDDF741BF4}" name="Average weight per head (kg)"/>
+    <tableColumn id="5" xr3:uid="{9F84455A-39E1-4212-B9E8-759D853A4C96}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
+      <calculatedColumnFormula>F34*G34</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{EC0B98FF-3B1A-4F33-9028-A6B26A7E6CE4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+  <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{BBC50AC7-FEC1-431E-AD41-7CB9E130FE72}" name="Leaching Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{ED997B4B-69AA-458D-AD94-F4C79A1B94D0}" name="Leaching criteria">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C1B321B1-DD2B-4EC5-AE20-D47C87F02BBF}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+  <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{18CA1470-758E-4475-BE8B-25D35A86BE01}" name="Data source">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{1F17B60B-4C21-4D79-B503-2BB5C2CDDBDF}" name="Data score">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{14C890C4-4A77-40EC-A6C1-19C0895BD309}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+  <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{AEB37CE8-5689-4CCA-AF1D-E45E37F37CC1}" name="Is in leaching zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{8ABB6BDF-FE17-4B3B-BDE2-B9AAF30FF3BD}" name="FracWET" dataDxfId="19">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6BB36C9A-81C9-4008-9621-02E7765F4217}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+  <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7F8F31AC-00F6-4249-87C9-3FC6FE61BBC6}" name="Production system j">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{C297EA64-FE6E-4A07-A69E-528AF5291D69}" name="EFN2O">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{6AF2FB50-AEC5-4A97-85DD-5BA28FE67661}" name="Production system only">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{86FFBCC3-0C43-4C00-A2EE-6BE3F2E4BF06}" name="Irrigation method">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{149802D4-7D06-4288-AFC4-EA24F6C8F48E}" name="Rainfall zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{81046769-5E78-4435-8902-BE2F7ED271E9}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+  <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1EE4C9C2-CE36-41D3-A67F-CC85678D8B80}" name="Irrigation type i">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{DD5CBEE2-8756-4D0C-9A90-6E931CF609D0}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0D2D24A9-44B5-40A8-9D93-5D127038E490}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+  <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{76483A9E-91D3-4695-AB70-E830E24596D9}" name="Climate zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{1127A673-CAEF-41F9-A48A-D438D3FFF619}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E20A54E0-06E3-423D-998B-2E4A7C9A48F2}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+  <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{A2A66992-064C-4170-856F-B81D835CEE21}" name="Month">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{48B6FC8D-6503-4BB2-B07D-00597C808CB0}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{06A63BFC-1602-47C1-AF55-49AA6B4633CD}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+  <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{D344A8E3-CBAD-4F7E-B0CA-85C4550A31FF}" name="Temperature zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{4C26B9B4-F509-4ACF-A306-F52C2D83B94C}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{06D3FCFB-672E-43AB-BAD6-C5F3A36DC255}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{286B0E39-9F46-4519-A952-1FCC90F0A23E}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{CAB3566B-B894-433E-9D4A-4CA76B82C3BD}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{6D655DEC-7C3C-4046-9046-7ABE03AF26CA}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{DC01C908-9F78-404B-A8A9-081231B6DBAF}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{016BC200-DE2E-4607-9A3A-E48F6A72FB0F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{3D073AF2-25E0-49BE-825D-D38FD86B34D8}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{2C00D039-8FF7-4CF7-B97D-987BAE97BA35}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{C3FD2E13-24D5-402A-8C77-E324B6925825}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{6CCAA4CD-85BD-481B-A987-0719DD47798C}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{12540CA2-E51E-45F0-A036-45D45913194C}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{393A0B3F-42CD-412F-B1E5-79CF90491213}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{44E9918F-2DF8-4DE9-AD76-C61362285599}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{FE671AF8-F8E0-4322-B78A-1B6A3A96A4E0}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{949FFD0F-1699-4700-8323-CF2162C2663F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{82DE88A1-FD3E-429F-81D0-81A0580D58D8}" name="Climate Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{3505652E-76CD-41ED-BC1F-830404A5E233}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BFA511D-1E33-4FA7-9E53-155741FDE40A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+  <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A7717A66-4BDA-43C0-BFCD-4A6F29AEE8A3}" name="State/Territory">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{D6D2A619-26C3-4096-9C5E-261DB4783E3F}" name="Common Name">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{8F8F275A-708B-458E-9ABF-5295B622DDF7}" name="Abbreviation">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A251EF82-BC21-4875-B405-6D0F230C2B8D}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+  <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
+    <filterColumn colId="0" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{0A16A557-CD1A-4230-A0E4-670FBDA4CD09}" name="SA 4 Name">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3F15B4B0-BD4E-4903-9096-ED3FE0A9167C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+  <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9BFA3AA7-7549-47B7-8147-49CC22B23598}" name="Gas">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{56BBDB36-E3BB-4678-8824-A909AEED8E49}" name="CO2-e factor">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{66C67C36-18E1-4B8A-BFF1-35CF3DC4AC81}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+  <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{BCBBB9D5-7AA2-41EA-B99D-63DD8E7116D6}" name="Gas">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{1F10E85A-E8E7-4403-B922-7CD822BDAAAC}" name="Conversion factor">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A186BBCE-16ED-4C60-8611-6582C90E465F}" name="Conversion factor 1">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{E1D6C7D2-A210-4091-8447-15F9317092F9}" name="Conversion factor 2">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{7B5653AF-5CD0-44F6-827E-4F17D013B028}" name="Conversion factor combined">
+      <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1D6C8105-982C-4B9F-A603-F884FE56E1B4}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+  <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{ED61DF3B-A431-4956-B923-158AD5BF4554}" name="Climate zone" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{277D098C-8B59-4F56-B373-2BF7AAA9A607}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{827CC720-B781-4728-ABFA-68C972B57850}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{38653B97-E186-444A-AFBD-15CE44DEBED7}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{735BA31E-1D4B-45A4-B9FF-7F8ED5243D20}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{370BE1BB-C3DF-4E43-B8DD-B18D69884A4B}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{37A53713-47F8-4F27-9505-8BED300E0222}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{D9399681-9FC5-41A0-A367-D4D41BBB28CA}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{65211A71-1ABE-4E6D-843C-B0028543D400}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{8ED03576-B413-4D12-B37A-5F11E15AA54D}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{E749576A-EB5F-4709-BD15-9BD4E87548D5}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{61CC0B40-56FD-487C-A589-45456757E8A1}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{32B52E24-5576-47A4-A024-CDC090D88746}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{B4341912-AB7E-4E58-9B4D-9791D45FB352}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{67418986-6C11-45D0-A4DC-D7861BD61C09}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{90614980-AE79-4306-A6ED-229525821D94}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D228FD2E-DAAA-4D4F-BEFF-0E68A1F33AA0}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+  <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{FEB61CA1-B375-461F-AD5A-5B01A03F7A14}" name="Climate zone" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{EE3C7A00-6DDA-427C-9573-7908B05111FB}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E436A27C-11D9-4092-B110-DE3B0C7D7A9C}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+  <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{3E477FC1-0E60-467C-87C8-DC619003DA7D}" name="Temperature Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{CD029E58-AF67-4858-BEF6-937BB536E757}" name="MAT">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{5195427E-32DD-4977-88C7-473D17A15EDE}" name="Min MAT">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{4C8D6B45-65E8-4A84-9B64-B4D1E990BE71}" name="Max MAT">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AA9D31FA-C10A-401A-A990-FD7418530E07}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+  <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{A1896C80-5B23-4971-85DF-908C9411D636}" name="Rainfall Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{776A729E-62FB-471E-9D55-F5C0C49DAFB1}" name="Annual rainfall">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{5C488583-1093-4920-BAEF-A4BD862E3623}" name="Min rainfall">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{EDCA589F-5D6E-4F25-A934-864B94D632CD}" name="Max rainfall">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2266,7 +4998,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="976" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="941" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2328,11 +5060,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="e" vm="1">
+      <c r="A1" s="17" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="25" t="s">
-        <v>15</v>
+      <c r="C1" s="22" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2388,27 +5120,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="G6" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="24" t="s">
+      <c r="I6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>8</v>
-      </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2418,17 +5148,23 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="19" t="e" cm="1">
+        <f t="array" ref="E7">VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F7" s="19" t="e" cm="1">
+        <f t="array" ref="F7">VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="16" t="s">
         <v>9</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="18" t="s">
-        <v>10</v>
       </c>
       <c r="K7" s="9"/>
     </row>
@@ -2439,17 +5175,21 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="18" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="19">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="K8" s="9"/>
     </row>
@@ -2457,17 +5197,21 @@
       <c r="A9" s="5"/>
       <c r="C9" s="9"/>
       <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="18" t="s">
-        <v>10</v>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="19">
+        <v>2</v>
+      </c>
+      <c r="I9" s="19">
+        <v>3</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="K9" s="9"/>
     </row>
@@ -2477,42 +5221,46 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="18" t="s">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="19">
+        <v>3</v>
+      </c>
+      <c r="I10" s="19">
+        <v>4</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="23">
-        <f>SUM(H7:H10)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="23">
-        <f>SUM(I7:I10)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="20" t="s">
-        <v>10</v>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="19">
+        <v>4</v>
+      </c>
+      <c r="I11" s="19">
+        <v>5</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="K11" s="9"/>
     </row>
@@ -2522,13 +5270,25 @@
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="19" t="e" cm="1">
+        <f t="array" ref="E12">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F12" s="19" t="e" cm="1">
+        <f t="array" ref="F12">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2537,359 +5297,617 @@
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="D13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="19" t="e" cm="1">
+        <f t="array" ref="E13">VEERG_5_1_1_3__1_InorganicFertiliserApplicationCO2Emissions_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F13" s="19" t="e">
+        <f>E13</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="D14" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="19" t="e" cm="1">
+        <f t="array" ref="E14">VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F14" s="19" t="e">
+        <f>E14</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="D15" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="19" t="e" cm="1">
+        <f t="array" ref="E15">VEERG_5_3_1_1__1_LimeApplicationCO2Emissions_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F15" s="19" t="e">
+        <f>E15</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="D16" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="19" t="e" cm="1">
+        <f t="array" ref="E16">VEERG_5_4_1_3__1_OrganicFertiliserAtmosphericDepositionN2OEmissions_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F16" s="19" t="e">
+        <f>E16</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="D17" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="19" t="e" cm="1">
+        <f t="array" ref="E17">VEERG_5_5_1_1__1_FertiliserLeachingAndRunoffN2OEmissions_result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F17" s="19" t="e">
+        <f>E17</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
       </c>
       <c r="C18" s="9"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="D18" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E18" s="19" t="e" cm="1">
+        <f t="array" ref="E18">VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F18" s="19" t="e" cm="1">
+        <f t="array" ref="F18">VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="D19" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="19" t="e" cm="1">
+        <f t="array" ref="E19">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_PastureOnly_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F19" s="19" t="e" cm="1">
+        <f t="array" ref="F19">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_PastureOnly_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="D20" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="19" t="e" cm="1">
+        <f t="array" ref="E20">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F20" s="19" t="e">
+        <f>E20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="D21" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="19" t="e" cm="1">
+        <f t="array" ref="E21">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F21" s="19" t="e">
+        <f>E21</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="C22" s="9"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="D22" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" s="19" t="e" cm="1">
+        <f t="array" ref="E22">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F22" s="19" t="e">
+        <f>E22</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="D23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" s="19" t="e" cm="1">
+        <f t="array" ref="E23">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F23" s="19" t="e">
+        <f>E23</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="D24" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24" s="19" t="e" cm="1">
+        <f t="array" ref="E24">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F24" s="19" t="e">
+        <f t="shared" ref="F24:F27" si="0">E24</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="D25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="19" t="e" cm="1">
+        <f t="array" ref="E25">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F25" s="19" t="e">
+        <f t="shared" si="0"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="D26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="19" t="e" cm="1">
+        <f t="array" ref="E26">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F26" s="19" t="e">
+        <f t="shared" si="0"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="9"/>
+      <c r="D27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="19" t="e" cm="1">
+        <f t="array" ref="E27">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F27" s="19" t="e">
+        <f t="shared" si="0"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="9"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="9"/>
+      <c r="D28" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="20">
+        <f>SUM(H7:H27)</f>
+        <v>10</v>
+      </c>
+      <c r="I28" s="20">
+        <f>SUM(I7:I27)</f>
+        <v>14</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="9"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="9"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="9"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="9"/>
-      <c r="D32" s="1"/>
+      <c r="D32" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
     </row>
-    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="9"/>
-      <c r="D33" s="1"/>
+      <c r="D33" s="90" t="str" cm="1">
+        <f t="array" ref="D33">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
+        <v>There are 3 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="9"/>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
     </row>
-    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="9"/>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="9"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
+      <c r="H35" s="14"/>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
     </row>
-    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="9"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="D36" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="H36" s="14"/>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
     </row>
-    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="9"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="D37" s="1" t="str" cm="1">
+        <f t="array" ref="D37:D39">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
+        <v>01 Jan 2023 to 31 Dec 2023</v>
+      </c>
+      <c r="E37" s="88" t="str">
+        <f>IF(ISBLANK($D37), "", IF(ISNUMBER(SEARCH("reporting", $D37)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="F37" s="88" t="str">
+        <f>IF(ISBLANK($D37), "", IF(ISNUMBER(SEARCH("reporting", $D37)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="14"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
     </row>
-    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="9"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
+      <c r="D38" s="1" t="str">
+        <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
+      </c>
+      <c r="E38" s="88">
+        <f>IF(ISBLANK($D38), "", IF(ISNUMBER(SEARCH("reporting", $D38)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v>10</v>
+      </c>
+      <c r="F38" s="88">
+        <f>IF(ISBLANK($D38), "", IF(ISNUMBER(SEARCH("reporting", $D38)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v>14</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
       <c r="K38" s="9"/>
     </row>
-    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="9"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
+      <c r="D39" s="1" t="str">
+        <v>01 Jan 2025 to 31 Dec 2025</v>
+      </c>
+      <c r="E39" s="88" t="str">
+        <f>IF(ISBLANK($D39), "", IF(ISNUMBER(SEARCH("reporting", $D39)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="F39" s="88" t="str">
+        <f>IF(ISBLANK($D39), "", IF(ISNUMBER(SEARCH("reporting", $D39)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="14"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
       <c r="K39" s="9"/>
     </row>
-    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="9"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
+      <c r="E40" s="88" t="str">
+        <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v/>
+      </c>
+      <c r="F40" s="88" t="str">
+        <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="9"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="88" t="str">
+        <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
+        <v/>
+      </c>
+      <c r="F41" s="88" t="str">
+        <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="14"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
       <c r="K41" s="9"/>
     </row>
-    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="9"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="D42" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="20">
+        <f>SUM(E37:E41)</f>
+        <v>10</v>
+      </c>
+      <c r="F42" s="20">
+        <f>SUM(F37:F41)</f>
+        <v>14</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="9"/>
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2899,8 +5917,8 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="9"/>
       <c r="K43" s="9"/>
     </row>
     <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2910,19 +5928,21 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="9"/>
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
-      <c r="D45" s="1"/>
+      <c r="D45" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="9"/>
       <c r="K45" s="9"/>
     </row>
     <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2932,85 +5952,117 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
       <c r="K46" s="9"/>
     </row>
     <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="D47" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>157</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
       <c r="K47" s="9"/>
     </row>
     <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="9"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="D48" s="1" t="str" cm="1">
+        <f t="array" ref="D48:D50">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
+        <v>01 Jan 2023 to 31 Dec 2023</v>
+      </c>
+      <c r="E48" s="88">
+        <v>0.6</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
       <c r="K48" s="9"/>
     </row>
     <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="9"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="D49" s="1" t="str">
+        <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
+      </c>
+      <c r="E49" s="88">
+        <v>0.5</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G49" s="1"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
       <c r="K49" s="9"/>
     </row>
     <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="9"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="D50" s="1" t="str">
+        <v>01 Jan 2025 to 31 Dec 2025</v>
+      </c>
+      <c r="E50" s="88" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="9"/>
     </row>
     <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G51" s="1"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="9"/>
     </row>
     <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="E52" s="88"/>
+      <c r="F52" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
       <c r="K52" s="9"/>
     </row>
-    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="9"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
+      <c r="D53" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="E53" s="20">
+        <f>SUM(E48:E51)</f>
+        <v>1.1000000000000001</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="9"/>
     </row>
     <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3019,9 +6071,9 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="9"/>
     </row>
     <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3030,19 +6082,21 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="9"/>
     </row>
     <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
-      <c r="D56" s="1"/>
+      <c r="D56" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
     </row>
@@ -3052,27 +6106,39 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="9"/>
     </row>
     <row r="58" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="9"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="9"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
+      <c r="D59" s="91" t="s">
+        <v>161</v>
+      </c>
+      <c r="E59" s="89">
+        <f>E42-E53</f>
+        <v>8.9</v>
+      </c>
+      <c r="F59" s="89">
+        <f>F42-E53</f>
+        <v>12.9</v>
+      </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -3092,79 +6158,174 @@
     </row>
     <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
+      <c r="D61" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="H61" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="I61" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="J61" s="21" t="s">
+        <v>143</v>
+      </c>
       <c r="K61" s="9"/>
     </row>
     <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
+      <c r="D62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F62" s="19">
+        <f>'Input - Enterprise'!E22</f>
+        <v>9.5</v>
+      </c>
+      <c r="G62" s="19">
+        <f>F62/(F62+F63)</f>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H62" s="19">
+        <f>($E$42/F62)*G62</f>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="I62" s="19">
+        <f>($F$42/F62)*G62</f>
+        <v>1.1666666666666665</v>
+      </c>
+      <c r="J62" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="K62" s="9"/>
     </row>
     <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="D63" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F63" s="19">
+        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E26</f>
+        <v>2.5</v>
+      </c>
+      <c r="G63" s="19">
+        <f>F63/(F62+F63)</f>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="H63" s="19">
+        <f>($E$42/F63)*G63</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I63" s="19">
+        <f>($F$42/F63)*G63</f>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>147</v>
+      </c>
       <c r="K63" s="9"/>
     </row>
     <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
+      <c r="D64" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F64" s="19">
+        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E27</f>
+        <v>1.5</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="J64" s="9"/>
       <c r="K64" s="9"/>
     </row>
     <row r="65" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="9"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="18"/>
       <c r="K65" s="9"/>
     </row>
     <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
+      <c r="D66" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F66" s="19">
+        <f>'Input - Enterprise'!E23</f>
+        <v>300</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H66" s="19">
+        <f>E59/F66</f>
+        <v>2.9666666666666668E-2</v>
+      </c>
+      <c r="I66" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="J66" s="16" t="s">
+        <v>167</v>
+      </c>
       <c r="K66" s="9"/>
     </row>
     <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="D67" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F67" s="19">
+        <f>'Input - Enterprise'!E24</f>
+        <v>310</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="H67" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="I67" s="19">
+        <f>F59/F67</f>
+        <v>4.161290322580645E-2</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>167</v>
+      </c>
       <c r="K67" s="9"/>
     </row>
     <row r="68" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3173,9 +6334,9 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
       <c r="K68" s="9"/>
     </row>
     <row r="69" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3184,9 +6345,9 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
       <c r="K69" s="9"/>
     </row>
     <row r="70" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3195,9 +6356,9 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
       <c r="K70" s="9"/>
     </row>
     <row r="71" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3206,9 +6367,9 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
       <c r="K71" s="9"/>
     </row>
     <row r="72" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3217,9 +6378,9 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
       <c r="K72" s="9"/>
     </row>
     <row r="73" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3390,6 +6551,5078 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24791D62-75BF-4814-B1FA-242161A163DA}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:AA115"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="34" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="37" customWidth="1"/>
+    <col min="4" max="4" width="60.7109375" style="37" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" style="37" customWidth="1"/>
+    <col min="6" max="11" width="28.7109375" style="37" customWidth="1"/>
+    <col min="12" max="25" width="28.7109375" style="34" customWidth="1"/>
+    <col min="26" max="27" width="9.140625" style="34"/>
+    <col min="28" max="16384" width="9.140625" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" s="34" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="str">
+        <f>HYPERLINK("#'Home'!A1", "Home")</f>
+        <v>Home</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+    </row>
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="str">
+        <f>HYPERLINK("#'Results'!A1", "Results")</f>
+        <v>Results</v>
+      </c>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+    </row>
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N5" s="43"/>
+    </row>
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="45"/>
+    </row>
+    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
+        <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
+        <v>Site</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="57"/>
+    </row>
+    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="str">
+        <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
+        <v>Pasture Beef</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="60"/>
+    </row>
+    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="28"/>
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="str">
+        <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
+        <v>4.2.1.1-2 Methane</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="N11" s="52"/>
+    </row>
+    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="str">
+        <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
+        <v>4.2.1.3-4 Soil direct N2O</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="str">
+        <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
+        <v>4.2.1.5-6 Soil atm. deposition</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="46">
+        <v>307.7</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+    </row>
+    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="str">
+        <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
+        <v>4.2.1.7-8 Soil leach &amp; runoff</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="46">
+        <v>18</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+    </row>
+    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="D15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="46">
+        <v>601</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+    </row>
+    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="46">
+        <v>1326</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+    </row>
+    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="str">
+        <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
+        <v>Constants - Pasture Beef</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="46">
+        <v>7</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="str">
+        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
+        <v>Constants - Livestock</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="27">
+        <f>E15/E16</f>
+        <v>0.45324283559577677</v>
+      </c>
+      <c r="F18" s="28"/>
+    </row>
+    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="str">
+        <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
+        <v>Constants - Common</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="27" t="str">
+        <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E15,Table_SourceData_RainfallZones[Min rainfall],Table_SourceData_RainfallZones[Max rainfall],Table_SourceData_RainfallZones[Rainfall Zone])</f>
+        <v>High rainfall</v>
+      </c>
+      <c r="G19" s="62"/>
+      <c r="N19" s="43"/>
+    </row>
+    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="str">
+        <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
+        <v>Acknowledgements</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="27" t="str">
+        <f>Common_InputFunctions.Utility_GetClimateZone(E14,E15,E17,E13,E18,Table_SourceData_ClimateZones[Min temp],Table_SourceData_ClimateZones[Max temp],Table_SourceData_ClimateZones[Min rainfall],Table_SourceData_ClimateZones[Max rainfall],Table_SourceData_ClimateZones[Min frost days],Table_SourceData_ClimateZones[Max frost days],Table_SourceData_ClimateZones[Min elevation],Table_SourceData_ClimateZones[Max elevation],Table_SourceData_ClimateZones[Min MAP:PET],Table_SourceData_ClimateZones[Max MAP:PET],Table_SourceData_ClimateZones[Climate zone])</f>
+        <v>Warm temperate dry</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="61"/>
+      <c r="N20" s="45"/>
+    </row>
+    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+      <c r="D21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="27" t="str">
+        <f>Common_InputFunctions.Utility_LookupValueInTable($E$20,Table_SourceData_WetDryZones[Climate zone],Table_SourceData_WetDryZones[Wet or Dry Zone])</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="61"/>
+    </row>
+    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="D22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="27" t="str">
+        <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E14,Table_SourceData_TemperatureZones[Min MAT],Table_SourceData_TemperatureZones[Max MAT],Table_SourceData_TemperatureZones[Temperature Zone])</f>
+        <v>Temperate</v>
+      </c>
+      <c r="G22" s="65"/>
+    </row>
+    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25"/>
+      <c r="N25" s="45"/>
+    </row>
+    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+    </row>
+    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+    </row>
+    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+    </row>
+    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+    </row>
+    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="63"/>
+      <c r="P30" s="63"/>
+      <c r="Q30" s="63"/>
+      <c r="R30" s="63"/>
+      <c r="S30" s="63"/>
+      <c r="T30" s="63"/>
+      <c r="U30" s="63"/>
+      <c r="V30" s="63"/>
+      <c r="W30" s="63"/>
+      <c r="X30" s="63"/>
+      <c r="Y30" s="63"/>
+    </row>
+    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64"/>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="64"/>
+      <c r="S31" s="64"/>
+      <c r="T31" s="64"/>
+      <c r="U31" s="64"/>
+      <c r="V31" s="64"/>
+      <c r="W31" s="64"/>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="64"/>
+    </row>
+    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="64"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="64"/>
+      <c r="Q32" s="64"/>
+      <c r="R32" s="64"/>
+      <c r="S32" s="64"/>
+      <c r="T32" s="64"/>
+      <c r="U32" s="64"/>
+      <c r="V32" s="64"/>
+      <c r="W32" s="64"/>
+      <c r="X32" s="64"/>
+      <c r="Y32" s="64"/>
+    </row>
+    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="64"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="64"/>
+      <c r="S33" s="64"/>
+      <c r="T33" s="64"/>
+      <c r="U33" s="64"/>
+      <c r="V33" s="64"/>
+      <c r="W33" s="64"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="64"/>
+    </row>
+    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="64"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="64"/>
+      <c r="T34" s="64"/>
+      <c r="U34" s="64"/>
+      <c r="V34" s="64"/>
+      <c r="W34" s="64"/>
+      <c r="X34" s="64"/>
+      <c r="Y34" s="64"/>
+    </row>
+    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="64"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="64"/>
+      <c r="R35" s="64"/>
+      <c r="S35" s="64"/>
+      <c r="T35" s="64"/>
+      <c r="U35" s="64"/>
+      <c r="V35" s="64"/>
+      <c r="W35" s="64"/>
+      <c r="X35" s="64"/>
+      <c r="Y35" s="64"/>
+    </row>
+    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="66"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="64"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="64"/>
+      <c r="O36" s="64"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="64"/>
+      <c r="R36" s="64"/>
+      <c r="S36" s="64"/>
+      <c r="T36" s="64"/>
+      <c r="U36" s="64"/>
+      <c r="V36" s="64"/>
+      <c r="W36" s="64"/>
+      <c r="X36" s="64"/>
+      <c r="Y36" s="64"/>
+    </row>
+    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="64"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="64"/>
+      <c r="S37" s="64"/>
+      <c r="T37" s="64"/>
+      <c r="U37" s="64"/>
+      <c r="V37" s="64"/>
+      <c r="W37" s="64"/>
+      <c r="X37" s="64"/>
+      <c r="Y37" s="64"/>
+    </row>
+    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
+      <c r="N38" s="64"/>
+      <c r="O38" s="64"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="64"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="64"/>
+      <c r="V38" s="64"/>
+      <c r="W38" s="64"/>
+      <c r="X38" s="64"/>
+      <c r="Y38" s="64"/>
+    </row>
+    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="66"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="64"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="64"/>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="64"/>
+      <c r="S39" s="64"/>
+      <c r="T39" s="64"/>
+      <c r="U39" s="64"/>
+      <c r="V39" s="64"/>
+      <c r="W39" s="64"/>
+      <c r="X39" s="64"/>
+      <c r="Y39" s="64"/>
+    </row>
+    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="73"/>
+      <c r="L40" s="74"/>
+      <c r="M40" s="74"/>
+      <c r="N40" s="74"/>
+      <c r="O40" s="74"/>
+      <c r="P40" s="74"/>
+      <c r="Q40" s="74"/>
+      <c r="R40" s="74"/>
+      <c r="S40" s="74"/>
+      <c r="T40" s="74"/>
+      <c r="U40" s="74"/>
+      <c r="V40" s="74"/>
+      <c r="W40" s="74"/>
+      <c r="X40" s="74"/>
+      <c r="Y40" s="74"/>
+    </row>
+    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+    </row>
+    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+    </row>
+    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+    </row>
+    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="75"/>
+    </row>
+    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="76"/>
+    </row>
+    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="76"/>
+    </row>
+    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="76"/>
+    </row>
+    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D51" s="78"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="79"/>
+      <c r="G51" s="79"/>
+      <c r="H51" s="80"/>
+    </row>
+    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="81"/>
+    </row>
+    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" s="82"/>
+      <c r="F57" s="83"/>
+    </row>
+    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D58" s="1"/>
+      <c r="E58" s="84"/>
+    </row>
+    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D59" s="1"/>
+      <c r="E59" s="84"/>
+    </row>
+    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D60" s="1"/>
+      <c r="E60" s="85"/>
+    </row>
+    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D63" s="82"/>
+    </row>
+    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D64" s="1"/>
+      <c r="E64" s="84"/>
+    </row>
+    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="1"/>
+      <c r="E65" s="84"/>
+    </row>
+    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="1"/>
+      <c r="E66" s="85"/>
+    </row>
+    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D69" s="86"/>
+      <c r="E69" s="86"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="86"/>
+      <c r="H69" s="86"/>
+      <c r="I69" s="86"/>
+    </row>
+    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D70" s="86"/>
+      <c r="E70" s="86"/>
+      <c r="F70" s="86"/>
+      <c r="G70" s="86"/>
+      <c r="H70" s="86"/>
+      <c r="I70" s="86"/>
+    </row>
+    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D71" s="86"/>
+      <c r="E71" s="86"/>
+      <c r="F71" s="86"/>
+      <c r="G71" s="86"/>
+      <c r="H71" s="86"/>
+      <c r="I71" s="86"/>
+    </row>
+    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D72" s="86"/>
+      <c r="E72" s="86"/>
+      <c r="F72" s="86"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="86"/>
+      <c r="I72" s="86"/>
+    </row>
+    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D78" s="87"/>
+    </row>
+    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D79" s="87"/>
+    </row>
+    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D80" s="87"/>
+    </row>
+    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D81" s="87"/>
+    </row>
+    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D82" s="87"/>
+    </row>
+    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
+      <formula1>"YES - In leaching zone, NO - Not in leaching zone"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G36:G39" xr:uid="{FC4F355F-8194-44E7-BAB7-2E788D632391}">
+      <formula1>$D$41:$D$43</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11" xr:uid="{674A5993-80C6-40F8-9C7E-8360EE985D6D}">
+      <formula1>INDIRECT("Table_WASA4Areas[SA 4 Name]")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10" xr:uid="{3E5D42A7-7A09-4510-8DDD-588AA6407F0E}">
+      <formula1>INDIRECT("Table_AustralianStates[Common Name]")</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30171F5-957D-4D10-AA21-0CE17EC217CD}">
+  <dimension ref="C1:J35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="69.28515625" style="1" customWidth="1"/>
+    <col min="5" max="9" width="30.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="C1" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+    </row>
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+    </row>
+    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="44"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D8" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D10" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="51"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D12" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="26">
+        <v>45292</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D13" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="53">
+        <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
+        <v>45657</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="37"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+    </row>
+    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="26">
+        <v>45231</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="26">
+        <v>45747</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="27">
+        <f>DATEDIF(E18,E19+1,"m")</f>
+        <v>17</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="27">
+        <f>SUM(Table_Input_LivestockSales3[Total liveweight sold])*10^-3</f>
+        <v>9.5</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="27">
+        <v>300</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="27">
+        <v>310</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="27">
+        <v>5</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="31">
+        <f>100%-E26-E27</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D31" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D32" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D33" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D34" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="32">
+        <v>45566</v>
+      </c>
+      <c r="F34" s="32">
+        <v>10</v>
+      </c>
+      <c r="G34" s="32">
+        <v>500</v>
+      </c>
+      <c r="H34" s="27">
+        <f>F34*G34</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="35" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D35" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="32">
+        <v>45415</v>
+      </c>
+      <c r="F35" s="32">
+        <v>10</v>
+      </c>
+      <c r="G35" s="32">
+        <v>450</v>
+      </c>
+      <c r="H35" s="27">
+        <f>F35*G35</f>
+        <v>4500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD7772F5-D62F-448B-BE59-D05AA2138B09}">
+  <dimension ref="A1:BY259"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" style="34" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="34" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="20.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="34.28515625" style="1" customWidth="1"/>
+    <col min="11" max="13" width="20.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="36.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.28515625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.140625" style="1" customWidth="1"/>
+    <col min="19" max="20" width="20.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.7109375" style="1" customWidth="1"/>
+    <col min="22" max="33" width="20.7109375" style="34" customWidth="1"/>
+    <col min="34" max="39" width="21.85546875" style="34" customWidth="1"/>
+    <col min="40" max="44" width="20.7109375" style="34" customWidth="1"/>
+    <col min="45" max="65" width="9.140625" style="34"/>
+    <col min="66" max="16384" width="9.140625" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:65" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+    </row>
+    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4"/>
+      <c r="BM4" s="37"/>
+    </row>
+    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5"/>
+      <c r="D5" s="2" t="str" cm="1">
+        <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
+        <v>Australian states and territories</v>
+      </c>
+      <c r="BM5" s="37"/>
+    </row>
+    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6"/>
+      <c r="D6" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+      <c r="D7" s="32" t="str" cm="1">
+        <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>New South Wales</v>
+      </c>
+      <c r="E7" s="32" t="str" cm="1">
+        <f t="array" ref="E7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>New South Wales</v>
+      </c>
+      <c r="F7" s="32" t="str" cm="1">
+        <f t="array" ref="F7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>NSW</v>
+      </c>
+    </row>
+    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="D8" s="32" t="str" cm="1">
+        <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Australian Capital Territory</v>
+      </c>
+      <c r="E8" s="32" t="str" cm="1">
+        <f t="array" ref="E8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>ACT</v>
+      </c>
+      <c r="F8" s="32" t="str" cm="1">
+        <f t="array" ref="F8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>ACT</v>
+      </c>
+    </row>
+    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9"/>
+      <c r="D9" s="32" t="str" cm="1">
+        <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Victoria</v>
+      </c>
+      <c r="E9" s="32" t="str" cm="1">
+        <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Victoria</v>
+      </c>
+      <c r="F9" s="32" t="str" cm="1">
+        <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>VIC</v>
+      </c>
+    </row>
+    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10"/>
+      <c r="D10" s="32" t="str" cm="1">
+        <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Queensland</v>
+      </c>
+      <c r="E10" s="32" t="str" cm="1">
+        <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Queensland</v>
+      </c>
+      <c r="F10" s="32" t="str" cm="1">
+        <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>QLD</v>
+      </c>
+    </row>
+    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11"/>
+      <c r="D11" s="32" t="str" cm="1">
+        <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>South Australia</v>
+      </c>
+      <c r="E11" s="32" t="str" cm="1">
+        <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>South Australia</v>
+      </c>
+      <c r="F11" s="32" t="str" cm="1">
+        <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>SA</v>
+      </c>
+      <c r="BM11" s="37"/>
+    </row>
+    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+      <c r="D12" s="32" t="str" cm="1">
+        <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Western Australia</v>
+      </c>
+      <c r="E12" s="32" t="str" cm="1">
+        <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Western Australia</v>
+      </c>
+      <c r="F12" s="32" t="str" cm="1">
+        <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>WA</v>
+      </c>
+      <c r="BM12" s="37"/>
+    </row>
+    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="D13" s="32" t="str" cm="1">
+        <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Tasmania</v>
+      </c>
+      <c r="E13" s="32" t="str" cm="1">
+        <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Tasmania</v>
+      </c>
+      <c r="F13" s="32" t="str" cm="1">
+        <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>TAS</v>
+      </c>
+    </row>
+    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="D14" s="32" t="str" cm="1">
+        <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Northern Territory</v>
+      </c>
+      <c r="E14" s="32" t="str" cm="1">
+        <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>Northern Territory</v>
+      </c>
+      <c r="F14" s="32" t="str" cm="1">
+        <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
+        <v>NT</v>
+      </c>
+    </row>
+    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+    </row>
+    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+    </row>
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17"/>
+    </row>
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18"/>
+      <c r="D18" s="2" t="str" cm="1">
+        <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
+        <v>ABS Statistcal Areas Level 4 - Western Australia</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19"/>
+      <c r="D19" s="29" t="str" cm="1">
+        <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
+        <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20"/>
+      <c r="D20" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21"/>
+      <c r="D21" s="32" t="str" cm="1">
+        <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Bunbury</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="D22" s="32" t="str" cm="1">
+        <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Mandurah</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="D23" s="32" t="str" cm="1">
+        <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Perth - Inner</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="D24" s="32" t="str" cm="1">
+        <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Perth - North East</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25"/>
+      <c r="D25" s="32" t="str" cm="1">
+        <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Perth - North West</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+      <c r="D26" s="32" t="str" cm="1">
+        <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Perth - South East</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+      <c r="D27" s="32" t="str" cm="1">
+        <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Perth - South West</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+      <c r="D28" s="32" t="str" cm="1">
+        <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Western Australia - Wheat Belt</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+      <c r="D29" s="32" t="str" cm="1">
+        <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Western Australia - Outback (North)</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="D30" s="32" t="str" cm="1">
+        <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
+        <v>Western Australia - Outback (South)</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+    </row>
+    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+    </row>
+    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+    </row>
+    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="D34" s="2" t="str" cm="1">
+        <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
+        <v>Global warming potential for greenhouse gases</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="D35" s="29" t="str" cm="1">
+        <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
+        <v>XXXXXXX</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="D36" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="D37" s="32" t="str" cm="1">
+        <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>CO2</v>
+      </c>
+      <c r="E37" s="32" cm="1">
+        <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="D38" s="32" t="str" cm="1">
+        <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>CH4</v>
+      </c>
+      <c r="E38" s="32" cm="1">
+        <f t="array" ref="E38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="D39" s="32" t="str" cm="1">
+        <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>N2O</v>
+      </c>
+      <c r="E39" s="32" cm="1">
+        <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="D40" s="32" t="str" cm="1">
+        <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>CF4</v>
+      </c>
+      <c r="E40" s="32" cm="1">
+        <f t="array" ref="E40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>6630</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="D41" s="32" t="str" cm="1">
+        <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>C2F6</v>
+      </c>
+      <c r="E41" s="32" cm="1">
+        <f t="array" ref="E41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="32" t="str" cm="1">
+        <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>SF6</v>
+      </c>
+      <c r="E42" s="32" cm="1">
+        <f t="array" ref="E42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43" s="32" t="str" cm="1">
+        <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>NF3</v>
+      </c>
+      <c r="E43" s="32" cm="1">
+        <f t="array" ref="E43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
+        <v>17200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" s="2" t="str" cm="1">
+        <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
+        <v>Factor to convert elemental mass of gas to molecular mass</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D46" s="29" t="str" cm="1">
+        <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
+        <v>XXXXXXX</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="H47" s="32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="32" t="str" cm="1">
+        <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>CO2</v>
+      </c>
+      <c r="E48" s="32" t="str" cm="1">
+        <f t="array" ref="E48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>44/12</v>
+      </c>
+      <c r="F48" s="32" cm="1">
+        <f t="array" ref="F48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>44</v>
+      </c>
+      <c r="G48" s="32" cm="1">
+        <f t="array" ref="G48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>12</v>
+      </c>
+      <c r="H48" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D49" s="32" t="str" cm="1">
+        <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>CH4</v>
+      </c>
+      <c r="E49" s="32" t="str" cm="1">
+        <f t="array" ref="E49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>16/12</v>
+      </c>
+      <c r="F49" s="32" cm="1">
+        <f t="array" ref="F49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>16</v>
+      </c>
+      <c r="G49" s="32" cm="1">
+        <f t="array" ref="G49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>12</v>
+      </c>
+      <c r="H49" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D50" s="32" t="str" cm="1">
+        <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>N2O</v>
+      </c>
+      <c r="E50" s="32" t="str" cm="1">
+        <f t="array" ref="E50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>44/28</v>
+      </c>
+      <c r="F50" s="32" cm="1">
+        <f t="array" ref="F50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>44</v>
+      </c>
+      <c r="G50" s="32" cm="1">
+        <f t="array" ref="G50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>28</v>
+      </c>
+      <c r="H50" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>1.5714285714285714</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D51" s="32" t="str" cm="1">
+        <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>Nox</v>
+      </c>
+      <c r="E51" s="32" t="str" cm="1">
+        <f t="array" ref="E51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>46/14</v>
+      </c>
+      <c r="F51" s="32" cm="1">
+        <f t="array" ref="F51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>46</v>
+      </c>
+      <c r="G51" s="32" cm="1">
+        <f t="array" ref="G51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>14</v>
+      </c>
+      <c r="H51" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>3.2857142857142856</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D52" s="32" t="str" cm="1">
+        <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>CO</v>
+      </c>
+      <c r="E52" s="32" t="str" cm="1">
+        <f t="array" ref="E52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>28/12</v>
+      </c>
+      <c r="F52" s="32" cm="1">
+        <f t="array" ref="F52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>28</v>
+      </c>
+      <c r="G52" s="32" cm="1">
+        <f t="array" ref="G52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>12</v>
+      </c>
+      <c r="H52" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>2.3333333333333335</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D53" s="32" t="str" cm="1">
+        <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>CO2 Lime</v>
+      </c>
+      <c r="E53" s="32" t="str" cm="1">
+        <f t="array" ref="E53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>44/12</v>
+      </c>
+      <c r="F53" s="32" cm="1">
+        <f t="array" ref="F53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>44</v>
+      </c>
+      <c r="G53" s="32" cm="1">
+        <f t="array" ref="G53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>12</v>
+      </c>
+      <c r="H53" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>3.6666666666666665</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="32" t="str" cm="1">
+        <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>NMVOC</v>
+      </c>
+      <c r="E54" s="32" t="str" cm="1">
+        <f t="array" ref="E54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>14/12</v>
+      </c>
+      <c r="F54" s="32" cm="1">
+        <f t="array" ref="F54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>14</v>
+      </c>
+      <c r="G54" s="32" cm="1">
+        <f t="array" ref="G54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
+        <v>12</v>
+      </c>
+      <c r="H54" s="32">
+        <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
+        <v>1.1666666666666667</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" s="2" t="str" cm="1">
+        <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
+        <v>VEERG Australian wet and dry zones</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D58" s="29" t="str" cm="1">
+        <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
+        <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D59" s="38" t="str" cm="1">
+        <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
+        <v>⚠️VARIATION OF SOURCE DATA:</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D60" s="38" t="str">
+        <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D61" s="38" t="str">
+        <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D63" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E63" s="32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D64" s="32" t="str" cm="1">
+        <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical montane</v>
+      </c>
+      <c r="E64" s="32" t="str" cm="1">
+        <f t="array" ref="E64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="32" t="str" cm="1">
+        <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical wet</v>
+      </c>
+      <c r="E65" s="32" t="str" cm="1">
+        <f t="array" ref="E65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="32" t="str" cm="1">
+        <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical moist</v>
+      </c>
+      <c r="E66" s="32" t="str" cm="1">
+        <f t="array" ref="E66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D67" s="32" t="str" cm="1">
+        <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical dry</v>
+      </c>
+      <c r="E67" s="32" t="str" cm="1">
+        <f t="array" ref="E67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+    </row>
+    <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D68" s="32" t="str" cm="1">
+        <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate moist</v>
+      </c>
+      <c r="E68" s="32" t="str" cm="1">
+        <f t="array" ref="E68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D69" s="32" t="str" cm="1">
+        <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate dry</v>
+      </c>
+      <c r="E69" s="32" t="str" cm="1">
+        <f t="array" ref="E69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+    </row>
+    <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D70" s="32" t="str" cm="1">
+        <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Cool temperate moist</v>
+      </c>
+      <c r="E70" s="32" t="str" cm="1">
+        <f t="array" ref="E70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D71" s="32" t="str" cm="1">
+        <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Cool temperate dry</v>
+      </c>
+      <c r="E71" s="32" t="str" cm="1">
+        <f t="array" ref="E71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+    </row>
+    <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D72" s="32" t="str" cm="1">
+        <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate moist - low frost</v>
+      </c>
+      <c r="E72" s="32" t="str" cm="1">
+        <f t="array" ref="E72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D73" s="32" t="str" cm="1">
+        <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate dry - low frost</v>
+      </c>
+      <c r="E73" s="32" t="str" cm="1">
+        <f t="array" ref="E73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+    </row>
+    <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D74" s="32" t="str" cm="1">
+        <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate moist - high temp</v>
+      </c>
+      <c r="E74" s="32" t="str" cm="1">
+        <f t="array" ref="E74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D75" s="32" t="str" cm="1">
+        <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate dry - high temp</v>
+      </c>
+      <c r="E75" s="32" t="str" cm="1">
+        <f t="array" ref="E75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+    </row>
+    <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D76" s="32" t="str" cm="1">
+        <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Cool temperate moist - low frost</v>
+      </c>
+      <c r="E76" s="32" t="str" cm="1">
+        <f t="array" ref="E76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+    </row>
+    <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D77" s="32" t="str" cm="1">
+        <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Cool temperate dry - low frost</v>
+      </c>
+      <c r="E77" s="32" t="str" cm="1">
+        <f t="array" ref="E77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+    </row>
+    <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D81" s="2" t="str" cm="1">
+        <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
+        <v>VEERG Australian climate zones</v>
+      </c>
+    </row>
+    <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D82" s="29" t="str" cm="1">
+        <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
+        <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
+      </c>
+    </row>
+    <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D83" s="38" t="str" cm="1">
+        <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
+        <v>⚠️VARIATION OF SOURCE DATA:</v>
+      </c>
+    </row>
+    <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D84" s="38" t="str">
+        <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
+      </c>
+    </row>
+    <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D85" s="38" t="str">
+        <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
+      </c>
+    </row>
+    <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D86" s="38" t="str">
+        <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
+      </c>
+    </row>
+    <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D87" s="38" t="str">
+        <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
+      </c>
+    </row>
+    <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D89" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="G89" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H89" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="I89" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="J89" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K89" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L89" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="M89" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="N89" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="O89" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="P89" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q89" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="R89" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="S89" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="T89" s="32"/>
+    </row>
+    <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D90" s="32" t="str" cm="1">
+        <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical montane</v>
+      </c>
+      <c r="E90" s="32" t="str" cm="1">
+        <f t="array" ref="E90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 18 C</v>
+      </c>
+      <c r="F90" s="32" t="str" cm="1">
+        <f t="array" ref="F90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="G90" s="32" t="str" cm="1">
+        <f t="array" ref="G90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 7</v>
+      </c>
+      <c r="H90" s="32" t="str" cm="1">
+        <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 1000 m</v>
+      </c>
+      <c r="I90" s="32" t="str" cm="1">
+        <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="J90" s="32" cm="1">
+        <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>18.001000000000001</v>
+      </c>
+      <c r="K90" s="32" cm="1">
+        <f t="array" ref="K90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="L90" s="32" cm="1">
+        <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="M90" s="32" cm="1">
+        <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="N90" s="32" cm="1">
+        <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O90" s="32" cm="1">
+        <f t="array" ref="O90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>7</v>
+      </c>
+      <c r="P90" s="32" cm="1">
+        <f t="array" ref="P90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1000</v>
+      </c>
+      <c r="Q90" s="32" cm="1">
+        <f t="array" ref="Q90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="R90" s="32" cm="1">
+        <f t="array" ref="R90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="S90" s="32" cm="1">
+        <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="T90" s="32"/>
+    </row>
+    <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D91" s="32" t="str" cm="1">
+        <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical wet</v>
+      </c>
+      <c r="E91" s="32" t="str" cm="1">
+        <f t="array" ref="E91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 18 C</v>
+      </c>
+      <c r="F91" s="32" t="str" cm="1">
+        <f t="array" ref="F91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 2000 mm</v>
+      </c>
+      <c r="G91" s="32" t="str" cm="1">
+        <f t="array" ref="G91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 7</v>
+      </c>
+      <c r="H91" s="32" t="str" cm="1">
+        <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 1000 m</v>
+      </c>
+      <c r="I91" s="32" t="str" cm="1">
+        <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="J91" s="32" cm="1">
+        <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>18.001000000000001</v>
+      </c>
+      <c r="K91" s="32" cm="1">
+        <f t="array" ref="K91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="L91" s="32" cm="1">
+        <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>2000.001</v>
+      </c>
+      <c r="M91" s="32" cm="1">
+        <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="N91" s="32" cm="1">
+        <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O91" s="32" cm="1">
+        <f t="array" ref="O91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>7</v>
+      </c>
+      <c r="P91" s="32" cm="1">
+        <f t="array" ref="P91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q91" s="32" cm="1">
+        <f t="array" ref="Q91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999.99900000000002</v>
+      </c>
+      <c r="R91" s="32" cm="1">
+        <f t="array" ref="R91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="S91" s="32" cm="1">
+        <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="T91" s="32"/>
+    </row>
+    <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D92" s="32" t="str" cm="1">
+        <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical moist</v>
+      </c>
+      <c r="E92" s="32" t="str" cm="1">
+        <f t="array" ref="E92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 18 C</v>
+      </c>
+      <c r="F92" s="32" t="str" cm="1">
+        <f t="array" ref="F92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 1000 mm - ≤ 2000 mm</v>
+      </c>
+      <c r="G92" s="32" t="str" cm="1">
+        <f t="array" ref="G92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 7</v>
+      </c>
+      <c r="H92" s="32" t="str" cm="1">
+        <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 1000 m</v>
+      </c>
+      <c r="I92" s="32" t="str" cm="1">
+        <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="J92" s="32" cm="1">
+        <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>18.001000000000001</v>
+      </c>
+      <c r="K92" s="32" cm="1">
+        <f t="array" ref="K92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="L92" s="32" cm="1">
+        <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1000.001</v>
+      </c>
+      <c r="M92" s="32" cm="1">
+        <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>2000</v>
+      </c>
+      <c r="N92" s="32" cm="1">
+        <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O92" s="32" cm="1">
+        <f t="array" ref="O92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>7</v>
+      </c>
+      <c r="P92" s="32" cm="1">
+        <f t="array" ref="P92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q92" s="32" cm="1">
+        <f t="array" ref="Q92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999.99900000000002</v>
+      </c>
+      <c r="R92" s="32" cm="1">
+        <f t="array" ref="R92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="S92" s="32" cm="1">
+        <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="T92" s="32"/>
+    </row>
+    <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D93" s="32" t="str" cm="1">
+        <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Tropical dry</v>
+      </c>
+      <c r="E93" s="32" t="str" cm="1">
+        <f t="array" ref="E93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 18 C</v>
+      </c>
+      <c r="F93" s="32" t="str" cm="1">
+        <f t="array" ref="F93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 1000 mm</v>
+      </c>
+      <c r="G93" s="32" t="str" cm="1">
+        <f t="array" ref="G93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 7</v>
+      </c>
+      <c r="H93" s="32" t="str" cm="1">
+        <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 1000 m</v>
+      </c>
+      <c r="I93" s="32" t="str" cm="1">
+        <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="J93" s="32" cm="1">
+        <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>18.001000000000001</v>
+      </c>
+      <c r="K93" s="32" cm="1">
+        <f t="array" ref="K93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="L93" s="32" cm="1">
+        <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="M93" s="32" cm="1">
+        <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1000</v>
+      </c>
+      <c r="N93" s="32" cm="1">
+        <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O93" s="32" cm="1">
+        <f t="array" ref="O93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>7</v>
+      </c>
+      <c r="P93" s="32" cm="1">
+        <f t="array" ref="P93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q93" s="32" cm="1">
+        <f t="array" ref="Q93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999.99900000000002</v>
+      </c>
+      <c r="R93" s="32" cm="1">
+        <f t="array" ref="R93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="S93" s="32" cm="1">
+        <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="T93" s="32"/>
+    </row>
+    <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D94" s="32" t="str" cm="1">
+        <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate moist</v>
+      </c>
+      <c r="E94" s="32" t="str" cm="1">
+        <f t="array" ref="E94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 10 C</v>
+      </c>
+      <c r="F94" s="32" t="str" cm="1">
+        <f t="array" ref="F94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="G94" s="32" t="str" cm="1">
+        <f t="array" ref="G94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H94" s="32" t="str" cm="1">
+        <f t="array" ref="H94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="I94" s="32" t="str" cm="1">
+        <f t="array" ref="I94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 1</v>
+      </c>
+      <c r="J94" s="32" cm="1">
+        <f t="array" ref="J94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>10.000999999999999</v>
+      </c>
+      <c r="K94" s="32" cm="1">
+        <f t="array" ref="K94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="L94" s="32" cm="1">
+        <f t="array" ref="L94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="M94" s="32" cm="1">
+        <f t="array" ref="M94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="N94" s="32" cm="1">
+        <f t="array" ref="N94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O94" s="32" cm="1">
+        <f t="array" ref="O94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="P94" s="32" cm="1">
+        <f t="array" ref="P94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q94" s="32" cm="1">
+        <f t="array" ref="Q94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="R94" s="32" cm="1">
+        <f t="array" ref="R94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="S94" s="32" cm="1">
+        <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="T94" s="32"/>
+    </row>
+    <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D95" s="32" t="str" cm="1">
+        <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Warm temperate dry</v>
+      </c>
+      <c r="E95" s="32" t="str" cm="1">
+        <f t="array" ref="E95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 10 C</v>
+      </c>
+      <c r="F95" s="32" t="str" cm="1">
+        <f t="array" ref="F95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="G95" s="32" t="str" cm="1">
+        <f t="array" ref="G95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H95" s="32" t="str" cm="1">
+        <f t="array" ref="H95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="I95" s="32" t="str" cm="1">
+        <f t="array" ref="I95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 1</v>
+      </c>
+      <c r="J95" s="32" cm="1">
+        <f t="array" ref="J95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>10.000999999999999</v>
+      </c>
+      <c r="K95" s="32" cm="1">
+        <f t="array" ref="K95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="L95" s="32" cm="1">
+        <f t="array" ref="L95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="M95" s="32" cm="1">
+        <f t="array" ref="M95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="N95" s="32" cm="1">
+        <f t="array" ref="N95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O95" s="32" cm="1">
+        <f t="array" ref="O95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="P95" s="32" cm="1">
+        <f t="array" ref="P95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q95" s="32" cm="1">
+        <f t="array" ref="Q95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="R95" s="32" cm="1">
+        <f t="array" ref="R95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="S95" s="32" cm="1">
+        <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="T95" s="32"/>
+    </row>
+    <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D96" s="32" t="str" cm="1">
+        <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Cool temperate moist</v>
+      </c>
+      <c r="E96" s="32" t="str" cm="1">
+        <f t="array" ref="E96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 0 C - ≤ 10 C</v>
+      </c>
+      <c r="F96" s="32" t="str" cm="1">
+        <f t="array" ref="F96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="G96" s="32" t="str" cm="1">
+        <f t="array" ref="G96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H96" s="32" t="str" cm="1">
+        <f t="array" ref="H96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="I96" s="32" t="str" cm="1">
+        <f t="array" ref="I96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 1</v>
+      </c>
+      <c r="J96" s="32" cm="1">
+        <f t="array" ref="J96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="K96" s="32" cm="1">
+        <f t="array" ref="K96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>10</v>
+      </c>
+      <c r="L96" s="32" cm="1">
+        <f t="array" ref="L96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="M96" s="32" cm="1">
+        <f t="array" ref="M96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="N96" s="32" cm="1">
+        <f t="array" ref="N96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O96" s="32" cm="1">
+        <f t="array" ref="O96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="P96" s="32" cm="1">
+        <f t="array" ref="P96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q96" s="32" cm="1">
+        <f t="array" ref="Q96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="R96" s="32" cm="1">
+        <f t="array" ref="R96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="S96" s="32" cm="1">
+        <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="T96" s="32"/>
+    </row>
+    <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D97" s="32" t="str" cm="1">
+        <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Cool temperate dry</v>
+      </c>
+      <c r="E97" s="32" t="str" cm="1">
+        <f t="array" ref="E97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>&gt; 0 C - ≤ 10 C</v>
+      </c>
+      <c r="F97" s="32" t="str" cm="1">
+        <f t="array" ref="F97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="G97" s="32" t="str" cm="1">
+        <f t="array" ref="G97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H97" s="32" t="str" cm="1">
+        <f t="array" ref="H97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="I97" s="32" t="str" cm="1">
+        <f t="array" ref="I97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>≤ 1</v>
+      </c>
+      <c r="J97" s="32" cm="1">
+        <f t="array" ref="J97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="K97" s="32" cm="1">
+        <f t="array" ref="K97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>10</v>
+      </c>
+      <c r="L97" s="32" cm="1">
+        <f t="array" ref="L97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="M97" s="32" cm="1">
+        <f t="array" ref="M97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="N97" s="32" cm="1">
+        <f t="array" ref="N97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="O97" s="32" cm="1">
+        <f t="array" ref="O97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="P97" s="32" cm="1">
+        <f t="array" ref="P97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="Q97" s="32" cm="1">
+        <f t="array" ref="Q97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>999999</v>
+      </c>
+      <c r="R97" s="32" cm="1">
+        <f t="array" ref="R97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="S97" s="32" cm="1">
+        <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="T97" s="32"/>
+    </row>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="16" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+        <v>Note:</v>
+      </c>
+    </row>
+    <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D100" s="16" t="str">
+        <v>MAT = mean annual temperature</v>
+      </c>
+    </row>
+    <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D101" s="16" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="16" t="str">
+        <v>PET = potential evapotranspiration</v>
+      </c>
+    </row>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="16"/>
+    </row>
+    <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D105" s="2" t="str" cm="1">
+        <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
+        <v>VEERG Australian temperature zones</v>
+      </c>
+    </row>
+    <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D106" s="29" t="str" cm="1">
+        <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
+        <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
+      </c>
+    </row>
+    <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D107" s="38" t="str" cm="1">
+        <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
+        <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
+      </c>
+    </row>
+    <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D109" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E109" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="G109" s="32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D110" s="32" t="str" cm="1">
+        <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E110" s="32" t="str" cm="1">
+        <f t="array" ref="E110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>≥ 26 C</v>
+      </c>
+      <c r="F110" s="32" cm="1">
+        <f t="array" ref="F110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>26</v>
+      </c>
+      <c r="G110" s="32" cm="1">
+        <f t="array" ref="G110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D111" s="32" t="str" cm="1">
+        <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E111" s="32" t="str" cm="1">
+        <f t="array" ref="E111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>15 - 25 C</v>
+      </c>
+      <c r="F111" s="32" cm="1">
+        <f t="array" ref="F111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>15</v>
+      </c>
+      <c r="G111" s="32" cm="1">
+        <f t="array" ref="G111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>25.998999999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D112" s="32" t="str" cm="1">
+        <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E112" s="32" t="str" cm="1">
+        <f t="array" ref="E112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>≤ 14 C</v>
+      </c>
+      <c r="F112" s="32" cm="1">
+        <f t="array" ref="F112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="G112" s="32" cm="1">
+        <f t="array" ref="G112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
+        <v>14.999000000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D115" s="2" t="str" cm="1">
+        <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
+        <v>VEERG Australian rainfall zones</v>
+      </c>
+      <c r="BN115" s="34"/>
+    </row>
+    <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D116" s="29" t="str" cm="1">
+        <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
+        <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
+      </c>
+      <c r="BN116" s="34"/>
+    </row>
+    <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D117" s="38" t="str" cm="1">
+        <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
+        <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
+      </c>
+      <c r="BN117" s="34"/>
+    </row>
+    <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN118" s="34"/>
+    </row>
+    <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D119" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E119" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="F119" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G119" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN119" s="34"/>
+    </row>
+    <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D120" s="32" t="str" cm="1">
+        <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>High rainfall</v>
+      </c>
+      <c r="E120" s="32" t="str" cm="1">
+        <f t="array" ref="E120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>Annual rainfall &gt; 600mm</v>
+      </c>
+      <c r="F120" s="32" cm="1">
+        <f t="array" ref="F120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>600.00099999999998</v>
+      </c>
+      <c r="G120" s="32" cm="1">
+        <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>999999</v>
+      </c>
+      <c r="BN120" s="34"/>
+    </row>
+    <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D121" s="32" t="str" cm="1">
+        <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>Low rainfall</v>
+      </c>
+      <c r="E121" s="32" t="str" cm="1">
+        <f t="array" ref="E121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>Annual rainfall ≤ 600mm</v>
+      </c>
+      <c r="F121" s="32" cm="1">
+        <f t="array" ref="F121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>-999999</v>
+      </c>
+      <c r="G121" s="32" cm="1">
+        <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
+        <v>600</v>
+      </c>
+      <c r="BN121" s="34"/>
+    </row>
+    <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN122" s="34"/>
+    </row>
+    <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D124" s="2" t="str" cm="1">
+        <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
+        <v>VEERG Australian leaching zones</v>
+      </c>
+    </row>
+    <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D125" s="29" t="str" cm="1">
+        <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
+        <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
+      </c>
+    </row>
+    <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D127" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E127" s="32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D128" s="32" t="str" cm="1">
+        <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v>Leaching occurs</v>
+      </c>
+      <c r="E128" s="32" t="str" cm="1">
+        <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
+      </c>
+    </row>
+    <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D129" s="32" t="str" cm="1">
+        <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v>Leaching does not occur</v>
+      </c>
+      <c r="E129" s="32" t="str" cm="1">
+        <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
+        <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
+      </c>
+    </row>
+    <row r="130" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="2" t="str" cm="1">
+        <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
+        <v>Fraction of N that is available for leaching and runoff</v>
+      </c>
+      <c r="E132" s="9"/>
+    </row>
+    <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D133" s="29" t="str" cm="1">
+        <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
+        <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
+      </c>
+      <c r="E133" s="9"/>
+    </row>
+    <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>77</v>
+      </c>
+      <c r="E134" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D135" t="str" cm="1">
+        <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v>Yes - in leaching zone</v>
+      </c>
+      <c r="E135" cm="1">
+        <f t="array" ref="E135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D136" s="1" t="str" cm="1">
+        <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v>No - not in leaching zone</v>
+      </c>
+      <c r="E136" s="32" cm="1">
+        <f t="array" ref="E136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN138" s="34"/>
+      <c r="BO138" s="34"/>
+      <c r="BP138" s="34"/>
+      <c r="BQ138" s="34"/>
+      <c r="BR138" s="34"/>
+      <c r="BS138" s="34"/>
+      <c r="BT138" s="34"/>
+      <c r="BU138" s="34"/>
+      <c r="BV138" s="34"/>
+      <c r="BW138" s="34"/>
+      <c r="BX138" s="34"/>
+      <c r="BY138" s="34"/>
+    </row>
+    <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D139" s="2" t="str" cm="1">
+        <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
+        <v>FracWET for irrigation types</v>
+      </c>
+      <c r="BN139" s="34"/>
+      <c r="BO139" s="34"/>
+      <c r="BP139" s="34"/>
+      <c r="BQ139" s="34"/>
+      <c r="BR139" s="34"/>
+      <c r="BS139" s="34"/>
+      <c r="BT139" s="34"/>
+      <c r="BU139" s="34"/>
+      <c r="BV139" s="34"/>
+      <c r="BW139" s="34"/>
+      <c r="BX139" s="34"/>
+      <c r="BY139" s="34"/>
+    </row>
+    <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D140" s="29" t="str" cm="1">
+        <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
+        <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
+      </c>
+      <c r="BN140" s="34"/>
+      <c r="BO140" s="34"/>
+      <c r="BP140" s="34"/>
+      <c r="BQ140" s="34"/>
+      <c r="BR140" s="34"/>
+      <c r="BS140" s="34"/>
+      <c r="BT140" s="34"/>
+      <c r="BU140" s="34"/>
+      <c r="BV140" s="34"/>
+      <c r="BW140" s="34"/>
+      <c r="BX140" s="34"/>
+      <c r="BY140" s="34"/>
+    </row>
+    <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D141" s="38" t="str" cm="1">
+        <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
+        <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
+      </c>
+      <c r="BN141" s="34"/>
+    </row>
+    <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D142" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E142" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="BN142" s="34"/>
+    </row>
+    <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D143" s="32" t="str" cm="1">
+        <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="E143" s="32" cm="1">
+        <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>0</v>
+      </c>
+      <c r="BN143" s="34"/>
+    </row>
+    <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D144" s="1" t="str" cm="1">
+        <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Drip irrigation</v>
+      </c>
+      <c r="E144" s="32" cm="1">
+        <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>0</v>
+      </c>
+      <c r="BN144" s="34"/>
+    </row>
+    <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D145" s="1" t="str" cm="1">
+        <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Sprinkler irrigation</v>
+      </c>
+      <c r="E145" s="32" cm="1">
+        <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="BN145" s="34"/>
+    </row>
+    <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D146" s="1" t="str" cm="1">
+        <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Surface irrigation</v>
+      </c>
+      <c r="E146" s="32" cm="1">
+        <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="BN146" s="34"/>
+    </row>
+    <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D147" s="1" t="str" cm="1">
+        <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>Other irrigation</v>
+      </c>
+      <c r="E147" s="32" cm="1">
+        <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="BN147" s="34"/>
+    </row>
+    <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN148" s="34"/>
+    </row>
+    <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN149" s="34"/>
+    </row>
+    <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D150" s="2" t="str" cm="1">
+        <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
+        <v>Australian data scores for scope 3</v>
+      </c>
+      <c r="BN150" s="34"/>
+    </row>
+    <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D151" s="29" t="str" cm="1">
+        <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
+        <v>VEERG 2026: XXXXXXXX</v>
+      </c>
+      <c r="BN151" s="34"/>
+    </row>
+    <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN152" s="34"/>
+    </row>
+    <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D153" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E153" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="BC153" s="37"/>
+      <c r="BD153" s="37"/>
+      <c r="BE153" s="37"/>
+      <c r="BF153" s="37"/>
+      <c r="BG153" s="37"/>
+      <c r="BH153" s="37"/>
+      <c r="BI153" s="37"/>
+      <c r="BJ153" s="37"/>
+      <c r="BK153" s="37"/>
+      <c r="BL153" s="37"/>
+      <c r="BM153" s="37"/>
+    </row>
+    <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D154" s="32" t="str" cm="1">
+        <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>International scope 3 database</v>
+      </c>
+      <c r="E154" s="32" cm="1">
+        <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC154" s="37"/>
+      <c r="BD154" s="37"/>
+      <c r="BE154" s="37"/>
+      <c r="BF154" s="37"/>
+      <c r="BG154" s="37"/>
+      <c r="BH154" s="37"/>
+      <c r="BI154" s="37"/>
+      <c r="BJ154" s="37"/>
+      <c r="BK154" s="37"/>
+      <c r="BL154" s="37"/>
+      <c r="BM154" s="37"/>
+    </row>
+    <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D155" s="32" t="str" cm="1">
+        <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>Australian scope 3 database</v>
+      </c>
+      <c r="E155" s="32" cm="1">
+        <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>2</v>
+      </c>
+      <c r="BC155" s="37"/>
+      <c r="BD155" s="37"/>
+      <c r="BE155" s="37"/>
+      <c r="BF155" s="37"/>
+      <c r="BG155" s="37"/>
+      <c r="BH155" s="37"/>
+      <c r="BI155" s="37"/>
+      <c r="BJ155" s="37"/>
+      <c r="BK155" s="37"/>
+      <c r="BL155" s="37"/>
+      <c r="BM155" s="37"/>
+    </row>
+    <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D156" s="32" t="str" cm="1">
+        <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>State or regional scope 3 database</v>
+      </c>
+      <c r="E156" s="32" cm="1">
+        <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D157" s="32" t="str" cm="1">
+        <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>Emissions intensity calculated from approved method</v>
+      </c>
+      <c r="E157" s="32" cm="1">
+        <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D158" s="32" t="str" cm="1">
+        <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>Verified credential matching ISO14067</v>
+      </c>
+      <c r="E158" s="32" cm="1">
+        <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D161" s="2" t="str" cm="1">
+        <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
+        <v>Fraction of N that is available for leaching and runoff</v>
+      </c>
+      <c r="E161" s="9"/>
+    </row>
+    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D162" s="29" t="str" cm="1">
+        <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
+        <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
+      </c>
+      <c r="E162" s="9"/>
+    </row>
+    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D163" s="29" t="str" cm="1">
+        <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
+        <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
+      </c>
+      <c r="E163" s="9"/>
+    </row>
+    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D164" s="9" t="str" cm="1">
+        <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
+        <v>FracLEACH</v>
+      </c>
+      <c r="E164" s="9">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN165" s="34"/>
+      <c r="BO165" s="34"/>
+      <c r="BP165" s="34"/>
+    </row>
+    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN166" s="34"/>
+      <c r="BO166" s="34"/>
+      <c r="BP166" s="34"/>
+    </row>
+    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D167" s="2" t="str" cm="1">
+        <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
+        <v>Emission factor for nitrogen leaching and runoff</v>
+      </c>
+      <c r="BN167" s="34"/>
+      <c r="BO167" s="34"/>
+      <c r="BP167" s="34"/>
+    </row>
+    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D168" s="29" t="str" cm="1">
+        <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
+        <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
+      </c>
+      <c r="BN168" s="34"/>
+      <c r="BO168" s="34"/>
+      <c r="BP168" s="34"/>
+    </row>
+    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D169" s="29" t="str" cm="1">
+        <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
+        <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
+      </c>
+      <c r="BN169" s="34"/>
+      <c r="BO169" s="34"/>
+      <c r="BP169" s="34"/>
+    </row>
+    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D170" s="1" t="str" cm="1">
+        <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
+        <v>EFleach</v>
+      </c>
+      <c r="E170" s="1">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="BN170" s="34"/>
+      <c r="BO170" s="34"/>
+      <c r="BP170" s="34"/>
+    </row>
+    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN171" s="34"/>
+      <c r="BO171" s="34"/>
+      <c r="BP171" s="34"/>
+    </row>
+    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN172" s="34"/>
+      <c r="BO172" s="34"/>
+      <c r="BP172" s="34"/>
+    </row>
+    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D173" s="2" t="str" cm="1">
+        <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
+        <v>p = density of methane</v>
+      </c>
+      <c r="BN173" s="34"/>
+      <c r="BO173" s="34"/>
+      <c r="BP173" s="34"/>
+    </row>
+    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D174" s="29" t="str" cm="1">
+        <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
+        <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
+      </c>
+      <c r="BN174" s="34"/>
+      <c r="BO174" s="34"/>
+      <c r="BP174" s="34"/>
+    </row>
+    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D175" s="1" cm="1">
+        <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
+        <v>0.6784</v>
+      </c>
+      <c r="E175" s="16" t="str" cm="1">
+        <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
+        <v>kg/m3</v>
+      </c>
+      <c r="BN175" s="34"/>
+      <c r="BO175" s="34"/>
+      <c r="BP175" s="34"/>
+    </row>
+    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN176" s="34"/>
+      <c r="BO176" s="34"/>
+      <c r="BP176" s="34"/>
+    </row>
+    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN177" s="34"/>
+      <c r="BO177" s="34"/>
+      <c r="BP177" s="34"/>
+    </row>
+    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D178" s="2" t="str" cm="1">
+        <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
+        <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
+      </c>
+      <c r="BN178" s="34"/>
+      <c r="BO178" s="34"/>
+      <c r="BP178" s="34"/>
+    </row>
+    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D179" s="29" t="str" cm="1">
+        <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
+        <v>VEERG 2026: Table A.2.2.1</v>
+      </c>
+      <c r="BN179" s="34"/>
+      <c r="BO179" s="34"/>
+      <c r="BP179" s="34"/>
+    </row>
+    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D180" s="16" t="str" cm="1">
+        <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
+        <v>(kg N2O-N / kg N</v>
+      </c>
+    </row>
+    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D181" s="38" t="str" cm="1">
+        <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
+        <v>VARIATION OF SOURCE DATA:</v>
+      </c>
+    </row>
+    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D182" s="38" t="str">
+        <v>Removed duplicate 'Aquaculture' row.</v>
+      </c>
+    </row>
+    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D183" s="38" t="str">
+        <v>Removed asterisks to aid lookup.</v>
+      </c>
+    </row>
+    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D184" s="38" t="str">
+        <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
+      </c>
+    </row>
+    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D185" s="38" t="str">
+        <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
+      </c>
+    </row>
+    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D186" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="E186" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="F186" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="G186" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H186" s="32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D187" s="32" t="str" cm="1">
+        <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Irrigated pasture</v>
+      </c>
+      <c r="E187" s="32" cm="1">
+        <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="F187" s="32" t="str" cm="1">
+        <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Pasture</v>
+      </c>
+      <c r="G187" s="32" t="str" cm="1">
+        <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H187" s="32" t="str" cm="1">
+        <f t="array" ref="H187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D188" s="32" t="str" cm="1">
+        <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Irrigated crop</v>
+      </c>
+      <c r="E188" s="32" cm="1">
+        <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F188" s="32" t="str" cm="1">
+        <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Crop</v>
+      </c>
+      <c r="G188" s="32" t="str" cm="1">
+        <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H188" s="32" t="str" cm="1">
+        <f t="array" ref="H188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D189" s="32" t="str" cm="1">
+        <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated pasture</v>
+      </c>
+      <c r="E189" s="32" cm="1">
+        <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="F189" s="32" t="str" cm="1">
+        <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Pasture</v>
+      </c>
+      <c r="G189" s="32" t="str" cm="1">
+        <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H189" s="32" t="str" cm="1">
+        <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Low rainfall</v>
+      </c>
+    </row>
+    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D190" s="32" t="str" cm="1">
+        <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated pasture</v>
+      </c>
+      <c r="E190" s="32" cm="1">
+        <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="F190" s="32" t="str" cm="1">
+        <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Pasture</v>
+      </c>
+      <c r="G190" s="32" t="str" cm="1">
+        <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H190" s="32" t="str" cm="1">
+        <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>High rainfall</v>
+      </c>
+    </row>
+    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D191" s="32" t="str" cm="1">
+        <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated crop (low rainfall)</v>
+      </c>
+      <c r="E191" s="32" cm="1">
+        <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="F191" s="32" t="str" cm="1">
+        <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Crop</v>
+      </c>
+      <c r="G191" s="32" t="str" cm="1">
+        <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H191" s="32" t="str" cm="1">
+        <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Low rainfall</v>
+      </c>
+    </row>
+    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D192" s="32" t="str" cm="1">
+        <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Non-irrigated crop (high rainfall)</v>
+      </c>
+      <c r="E192" s="32" cm="1">
+        <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F192" s="32" t="str" cm="1">
+        <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Crop</v>
+      </c>
+      <c r="G192" s="32" t="str" cm="1">
+        <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Not irrigated</v>
+      </c>
+      <c r="H192" s="32" t="str" cm="1">
+        <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>High rainfall</v>
+      </c>
+    </row>
+    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D193" s="32" t="str" cm="1">
+        <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Sugar</v>
+      </c>
+      <c r="E193" s="32" cm="1">
+        <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="F193" s="32" t="str" cm="1">
+        <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Sugar</v>
+      </c>
+      <c r="G193" s="32" t="str" cm="1">
+        <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H193" s="32" t="str" cm="1">
+        <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D194" s="32" t="str" cm="1">
+        <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Cotton</v>
+      </c>
+      <c r="E194" s="32" cm="1">
+        <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>5.3E-3</v>
+      </c>
+      <c r="F194" s="32" t="str" cm="1">
+        <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Cotton</v>
+      </c>
+      <c r="G194" s="32" t="str" cm="1">
+        <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H194" s="32" t="str" cm="1">
+        <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D195" s="32" t="str" cm="1">
+        <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Horticultural crops</v>
+      </c>
+      <c r="E195" s="32" cm="1">
+        <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="F195" s="32" t="str" cm="1">
+        <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Horticultural crops</v>
+      </c>
+      <c r="G195" s="32" t="str" cm="1">
+        <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H195" s="32" t="str" cm="1">
+        <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D196" s="32" t="str" cm="1">
+        <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice (continuous flooding)</v>
+      </c>
+      <c r="E196" s="32" cm="1">
+        <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F196" s="32" t="str" cm="1">
+        <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice</v>
+      </c>
+      <c r="G196" s="32" t="str" cm="1">
+        <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Continuous flooding</v>
+      </c>
+      <c r="H196" s="32" t="str" cm="1">
+        <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D197" s="32" t="str" cm="1">
+        <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
+      </c>
+      <c r="E197" s="32" cm="1">
+        <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F197" s="32" t="str" cm="1">
+        <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Rice</v>
+      </c>
+      <c r="G197" s="32" t="str" cm="1">
+        <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Single and multiple drainage, or alternate wetting and drying</v>
+      </c>
+      <c r="H197" s="32" t="str" cm="1">
+        <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D198" s="32" t="str" cm="1">
+        <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Aquaculture</v>
+      </c>
+      <c r="E198" s="32" cm="1">
+        <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F198" s="32" t="str" cm="1">
+        <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Aquaculture</v>
+      </c>
+      <c r="G198" s="32" t="str" cm="1">
+        <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H198" s="32" t="str" cm="1">
+        <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D199" s="32" t="str" cm="1">
+        <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Forestry</v>
+      </c>
+      <c r="E199" s="32" cm="1">
+        <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>1.8E-3</v>
+      </c>
+      <c r="F199" s="32" t="str" cm="1">
+        <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Forestry</v>
+      </c>
+      <c r="G199" s="32" t="str" cm="1">
+        <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+      <c r="H199" s="32" t="str" cm="1">
+        <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
+        <v>Any</v>
+      </c>
+    </row>
+    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D202" s="2" t="str" cm="1">
+        <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
+        <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
+      </c>
+    </row>
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D203" s="29" t="str" cm="1">
+        <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
+        <v>VEERG 2026: Table A.2.2.2</v>
+      </c>
+    </row>
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D204" s="38" t="str" cm="1">
+        <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
+        <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
+      </c>
+    </row>
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D205" s="16" t="str" cm="1">
+        <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D206" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E206" s="32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D207" s="32" t="str" cm="1">
+        <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E207" s="32" cm="1">
+        <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D208" s="1" t="str" cm="1">
+        <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E208" s="32" cm="1">
+        <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D211" s="1" t="str" cm="1">
+        <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
+        <v>Months to Seasons Mapping</v>
+      </c>
+    </row>
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D212" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="E212" s="32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D213" s="32" t="str" cm="1">
+        <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>January</v>
+      </c>
+      <c r="E213" s="32" t="str" cm="1">
+        <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Summer</v>
+      </c>
+    </row>
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D214" s="1" t="str" cm="1">
+        <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>February</v>
+      </c>
+      <c r="E214" s="32" t="str" cm="1">
+        <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Summer</v>
+      </c>
+    </row>
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D215" s="1" t="str" cm="1">
+        <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>March</v>
+      </c>
+      <c r="E215" s="32" t="str" cm="1">
+        <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Autumn</v>
+      </c>
+    </row>
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D216" s="1" t="str" cm="1">
+        <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>April</v>
+      </c>
+      <c r="E216" s="32" t="str" cm="1">
+        <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Autumn</v>
+      </c>
+    </row>
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D217" s="1" t="str" cm="1">
+        <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>May</v>
+      </c>
+      <c r="E217" s="32" t="str" cm="1">
+        <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Autumn</v>
+      </c>
+    </row>
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D218" s="1" t="str" cm="1">
+        <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>June</v>
+      </c>
+      <c r="E218" s="32" t="str" cm="1">
+        <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Winter</v>
+      </c>
+    </row>
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D219" s="1" t="str" cm="1">
+        <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>July</v>
+      </c>
+      <c r="E219" s="32" t="str" cm="1">
+        <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Winter</v>
+      </c>
+    </row>
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D220" s="1" t="str" cm="1">
+        <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>August</v>
+      </c>
+      <c r="E220" s="32" t="str" cm="1">
+        <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Winter</v>
+      </c>
+    </row>
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D221" s="1" t="str" cm="1">
+        <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>September</v>
+      </c>
+      <c r="E221" s="32" t="str" cm="1">
+        <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Spring</v>
+      </c>
+    </row>
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D222" s="1" t="str" cm="1">
+        <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>October</v>
+      </c>
+      <c r="E222" s="32" t="str" cm="1">
+        <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Spring</v>
+      </c>
+    </row>
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D223" s="1" t="str" cm="1">
+        <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>November</v>
+      </c>
+      <c r="E223" s="32" t="str" cm="1">
+        <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Spring</v>
+      </c>
+    </row>
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D224" s="1" t="str" cm="1">
+        <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>December</v>
+      </c>
+      <c r="E224" s="32" t="str" cm="1">
+        <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
+        <v>Summer</v>
+      </c>
+    </row>
+    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D227" s="2" t="str" cm="1">
+        <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
+        <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
+      </c>
+    </row>
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D228" s="29" t="str" cm="1">
+        <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
+        <v>VEERG 2026: Table A.1.8.1</v>
+      </c>
+    </row>
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D229" s="38" t="str" cm="1">
+        <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
+        <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
+      </c>
+    </row>
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D231" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E231" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F231" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="G231" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="H231" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="I231" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="J231" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="K231" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="L231" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="M231" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="N231" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="O231" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="P231" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q231" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="R231" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="S231" s="32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D232" s="32" t="str" cm="1">
+        <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E232" s="32" t="str" cm="1">
+        <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>≤10</v>
+      </c>
+      <c r="F232" s="32" cm="1">
+        <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.66</v>
+      </c>
+      <c r="G232" s="32" cm="1">
+        <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H232" s="32" cm="1">
+        <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="I232" s="32" cm="1">
+        <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J232" s="32" cm="1">
+        <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K232" s="32" cm="1">
+        <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L232" s="32" cm="1">
+        <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M232" s="32" cm="1">
+        <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N232" s="32" cm="1">
+        <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O232" s="32" cm="1">
+        <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P232" s="32" cm="1">
+        <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q232" s="32" cm="1">
+        <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R232" s="32" cm="1">
+        <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S232" s="32" cm="1">
+        <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D233" s="1" t="str" cm="1">
+        <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E233" s="32" cm="1">
+        <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>11</v>
+      </c>
+      <c r="F233" s="32" cm="1">
+        <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.68</v>
+      </c>
+      <c r="G233" s="32" cm="1">
+        <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H233" s="32" cm="1">
+        <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.11</v>
+      </c>
+      <c r="I233" s="32" cm="1">
+        <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J233" s="32" cm="1">
+        <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K233" s="32" cm="1">
+        <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L233" s="32" cm="1">
+        <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M233" s="32" cm="1">
+        <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N233" s="32" cm="1">
+        <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O233" s="32" cm="1">
+        <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P233" s="32" cm="1">
+        <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q233" s="32" cm="1">
+        <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R233" s="32" cm="1">
+        <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S233" s="32" cm="1">
+        <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D234" s="1" t="str" cm="1">
+        <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E234" s="32" cm="1">
+        <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>12</v>
+      </c>
+      <c r="F234" s="32" cm="1">
+        <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.7</v>
+      </c>
+      <c r="G234" s="32" cm="1">
+        <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H234" s="32" cm="1">
+        <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.13</v>
+      </c>
+      <c r="I234" s="32" cm="1">
+        <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J234" s="32" cm="1">
+        <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K234" s="32" cm="1">
+        <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L234" s="32" cm="1">
+        <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M234" s="32" cm="1">
+        <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N234" s="32" cm="1">
+        <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O234" s="32" cm="1">
+        <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P234" s="32" cm="1">
+        <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q234" s="32" cm="1">
+        <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R234" s="32" cm="1">
+        <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S234" s="32" cm="1">
+        <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D235" s="1" t="str" cm="1">
+        <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E235" s="32" cm="1">
+        <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>13</v>
+      </c>
+      <c r="F235" s="32" cm="1">
+        <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.71</v>
+      </c>
+      <c r="G235" s="32" cm="1">
+        <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H235" s="32" cm="1">
+        <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I235" s="32" cm="1">
+        <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J235" s="32" cm="1">
+        <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K235" s="32" cm="1">
+        <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L235" s="32" cm="1">
+        <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M235" s="32" cm="1">
+        <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N235" s="32" cm="1">
+        <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O235" s="32" cm="1">
+        <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P235" s="32" cm="1">
+        <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q235" s="32" cm="1">
+        <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R235" s="32" cm="1">
+        <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S235" s="32" cm="1">
+        <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D236" s="1" t="str" cm="1">
+        <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Cool</v>
+      </c>
+      <c r="E236" s="32" cm="1">
+        <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>14</v>
+      </c>
+      <c r="F236" s="32" cm="1">
+        <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.73</v>
+      </c>
+      <c r="G236" s="32" cm="1">
+        <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H236" s="32" cm="1">
+        <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.15</v>
+      </c>
+      <c r="I236" s="32" cm="1">
+        <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1E-3</v>
+      </c>
+      <c r="J236" s="32" cm="1">
+        <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K236" s="32" cm="1">
+        <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L236" s="32" cm="1">
+        <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M236" s="32" cm="1">
+        <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N236" s="32" cm="1">
+        <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O236" s="32" cm="1">
+        <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P236" s="32" cm="1">
+        <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q236" s="32" cm="1">
+        <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R236" s="32" cm="1">
+        <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S236" s="32" cm="1">
+        <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D237" s="1" t="str" cm="1">
+        <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E237" s="32" cm="1">
+        <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>15</v>
+      </c>
+      <c r="F237" s="32" cm="1">
+        <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.74</v>
+      </c>
+      <c r="G237" s="32" cm="1">
+        <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H237" s="32" cm="1">
+        <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.17</v>
+      </c>
+      <c r="I237" s="32" cm="1">
+        <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J237" s="32" cm="1">
+        <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K237" s="32" cm="1">
+        <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L237" s="32" cm="1">
+        <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M237" s="32" cm="1">
+        <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N237" s="32" cm="1">
+        <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O237" s="32" cm="1">
+        <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P237" s="32" cm="1">
+        <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q237" s="32" cm="1">
+        <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R237" s="32" cm="1">
+        <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S237" s="32" cm="1">
+        <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D238" s="1" t="str" cm="1">
+        <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E238" s="32" cm="1">
+        <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>16</v>
+      </c>
+      <c r="F238" s="32" cm="1">
+        <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.75</v>
+      </c>
+      <c r="G238" s="32" cm="1">
+        <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H238" s="32" cm="1">
+        <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I238" s="32" cm="1">
+        <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J238" s="32" cm="1">
+        <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K238" s="32" cm="1">
+        <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L238" s="32" cm="1">
+        <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M238" s="32" cm="1">
+        <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N238" s="32" cm="1">
+        <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O238" s="32" cm="1">
+        <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P238" s="32" cm="1">
+        <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q238" s="32" cm="1">
+        <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R238" s="32" cm="1">
+        <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S238" s="32" cm="1">
+        <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D239" s="1" t="str" cm="1">
+        <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E239" s="32" cm="1">
+        <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>17</v>
+      </c>
+      <c r="F239" s="32" cm="1">
+        <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.76</v>
+      </c>
+      <c r="G239" s="32" cm="1">
+        <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H239" s="32" cm="1">
+        <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.2</v>
+      </c>
+      <c r="I239" s="32" cm="1">
+        <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J239" s="32" cm="1">
+        <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K239" s="32" cm="1">
+        <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L239" s="32" cm="1">
+        <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M239" s="32" cm="1">
+        <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N239" s="32" cm="1">
+        <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O239" s="32" cm="1">
+        <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P239" s="32" cm="1">
+        <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q239" s="32" cm="1">
+        <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R239" s="32" cm="1">
+        <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S239" s="32" cm="1">
+        <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D240" s="1" t="str" cm="1">
+        <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E240" s="32" cm="1">
+        <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>18</v>
+      </c>
+      <c r="F240" s="32" cm="1">
+        <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.77</v>
+      </c>
+      <c r="G240" s="32" cm="1">
+        <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H240" s="32" cm="1">
+        <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.22</v>
+      </c>
+      <c r="I240" s="32" cm="1">
+        <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J240" s="32" cm="1">
+        <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K240" s="32" cm="1">
+        <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L240" s="32" cm="1">
+        <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M240" s="32" cm="1">
+        <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N240" s="32" cm="1">
+        <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O240" s="32" cm="1">
+        <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P240" s="32" cm="1">
+        <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q240" s="32" cm="1">
+        <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R240" s="32" cm="1">
+        <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S240" s="32" cm="1">
+        <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D241" s="1" t="str" cm="1">
+        <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E241" s="32" cm="1">
+        <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>19</v>
+      </c>
+      <c r="F241" s="32" cm="1">
+        <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.77</v>
+      </c>
+      <c r="G241" s="32" cm="1">
+        <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H241" s="32" cm="1">
+        <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.24</v>
+      </c>
+      <c r="I241" s="32" cm="1">
+        <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J241" s="32" cm="1">
+        <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K241" s="32" cm="1">
+        <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L241" s="32" cm="1">
+        <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M241" s="32" cm="1">
+        <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N241" s="32" cm="1">
+        <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O241" s="32" cm="1">
+        <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P241" s="32" cm="1">
+        <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q241" s="32" cm="1">
+        <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R241" s="32" cm="1">
+        <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S241" s="32" cm="1">
+        <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D242" s="1" t="str" cm="1">
+        <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E242" s="32" cm="1">
+        <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>20</v>
+      </c>
+      <c r="F242" s="32" cm="1">
+        <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G242" s="32" cm="1">
+        <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H242" s="32" cm="1">
+        <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.26</v>
+      </c>
+      <c r="I242" s="32" cm="1">
+        <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J242" s="32" cm="1">
+        <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K242" s="32" cm="1">
+        <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L242" s="32" cm="1">
+        <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M242" s="32" cm="1">
+        <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N242" s="32" cm="1">
+        <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O242" s="32" cm="1">
+        <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P242" s="32" cm="1">
+        <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q242" s="32" cm="1">
+        <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R242" s="32" cm="1">
+        <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S242" s="32" cm="1">
+        <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D243" s="1" t="str" cm="1">
+        <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E243" s="32" cm="1">
+        <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>21</v>
+      </c>
+      <c r="F243" s="32" cm="1">
+        <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G243" s="32" cm="1">
+        <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H243" s="32" cm="1">
+        <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I243" s="32" cm="1">
+        <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J243" s="32" cm="1">
+        <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K243" s="32" cm="1">
+        <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L243" s="32" cm="1">
+        <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M243" s="32" cm="1">
+        <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N243" s="32" cm="1">
+        <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O243" s="32" cm="1">
+        <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P243" s="32" cm="1">
+        <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q243" s="32" cm="1">
+        <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R243" s="32" cm="1">
+        <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S243" s="32" cm="1">
+        <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D244" s="1" t="str" cm="1">
+        <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E244" s="32" cm="1">
+        <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>22</v>
+      </c>
+      <c r="F244" s="32" cm="1">
+        <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.78</v>
+      </c>
+      <c r="G244" s="32" cm="1">
+        <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H244" s="32" cm="1">
+        <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.31</v>
+      </c>
+      <c r="I244" s="32" cm="1">
+        <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J244" s="32" cm="1">
+        <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K244" s="32" cm="1">
+        <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L244" s="32" cm="1">
+        <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M244" s="32" cm="1">
+        <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N244" s="32" cm="1">
+        <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O244" s="32" cm="1">
+        <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P244" s="32" cm="1">
+        <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q244" s="32" cm="1">
+        <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R244" s="32" cm="1">
+        <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S244" s="32" cm="1">
+        <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D245" s="1" t="str" cm="1">
+        <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E245" s="32" cm="1">
+        <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>23</v>
+      </c>
+      <c r="F245" s="32" cm="1">
+        <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G245" s="32" cm="1">
+        <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H245" s="32" cm="1">
+        <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.34</v>
+      </c>
+      <c r="I245" s="32" cm="1">
+        <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J245" s="32" cm="1">
+        <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K245" s="32" cm="1">
+        <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L245" s="32" cm="1">
+        <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M245" s="32" cm="1">
+        <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N245" s="32" cm="1">
+        <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O245" s="32" cm="1">
+        <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P245" s="32" cm="1">
+        <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q245" s="32" cm="1">
+        <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R245" s="32" cm="1">
+        <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S245" s="32" cm="1">
+        <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D246" s="1" t="str" cm="1">
+        <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E246" s="32" cm="1">
+        <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>24</v>
+      </c>
+      <c r="F246" s="32" cm="1">
+        <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G246" s="32" cm="1">
+        <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H246" s="32" cm="1">
+        <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.37</v>
+      </c>
+      <c r="I246" s="32" cm="1">
+        <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J246" s="32" cm="1">
+        <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K246" s="32" cm="1">
+        <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L246" s="32" cm="1">
+        <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M246" s="32" cm="1">
+        <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N246" s="32" cm="1">
+        <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O246" s="32" cm="1">
+        <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P246" s="32" cm="1">
+        <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q246" s="32" cm="1">
+        <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R246" s="32" cm="1">
+        <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S246" s="32" cm="1">
+        <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D247" s="1" t="str" cm="1">
+        <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Temperate</v>
+      </c>
+      <c r="E247" s="32" cm="1">
+        <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>25</v>
+      </c>
+      <c r="F247" s="32" cm="1">
+        <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G247" s="32" cm="1">
+        <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H247" s="32" cm="1">
+        <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.41</v>
+      </c>
+      <c r="I247" s="32" cm="1">
+        <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J247" s="32" cm="1">
+        <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="K247" s="32" cm="1">
+        <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L247" s="32" cm="1">
+        <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M247" s="32" cm="1">
+        <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N247" s="32" cm="1">
+        <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O247" s="32" cm="1">
+        <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P247" s="32" cm="1">
+        <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q247" s="32" cm="1">
+        <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R247" s="32" cm="1">
+        <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S247" s="32" cm="1">
+        <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D248" s="1" t="str" cm="1">
+        <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E248" s="32" cm="1">
+        <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>26</v>
+      </c>
+      <c r="F248" s="32" cm="1">
+        <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.79</v>
+      </c>
+      <c r="G248" s="32" cm="1">
+        <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H248" s="32" cm="1">
+        <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.44</v>
+      </c>
+      <c r="I248" s="32" cm="1">
+        <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J248" s="32" cm="1">
+        <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K248" s="32" cm="1">
+        <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L248" s="32" cm="1">
+        <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M248" s="32" cm="1">
+        <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N248" s="32" cm="1">
+        <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O248" s="32" cm="1">
+        <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P248" s="32" cm="1">
+        <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q248" s="32" cm="1">
+        <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R248" s="32" cm="1">
+        <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S248" s="32" cm="1">
+        <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D249" s="1" t="str" cm="1">
+        <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E249" s="32" cm="1">
+        <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>27</v>
+      </c>
+      <c r="F249" s="32" cm="1">
+        <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G249" s="32" cm="1">
+        <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H249" s="32" cm="1">
+        <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.48</v>
+      </c>
+      <c r="I249" s="32" cm="1">
+        <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J249" s="32" cm="1">
+        <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K249" s="32" cm="1">
+        <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L249" s="32" cm="1">
+        <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M249" s="32" cm="1">
+        <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N249" s="32" cm="1">
+        <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O249" s="32" cm="1">
+        <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P249" s="32" cm="1">
+        <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q249" s="32" cm="1">
+        <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R249" s="32" cm="1">
+        <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S249" s="32" cm="1">
+        <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D250" s="1" t="str" cm="1">
+        <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>Warm</v>
+      </c>
+      <c r="E250" s="32" t="str" cm="1">
+        <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>≥28</v>
+      </c>
+      <c r="F250" s="32" cm="1">
+        <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G250" s="32" cm="1">
+        <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H250" s="32" cm="1">
+        <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I250" s="32" cm="1">
+        <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J250" s="32" cm="1">
+        <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K250" s="32" cm="1">
+        <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.02</v>
+      </c>
+      <c r="L250" s="32" cm="1">
+        <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.03</v>
+      </c>
+      <c r="M250" s="32" cm="1">
+        <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0.04</v>
+      </c>
+      <c r="N250" s="32" cm="1">
+        <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O250" s="32" cm="1">
+        <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P250" s="32" cm="1">
+        <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q250" s="32" cm="1">
+        <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>0</v>
+      </c>
+      <c r="R250" s="32" cm="1">
+        <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="S250" s="32" cm="1">
+        <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="D253" s="2" t="str" cm="1">
+        <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
+        <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
+      </c>
+    </row>
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D254" s="29" t="str" cm="1">
+        <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
+        <v>VEERG 2026: Table A.2.1.4</v>
+      </c>
+    </row>
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D255" s="1" t="str" cm="1">
+        <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
+        <v>EFNi &amp; EFN2Oi</v>
+      </c>
+    </row>
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+      <c r="D256" s="16" t="str" cm="1">
+        <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
+        <v>kg N2O - N / kg N</v>
+      </c>
+    </row>
+    <row r="257" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D257" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="E257" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D258" s="32" t="str" cm="1">
+        <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Wet climate zone</v>
+      </c>
+      <c r="E258" s="32" cm="1">
+        <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="259" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="1" t="str" cm="1">
+        <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>Dry climate zone</v>
+      </c>
+      <c r="E259" s="32" cm="1">
+        <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="17">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3403,6 +11636,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -3597,19 +11841,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3621,6 +11854,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3639,17 +11883,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>

--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E627771-0161-402E-9E77-45D4CEA4F452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1053A381-C60D-42E0-8CA4-FC755A77FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="180" windowWidth="35640" windowHeight="18855" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="35745" windowHeight="18900" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -502,24 +502,8 @@
     <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Unit">_xlfn.LAMBDA("kg")</definedName>
     <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Variable">_xlfn.LAMBDA("SRWk")</definedName>
     <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_StandardReferenceWeights_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Split ACT and NSW into separate rows. Added 'State abbreviation' column to aid lookup.")</definedName>
-    <definedName name="Step1">#REF!</definedName>
-    <definedName name="Step2">#REF!</definedName>
-    <definedName name="Step3">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Result_Method1">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Result_Method2">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Result_Method1">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Result_Method2">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method1">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method2">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method1">#REF!</definedName>
-    <definedName name="VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method2">#REF!</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeEnd">'Input - Enterprise'!$E$19</definedName>
     <definedName name="X_Cell_Enterprise_ProductionTimeframeStart">'Input - Enterprise'!$E$18</definedName>
-    <definedName name="X_Cell_PastureBeef_Breed">#REF!</definedName>
-    <definedName name="X_Cell_PastureBeef_FencedWater">#REF!</definedName>
-    <definedName name="X_Cell_PastureBeef_GrazingIrrigationMethod">#REF!</definedName>
-    <definedName name="X_Cell_PastureBeef_GrazingProductionSystem">#REF!</definedName>
-    <definedName name="X_Cell_PastureBeef_ProductionRegion">#REF!</definedName>
     <definedName name="X_Cell_Site_AverageTemperature">'Input - Site'!$E$14</definedName>
     <definedName name="X_Cell_Site_ClimateZone">'Input - Site'!$E$20</definedName>
     <definedName name="X_Cell_Site_Elevation">'Input - Site'!$E$13</definedName>
@@ -536,18 +520,6 @@
     <definedName name="X_Cell_Site_TemperatureZone">'Input - Site'!$E$22</definedName>
     <definedName name="X_Cell_Site_TotalRainfall">'Input - Site'!$E$15</definedName>
     <definedName name="X_Cell_Site_WetOrDryClimateZone">'Input - Site'!$E$21</definedName>
-    <definedName name="X_Table_PastureBeef_CrudeProtein_Method1">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_CrudeProtein_Method2">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_DryMatterDigestibility_Method1">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_DryMatterDigestibility_Method2">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_Duration_Method1">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_Duration_Method2">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_Head_Method1">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_Head_Method2">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_Liveweight_Method1">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_Liveweight_Method2">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_LiveweightGain_Method1">#REF!</definedName>
-    <definedName name="X_Table_PastureBeef_LiveweightGain_Method2">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -607,7 +579,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="181">
   <si>
     <t>Home</t>
   </si>
@@ -618,9 +590,6 @@
     <t>APPENDICES</t>
   </si>
   <si>
-    <t>Emissions breakdown</t>
-  </si>
-  <si>
     <t>CALCULATIONS</t>
   </si>
   <si>
@@ -706,30 +675,6 @@
   </si>
   <si>
     <t>Percent manure applied to soil with no purpose (as waste)</t>
-  </si>
-  <si>
-    <t>Livestock sales</t>
-  </si>
-  <si>
-    <t>⚠️ Livestock sales are not automatically reflected in the herd movement data - you will need to manually adjust head count and average liveweight</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Sale date</t>
-  </si>
-  <si>
-    <t>Head sold</t>
-  </si>
-  <si>
-    <t>Average weight per head (kg)</t>
-  </si>
-  <si>
-    <t>Total liveweight sold</t>
-  </si>
-  <si>
-    <t>Bulls &gt; 1 year</t>
   </si>
   <si>
     <t>tonnes</t>
@@ -1222,6 +1167,15 @@
   </si>
   <si>
     <t>Input - Enterprise</t>
+  </si>
+  <si>
+    <t>Liveweight sold - method 1</t>
+  </si>
+  <si>
+    <t>Liveweight sold - method 2</t>
+  </si>
+  <si>
+    <t>percent</t>
   </si>
 </sst>
 </file>
@@ -4296,46 +4250,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CBCD503-838A-4523-932C-9BA527D1C34C}" name="Table_Input_LivestockSales3" displayName="Table_Input_LivestockSales3" ref="D33:H35" totalsRowShown="0">
-  <autoFilter ref="D33:H35" xr:uid="{6CBCD503-838A-4523-932C-9BA527D1C34C}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BFA511D-1E33-4FA7-9E53-155741FDE40A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+  <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{10611EAE-C98A-4772-A79C-DBC0DEE0D909}" name="Class"/>
-    <tableColumn id="2" xr3:uid="{C72E6C94-BA4D-4748-84FC-BCCF1BBBA7D6}" name="Sale date"/>
-    <tableColumn id="3" xr3:uid="{BC87B559-6411-49E0-9FED-D9EC6CFBBD83}" name="Head sold"/>
-    <tableColumn id="4" xr3:uid="{F08DE3C5-21CB-42C6-A868-7EFDDF741BF4}" name="Average weight per head (kg)"/>
-    <tableColumn id="5" xr3:uid="{9F84455A-39E1-4212-B9E8-759D853A4C96}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
-      <calculatedColumnFormula>F34*G34</calculatedColumnFormula>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A7717A66-4BDA-43C0-BFCD-4A6F29AEE8A3}" name="State/Territory">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Editable table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{EC0B98FF-3B1A-4F33-9028-A6B26A7E6CE4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
-  <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BBC50AC7-FEC1-431E-AD41-7CB9E130FE72}" name="Leaching Zone">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{D6D2A619-26C3-4096-9C5E-261DB4783E3F}" name="Common Name">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ED997B4B-69AA-458D-AD94-F4C79A1B94D0}" name="Leaching criteria">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{8F8F275A-708B-458E-9ABF-5295B622DDF7}" name="Abbreviation">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C1B321B1-DD2B-4EC5-AE20-D47C87F02BBF}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4353,7 +4289,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{14C890C4-4A77-40EC-A6C1-19C0895BD309}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4371,7 +4307,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6BB36C9A-81C9-4008-9621-02E7765F4217}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4401,7 +4337,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{81046769-5E78-4435-8902-BE2F7ED271E9}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4419,7 +4355,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0D2D24A9-44B5-40A8-9D93-5D127038E490}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4437,7 +4373,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{E20A54E0-06E3-423D-998B-2E4A7C9A48F2}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4455,7 +4391,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{06A63BFC-1602-47C1-AF55-49AA6B4633CD}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4529,7 +4465,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{949FFD0F-1699-4700-8323-CF2162C2663F}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4548,28 +4484,6 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2BFA511D-1E33-4FA7-9E53-155741FDE40A}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
-  <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A7717A66-4BDA-43C0-BFCD-4A6F29AEE8A3}" name="State/Territory">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{D6D2A619-26C3-4096-9C5E-261DB4783E3F}" name="Common Name">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{8F8F275A-708B-458E-9ABF-5295B622DDF7}" name="Abbreviation">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A251EF82-BC21-4875-B405-6D0F230C2B8D}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4583,7 +4497,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3F15B4B0-BD4E-4903-9096-ED3FE0A9167C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4601,7 +4515,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{66C67C36-18E1-4B8A-BFF1-35CF3DC4AC81}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4631,7 +4545,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1D6C8105-982C-4B9F-A603-F884FE56E1B4}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4705,7 +4619,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D228FD2E-DAAA-4D4F-BEFF-0E68A1F33AA0}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4723,7 +4637,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E436A27C-11D9-4092-B110-DE3B0C7D7A9C}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4749,7 +4663,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AA9D31FA-C10A-401A-A990-FD7418530E07}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -4769,6 +4683,24 @@
     </tableColumn>
     <tableColumn id="4" xr3:uid="{EDCA589F-5D6E-4F25-A934-864B94D632CD}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{EC0B98FF-3B1A-4F33-9028-A6B26A7E6CE4}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+  <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{BBC50AC7-FEC1-431E-AD41-7CB9E130FE72}" name="Leaching Zone">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{ED997B4B-69AA-458D-AD94-F4C79A1B94D0}" name="Leaching criteria">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4998,7 +4930,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="941" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="565" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -5064,7 +4996,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5092,8 +5024,9 @@
         <v>Results</v>
       </c>
       <c r="C4" s="9"/>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
+      <c r="D4" s="2" t="str">
+        <f>"Emissions breakdown for activities running between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmmm yyyy") &amp; " and " &amp; TEXT('Input - Enterprise'!E13, "dd mmmm yyyy")</f>
+        <v>Emissions breakdown for activities running between 01 January 2024 and 31 December 2024</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -5121,22 +5054,22 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="21" t="s">
+      <c r="I6" s="21" t="s">
         <v>12</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>13</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="9"/>
@@ -5148,7 +5081,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E7" s="19" t="e" cm="1">
         <f t="array" ref="E7">VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
@@ -5159,12 +5092,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G7" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="19" t="e" cm="1">
+        <f t="array" ref="H7">Common_Equations.Common_ConvertCH4ToCO2e(E7,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I7" s="19" t="e" cm="1">
+        <f t="array" ref="I7">Common_Equations.Common_ConvertCH4ToCO2e(F7,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>8</v>
-      </c>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="16" t="s">
-        <v>9</v>
       </c>
       <c r="K7" s="9"/>
     </row>
@@ -5175,21 +5114,29 @@
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+        <v>14</v>
+      </c>
+      <c r="E8" s="19" t="e" cm="1">
+        <f t="array" ref="E8">VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F8" s="19" t="e" cm="1">
+        <f t="array" ref="F8">VEERG_4_2_1_1__1_TotalAnnualMethaneProductionFromManureManagement_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
       <c r="G8" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="19" t="e" cm="1">
+        <f t="array" ref="H8">Common_Equations.Common_ConvertCH4ToCO2e(E8,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I8" s="19" t="e" cm="1">
+        <f t="array" ref="I8">Common_Equations.Common_ConvertCH4ToCO2e(F8,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>8</v>
-      </c>
-      <c r="H8" s="19">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19">
-        <v>2</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>9</v>
       </c>
       <c r="K8" s="9"/>
     </row>
@@ -5197,45 +5144,61 @@
       <c r="A9" s="5"/>
       <c r="C9" s="9"/>
       <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="E9" s="19" t="e" cm="1">
+        <f t="array" ref="E9">VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F9" s="19" t="e" cm="1">
+        <f t="array" ref="F9">VEERG_4_2_1_3__1_DirectNitrousOxideEmissionsOnPasture_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
       <c r="G9" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="19">
-        <v>2</v>
-      </c>
-      <c r="I9" s="19">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="H9" s="19" t="e" cm="1">
+        <f t="array" ref="H9">Common_Equations.Common_ConvertN2OToCO2e(E9,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I9" s="19" t="e" cm="1">
+        <f t="array" ref="I9">Common_Equations.Common_ConvertN2OToCO2e(F9,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="E10" s="19" t="e" cm="1">
+        <f t="array" ref="E10">VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F10" s="19" t="e" cm="1">
+        <f t="array" ref="F10">VEERG_4_2_1_5__1_AtmosphericDepositionEmissionsFromUrineAndDungOnPasture_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
       <c r="G10" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="19">
-        <v>3</v>
-      </c>
-      <c r="I10" s="19">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="H10" s="19" t="e" cm="1">
+        <f t="array" ref="H10">Common_Equations.Common_ConvertN2OToCO2e(E10,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I10" s="19" t="e" cm="1">
+        <f t="array" ref="I10">Common_Equations.Common_ConvertN2OToCO2e(F10,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K10" s="9"/>
     </row>
@@ -5246,21 +5209,29 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+        <v>18</v>
+      </c>
+      <c r="E11" s="19" t="e" cm="1">
+        <f t="array" ref="E11">VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method1</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F11" s="19" t="e" cm="1">
+        <f t="array" ref="F11">VEERG_4_2_1_7__1_LeachingAndRunoffEmissionsFromUrineAndDungOnPasture_Result_Method2</f>
+        <v>#NAME?</v>
+      </c>
       <c r="G11" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="19">
-        <v>4</v>
-      </c>
-      <c r="I11" s="19">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="H11" s="19" t="e" cm="1">
+        <f t="array" ref="H11">Common_Equations.Common_ConvertN2OToCO2e(E11,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I11" s="19" t="e" cm="1">
+        <f t="array" ref="I11">Common_Equations.Common_ConvertN2OToCO2e(F11,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K11" s="9"/>
     </row>
@@ -5271,7 +5242,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E12" s="19" t="e" cm="1">
         <f t="array" ref="E12">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method1</f>
@@ -5282,12 +5253,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="e" cm="1">
+        <f t="array" ref="H12">Common_Equations.Common_ConvertN2OToCO2e(E12,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I12" s="19" t="e" cm="1">
+        <f t="array" ref="I12">Common_Equations.Common_ConvertN2OToCO2e(F12,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J12" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K12" s="9"/>
     </row>
@@ -5298,7 +5275,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="1" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E13" s="19" t="e" cm="1">
         <f t="array" ref="E13">VEERG_5_1_1_3__1_InorganicFertiliserApplicationCO2Emissions_Result_Method1</f>
@@ -5309,12 +5286,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+        <v>149</v>
+      </c>
+      <c r="H13" s="19" t="e">
+        <f>E13</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I13" s="19" t="e">
+        <f>F13</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J13" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K13" s="9"/>
     </row>
@@ -5325,7 +5308,7 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E14" s="19" t="e" cm="1">
         <f t="array" ref="E14">VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser_Result_Method1</f>
@@ -5336,12 +5319,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H14" s="19" t="e" cm="1">
+        <f t="array" ref="H14">Common_Equations.Common_ConvertN2OToCO2e(E14,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I14" s="19" t="e" cm="1">
+        <f t="array" ref="I14">Common_Equations.Common_ConvertN2OToCO2e(F14,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J14" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K14" s="9"/>
     </row>
@@ -5349,7 +5338,7 @@
       <c r="A15" s="5"/>
       <c r="C15" s="9"/>
       <c r="D15" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E15" s="19" t="e" cm="1">
         <f t="array" ref="E15">VEERG_5_3_1_1__1_LimeApplicationCO2Emissions_Result_Method1</f>
@@ -5360,12 +5349,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
+        <v>149</v>
+      </c>
+      <c r="H15" s="19" t="e">
+        <f>E15</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I15" s="19" t="e">
+        <f>F15</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J15" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K15" s="9"/>
     </row>
@@ -5375,7 +5370,7 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="1" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E16" s="19" t="e" cm="1">
         <f t="array" ref="E16">VEERG_5_4_1_3__1_OrganicFertiliserAtmosphericDepositionN2OEmissions_Result_Method1</f>
@@ -5386,12 +5381,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H16" s="19" t="e" cm="1">
+        <f t="array" ref="H16">Common_Equations.Common_ConvertN2OToCO2e(E16,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I16" s="19" t="e" cm="1">
+        <f t="array" ref="I16">Common_Equations.Common_ConvertN2OToCO2e(F16,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J16" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K16" s="9"/>
     </row>
@@ -5402,7 +5403,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E17" s="19" t="e" cm="1">
         <f t="array" ref="E17">VEERG_5_5_1_1__1_FertiliserLeachingAndRunoffN2OEmissions_result_Method1</f>
@@ -5413,12 +5414,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H17" s="19" t="e" cm="1">
+        <f t="array" ref="H17">Common_Equations.Common_ConvertN2OToCO2e(E17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I17" s="19" t="e" cm="1">
+        <f t="array" ref="I17">Common_Equations.Common_ConvertN2OToCO2e(F17,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J17" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K17" s="9"/>
     </row>
@@ -5429,7 +5436,7 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="1" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E18" s="19" t="e" cm="1">
         <f t="array" ref="E18">VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method1</f>
@@ -5440,12 +5447,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H18" s="19" t="e" cm="1">
+        <f t="array" ref="H18">Common_Equations.Common_ConvertN2OToCO2e(E18,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I18" s="19" t="e" cm="1">
+        <f t="array" ref="I18">Common_Equations.Common_ConvertN2OToCO2e(F18,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J18" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K18" s="9"/>
     </row>
@@ -5456,7 +5469,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E19" s="19" t="e" cm="1">
         <f t="array" ref="E19">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_PastureOnly_Result_Method1</f>
@@ -5467,12 +5480,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H19" s="19" t="e" cm="1">
+        <f t="array" ref="H19">Common_Equations.Common_ConvertN2OToCO2e(E19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I19" s="19" t="e" cm="1">
+        <f t="array" ref="I19">Common_Equations.Common_ConvertN2OToCO2e(F19,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J19" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K19" s="9"/>
     </row>
@@ -5483,7 +5502,7 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E20" s="19" t="e" cm="1">
         <f t="array" ref="E20">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
@@ -5494,19 +5513,25 @@
         <v>#NAME?</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
+        <v>149</v>
+      </c>
+      <c r="H20" s="19" t="e">
+        <f>E20</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I20" s="19" t="e">
+        <f>F20</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J20" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="D21" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E21" s="19" t="e" cm="1">
         <f t="array" ref="E21">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
@@ -5517,12 +5542,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G21" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="19" t="e" cm="1">
+        <f t="array" ref="H21">Common_Equations.Common_ConvertCH4ToCO2e(E21,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I21" s="19" t="e" cm="1">
+        <f t="array" ref="I21">Common_Equations.Common_ConvertCH4ToCO2e(F21,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J21" s="16" t="s">
         <v>8</v>
-      </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="16" t="s">
-        <v>9</v>
       </c>
       <c r="K21" s="9"/>
     </row>
@@ -5530,7 +5561,7 @@
       <c r="A22" s="5"/>
       <c r="C22" s="9"/>
       <c r="D22" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E22" s="19" t="e" cm="1">
         <f t="array" ref="E22">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
@@ -5541,12 +5572,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H22" s="19" t="e" cm="1">
+        <f t="array" ref="H22">Common_Equations.Common_ConvertN2OToCO2e(E22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I22" s="19" t="e" cm="1">
+        <f t="array" ref="I22">Common_Equations.Common_ConvertN2OToCO2e(F22,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J22" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K22" s="9"/>
     </row>
@@ -5554,7 +5591,7 @@
       <c r="A23" s="5"/>
       <c r="C23" s="9"/>
       <c r="D23" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E23" s="19" t="e" cm="1">
         <f t="array" ref="E23">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
@@ -5565,12 +5602,18 @@
         <v>#NAME?</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
+        <v>149</v>
+      </c>
+      <c r="H23" s="19" t="e">
+        <f>E23</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I23" s="19" t="e">
+        <f>F23</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J23" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K23" s="9"/>
     </row>
@@ -5578,7 +5621,7 @@
       <c r="A24" s="5"/>
       <c r="C24" s="9"/>
       <c r="D24" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E24" s="19" t="e" cm="1">
         <f t="array" ref="E24">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
@@ -5589,19 +5632,25 @@
         <v>#NAME?</v>
       </c>
       <c r="G24" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="19" t="e" cm="1">
+        <f t="array" ref="H24">Common_Equations.Common_ConvertCH4ToCO2e(E24,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I24" s="19" t="e" cm="1">
+        <f t="array" ref="I24">Common_Equations.Common_ConvertCH4ToCO2e(F24,_xlfn.XLOOKUP("CH4", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J24" s="16" t="s">
         <v>8</v>
-      </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="16" t="s">
-        <v>9</v>
       </c>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="D25" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E25" s="19" t="e" cm="1">
         <f t="array" ref="E25">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
@@ -5612,19 +5661,25 @@
         <v>#NAME?</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
+        <v>15</v>
+      </c>
+      <c r="H25" s="19" t="e" cm="1">
+        <f t="array" ref="H25">Common_Equations.Common_ConvertN2OToCO2e(E25,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I25" s="19" t="e" cm="1">
+        <f t="array" ref="I25">Common_Equations.Common_ConvertN2OToCO2e(F25,_xlfn.XLOOKUP("N2O", Table_GWPData[Gas],Table_GWPData[CO2-e factor]))</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J25" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
       <c r="D26" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E26" s="19" t="e" cm="1">
         <f t="array" ref="E26">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
@@ -5635,19 +5690,25 @@
         <v>#NAME?</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
+        <v>8</v>
+      </c>
+      <c r="H26" s="19" t="e">
+        <f>E26</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I26" s="19" t="e">
+        <f>F26</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J26" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="D27" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E27" s="19" t="e" cm="1">
         <f t="array" ref="E27">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
@@ -5658,33 +5719,39 @@
         <v>#NAME?</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
+        <v>8</v>
+      </c>
+      <c r="H27" s="19" t="e">
+        <f>E27</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I27" s="19" t="e">
+        <f>F27</f>
+        <v>#NAME?</v>
+      </c>
       <c r="J27" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="9"/>
       <c r="D28" s="15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="15"/>
-      <c r="H28" s="20">
+      <c r="H28" s="20" t="e">
         <f>SUM(H7:H27)</f>
-        <v>10</v>
-      </c>
-      <c r="I28" s="20">
+        <v>#NAME?</v>
+      </c>
+      <c r="I28" s="20" t="e">
         <f>SUM(I7:I27)</f>
-        <v>14</v>
+        <v>#NAME?</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K28" s="9"/>
     </row>
@@ -5724,7 +5791,7 @@
     <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="9"/>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -5751,7 +5818,7 @@
     <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="9"/>
       <c r="D34" s="1" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -5775,13 +5842,13 @@
     <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="9"/>
       <c r="D36" s="21" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E36" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="21" t="s">
         <v>12</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>13</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="14"/>
@@ -5804,7 +5871,7 @@
         <v>Enter value</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="9"/>
@@ -5816,16 +5883,16 @@
       <c r="D38" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
-      <c r="E38" s="88">
+      <c r="E38" s="88" t="e">
         <f>IF(ISBLANK($D38), "", IF(ISNUMBER(SEARCH("reporting", $D38)), Result_Enterprise_Method1, "Enter value"))</f>
-        <v>10</v>
-      </c>
-      <c r="F38" s="88">
+        <v>#NAME?</v>
+      </c>
+      <c r="F38" s="88" t="e">
         <f>IF(ISBLANK($D38), "", IF(ISNUMBER(SEARCH("reporting", $D38)), Result_Enterprise_Method2, "Enter value"))</f>
-        <v>14</v>
+        <v>#NAME?</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="9"/>
@@ -5846,7 +5913,7 @@
         <v>Enter value</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H39" s="14"/>
       <c r="I39" s="9"/>
@@ -5865,7 +5932,7 @@
         <v/>
       </c>
       <c r="G40" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="9"/>
@@ -5884,7 +5951,7 @@
         <v/>
       </c>
       <c r="G41" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="9"/>
@@ -5894,15 +5961,15 @@
     <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="9"/>
       <c r="D42" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="20">
+        <v>150</v>
+      </c>
+      <c r="E42" s="20" t="e">
         <f>SUM(E37:E41)</f>
-        <v>10</v>
-      </c>
-      <c r="F42" s="20">
+        <v>#NAME?</v>
+      </c>
+      <c r="F42" s="20" t="e">
         <f>SUM(F37:F41)</f>
-        <v>14</v>
+        <v>#NAME?</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -5935,7 +6002,7 @@
     <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -5959,10 +6026,10 @@
     <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="21" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -5981,7 +6048,7 @@
         <v>0.6</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -5998,7 +6065,7 @@
         <v>0.5</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -6012,10 +6079,10 @@
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
       <c r="E50" s="88" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -6028,7 +6095,7 @@
       <c r="D51" s="1"/>
       <c r="E51" s="88"/>
       <c r="F51" s="16" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -6041,7 +6108,7 @@
       <c r="D52" s="1"/>
       <c r="E52" s="88"/>
       <c r="F52" s="16" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -6052,7 +6119,7 @@
     <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="9"/>
       <c r="D53" s="15" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E53" s="20">
         <f>SUM(E48:E51)</f>
@@ -6090,7 +6157,7 @@
     <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -6115,10 +6182,10 @@
       <c r="C58" s="9"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -6129,15 +6196,15 @@
     <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="9"/>
       <c r="D59" s="91" t="s">
-        <v>161</v>
-      </c>
-      <c r="E59" s="89">
+        <v>152</v>
+      </c>
+      <c r="E59" s="89" t="e">
         <f>E42-E53</f>
-        <v>8.9</v>
-      </c>
-      <c r="F59" s="89">
+        <v>#NAME?</v>
+      </c>
+      <c r="F59" s="89" t="e">
         <f>F42-E53</f>
-        <v>12.9</v>
+        <v>#NAME?</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -6159,106 +6226,106 @@
     <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="21" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H61" s="21" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J61" s="21" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="K61" s="9"/>
     </row>
     <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="9"/>
       <c r="D62" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F62" s="19">
         <f>'Input - Enterprise'!E22</f>
-        <v>9.5</v>
-      </c>
-      <c r="G62" s="19">
+        <v>0</v>
+      </c>
+      <c r="G62" s="19" t="e">
         <f>F62/(F62+F63)</f>
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H62" s="19">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H62" s="19" t="e">
         <f>($E$42/F62)*G62</f>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="I62" s="19">
+        <v>#NAME?</v>
+      </c>
+      <c r="I62" s="19" t="e">
         <f>($F$42/F62)*G62</f>
-        <v>1.1666666666666665</v>
+        <v>#NAME?</v>
       </c>
       <c r="J62" s="16" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K62" s="9"/>
     </row>
     <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F63" s="19">
-        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E26</f>
-        <v>2.5</v>
-      </c>
-      <c r="G63" s="19">
+        <f>'Input - Enterprise'!E26*'Input - Enterprise'!E27</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="19" t="e">
         <f>F63/(F62+F63)</f>
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="H63" s="19">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H63" s="19" t="e">
         <f>($E$42/F63)*G63</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="I63" s="19">
+        <v>#NAME?</v>
+      </c>
+      <c r="I63" s="19" t="e">
         <f>($F$42/F63)*G63</f>
-        <v>1.1666666666666667</v>
+        <v>#NAME?</v>
       </c>
       <c r="J63" s="16" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="K63" s="9"/>
     </row>
     <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F64" s="19">
-        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E27</f>
-        <v>1.5</v>
+        <f>'Input - Enterprise'!E26*'Input - Enterprise'!E28</f>
+        <v>0</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
@@ -6277,54 +6344,54 @@
     <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F66" s="19">
-        <f>'Input - Enterprise'!E23</f>
-        <v>300</v>
+        <f>'Input - Enterprise'!E24</f>
+        <v>0</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="H66" s="19">
+        <v>145</v>
+      </c>
+      <c r="H66" s="19" t="e">
         <f>E59/F66</f>
-        <v>2.9666666666666668E-2</v>
+        <v>#NAME?</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="J66" s="16" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="K66" s="9"/>
     </row>
     <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F67" s="19">
-        <f>'Input - Enterprise'!E24</f>
-        <v>310</v>
+        <f>'Input - Enterprise'!E25</f>
+        <v>0</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="I67" s="19">
+        <v>145</v>
+      </c>
+      <c r="I67" s="19" t="e">
         <f>F59/F67</f>
-        <v>4.161290322580645E-2</v>
+        <v>#NAME?</v>
       </c>
       <c r="J67" s="16" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="K67" s="9"/>
     </row>
@@ -6578,7 +6645,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="40" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:24" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6636,7 +6703,7 @@
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="N5" s="43"/>
     </row>
@@ -6652,7 +6719,7 @@
         <v>Site</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="56"/>
@@ -6664,7 +6731,7 @@
         <v>Pasture Beef</v>
       </c>
       <c r="D8" s="58" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E8" s="59"/>
       <c r="F8" s="59"/>
@@ -6679,16 +6746,16 @@
     </row>
     <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="N10" s="47"/>
     </row>
@@ -6698,13 +6765,13 @@
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G11" s="1"/>
       <c r="N11" s="52"/>
@@ -6715,13 +6782,13 @@
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6730,13 +6797,13 @@
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E13" s="46">
         <v>307.7</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="N13" s="54"/>
       <c r="O13" s="54"/>
@@ -6747,13 +6814,13 @@
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E14" s="46">
         <v>18</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="N14" s="54"/>
       <c r="O14" s="54"/>
@@ -6761,13 +6828,13 @@
     <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E15" s="46">
         <v>601</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="N15" s="54"/>
       <c r="O15" s="54"/>
@@ -6777,13 +6844,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E16" s="46">
         <v>1326</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="N16" s="54"/>
       <c r="O16" s="54"/>
@@ -6794,13 +6861,13 @@
         <v>Constants - Pasture Beef</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E17" s="46">
         <v>7</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6809,7 +6876,7 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E18" s="27">
         <f>E15/E16</f>
@@ -6823,7 +6890,7 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E19" s="27" t="str">
         <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E15,Table_SourceData_RainfallZones[Min rainfall],Table_SourceData_RainfallZones[Max rainfall],Table_SourceData_RainfallZones[Rainfall Zone])</f>
@@ -6838,7 +6905,7 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E20" s="27" t="str">
         <f>Common_InputFunctions.Utility_GetClimateZone(E14,E15,E17,E13,E18,Table_SourceData_ClimateZones[Min temp],Table_SourceData_ClimateZones[Max temp],Table_SourceData_ClimateZones[Min rainfall],Table_SourceData_ClimateZones[Max rainfall],Table_SourceData_ClimateZones[Min frost days],Table_SourceData_ClimateZones[Max frost days],Table_SourceData_ClimateZones[Min elevation],Table_SourceData_ClimateZones[Max elevation],Table_SourceData_ClimateZones[Min MAP:PET],Table_SourceData_ClimateZones[Max MAP:PET],Table_SourceData_ClimateZones[Climate zone])</f>
@@ -6851,7 +6918,7 @@
     <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E21" s="27" t="str">
         <f>Common_InputFunctions.Utility_LookupValueInTable($E$20,Table_SourceData_WetDryZones[Climate zone],Table_SourceData_WetDryZones[Wet or Dry Zone])</f>
@@ -6863,7 +6930,7 @@
     <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E22" s="27" t="str">
         <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E14,Table_SourceData_TemperatureZones[Min MAT],Table_SourceData_TemperatureZones[Max MAT],Table_SourceData_TemperatureZones[Temperature Zone])</f>
@@ -7327,7 +7394,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30171F5-957D-4D10-AA21-0CE17EC217CD}">
-  <dimension ref="C1:J35"/>
+  <dimension ref="C1:J32"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7341,7 +7408,7 @@
   <sheetData>
     <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
       <c r="C1" s="40" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D1" s="34"/>
       <c r="E1" s="34"/>
@@ -7373,7 +7440,7 @@
     </row>
     <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="37"/>
@@ -7387,20 +7454,20 @@
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="37"/>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D8" s="23" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
@@ -7413,7 +7480,7 @@
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D10" s="48" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E10" s="49"/>
       <c r="F10" s="50"/>
@@ -7427,26 +7494,26 @@
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D12" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" s="26">
         <v>45292</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G12" s="37"/>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D13" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="53">
         <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
         <v>45657</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G13" s="37"/>
     </row>
@@ -7456,181 +7523,130 @@
     </row>
     <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="26">
         <v>45231</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" s="26">
         <v>45747</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" s="27">
         <f>DATEDIF(E18,E19+1,"m")</f>
         <v>17</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="27">
-        <f>SUM(Table_Input_LivestockSales3[Total liveweight sold])*10^-3</f>
-        <v>9.5</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="E22" s="27"/>
       <c r="F22" s="28" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="27">
-        <v>300</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="E23" s="27"/>
       <c r="F23" s="28" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="27">
-        <v>310</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E24" s="27"/>
       <c r="F24" s="28" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="27">
-        <v>5</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E25" s="27"/>
       <c r="F25" s="28" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="30">
-        <v>0.5</v>
+        <v>28</v>
+      </c>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" s="30">
-        <v>0.3</v>
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="31">
-        <f>100%-E26-E27</f>
+        <v>30</v>
+      </c>
+      <c r="E28" s="30">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="31">
+        <f>100%-E27-E28</f>
         <v>0.2</v>
       </c>
+      <c r="F29" s="28" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="D31" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D33" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="G33" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D34" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="32">
-        <v>45566</v>
-      </c>
-      <c r="F34" s="32">
-        <v>10</v>
-      </c>
-      <c r="G34" s="32">
-        <v>500</v>
-      </c>
-      <c r="H34" s="27">
-        <f>F34*G34</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="35" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D35" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="32">
-        <v>45415</v>
-      </c>
-      <c r="F35" s="32">
-        <v>10</v>
-      </c>
-      <c r="G35" s="32">
-        <v>450</v>
-      </c>
-      <c r="H35" s="27">
-        <f>F35*G35</f>
-        <v>4500</v>
-      </c>
+      <c r="D32" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -7667,7 +7683,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7710,13 +7726,13 @@
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="D6" s="32" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7867,7 +7883,7 @@
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="32" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7966,10 +7982,10 @@
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="32" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8062,19 +8078,19 @@
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="32" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G47" s="32" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H47" s="32" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8264,10 +8280,10 @@
     <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="32" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E63" s="32" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8454,52 +8470,52 @@
     <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F89" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="G89" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H89" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="I89" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="J89" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="K89" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="L89" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="E89" s="32" t="s">
+      <c r="M89" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="N89" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="F89" s="32" t="s">
+      <c r="O89" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="G89" s="32" t="s">
+      <c r="P89" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="H89" s="32" t="s">
+      <c r="Q89" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I89" s="32" t="s">
+      <c r="R89" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="J89" s="32" t="s">
+      <c r="S89" s="32" t="s">
         <v>60</v>
-      </c>
-      <c r="K89" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L89" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="M89" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="N89" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="O89" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="P89" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q89" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="R89" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="S89" s="32" t="s">
-        <v>69</v>
       </c>
       <c r="T89" s="32"/>
     </row>
@@ -9086,16 +9102,16 @@
     <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="32" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E109" s="32" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F109" s="32" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G109" s="32" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9180,16 +9196,16 @@
     </row>
     <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="32" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E119" s="32" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F119" s="32" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G119" s="32" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="BN119" s="34"/>
     </row>
@@ -9250,10 +9266,10 @@
     <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="32" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E127" s="32" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9294,10 +9310,10 @@
     </row>
     <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E134" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9380,10 +9396,10 @@
     </row>
     <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="32" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E142" s="32" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BN142" s="34"/>
     </row>
@@ -9467,10 +9483,10 @@
     </row>
     <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D153" s="32" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E153" s="32" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="BC153" s="37"/>
       <c r="BD153" s="37"/>
@@ -9740,19 +9756,19 @@
     </row>
     <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="32" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E186" s="32" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F186" s="32" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G186" s="32" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H186" s="32" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10067,10 +10083,10 @@
     </row>
     <row r="206" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D206" s="32" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E206" s="32" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
@@ -10101,10 +10117,10 @@
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D212" s="32" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E212" s="32" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
@@ -10247,52 +10263,52 @@
     </row>
     <row r="231" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D231" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E231" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="F231" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G231" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="H231" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="I231" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J231" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="K231" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="L231" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="M231" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E231" s="32" t="s">
+      <c r="N231" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="F231" s="39" t="s">
+      <c r="O231" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="G231" s="32" t="s">
+      <c r="P231" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="H231" s="32" t="s">
+      <c r="Q231" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="I231" s="32" t="s">
+      <c r="R231" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="J231" s="32" t="s">
+      <c r="S231" s="32" t="s">
         <v>96</v>
-      </c>
-      <c r="K231" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="L231" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="M231" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="N231" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="O231" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="P231" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q231" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="R231" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="S231" s="32" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
@@ -11575,10 +11591,10 @@
     </row>
     <row r="257" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D257" s="32" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E257" s="32" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="258" spans="4:5" x14ac:dyDescent="0.25">
@@ -11627,15 +11643,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -11646,7 +11653,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -11841,19 +11848,20 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -11864,7 +11872,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11883,10 +11891,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1053A381-C60D-42E0-8CA4-FC755A77FDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680F03D4-84EC-4C66-BC5D-7A7510239EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="35745" windowHeight="18900" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1245" yWindow="555" windowWidth="35745" windowHeight="18900" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -579,7 +579,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="180">
   <si>
     <t>Home</t>
   </si>
@@ -1170,9 +1170,6 @@
   </si>
   <si>
     <t>Liveweight sold - method 1</t>
-  </si>
-  <si>
-    <t>Liveweight sold - method 2</t>
   </si>
   <si>
     <t>percent</t>
@@ -6286,7 +6283,7 @@
         <v>143</v>
       </c>
       <c r="F63" s="19">
-        <f>'Input - Enterprise'!E26*'Input - Enterprise'!E27</f>
+        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E26</f>
         <v>0</v>
       </c>
       <c r="G63" s="19" t="e">
@@ -6315,7 +6312,7 @@
         <v>146</v>
       </c>
       <c r="F64" s="19">
-        <f>'Input - Enterprise'!E26*'Input - Enterprise'!E28</f>
+        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E27</f>
         <v>0</v>
       </c>
       <c r="G64" s="19" t="s">
@@ -6350,7 +6347,7 @@
         <v>145</v>
       </c>
       <c r="F66" s="19">
-        <f>'Input - Enterprise'!E24</f>
+        <f>'Input - Enterprise'!E23</f>
         <v>0</v>
       </c>
       <c r="G66" s="19" t="s">
@@ -6377,7 +6374,7 @@
         <v>145</v>
       </c>
       <c r="F67" s="19">
-        <f>'Input - Enterprise'!E25</f>
+        <f>'Input - Enterprise'!E24</f>
         <v>0</v>
       </c>
       <c r="G67" s="19" t="s">
@@ -7571,7 +7568,7 @@
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
-        <v>179</v>
+        <v>26</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="28" t="s">
@@ -7580,7 +7577,7 @@
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="28" t="s">
@@ -7589,7 +7586,7 @@
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="28" t="s">
@@ -7598,45 +7595,36 @@
     </row>
     <row r="26" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="27"/>
+        <v>29</v>
+      </c>
+      <c r="E26" s="30">
+        <v>0.5</v>
+      </c>
       <c r="F26" s="28" t="s">
-        <v>32</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="30">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="30">
-        <v>0.3</v>
+        <v>31</v>
+      </c>
+      <c r="E28" s="31">
+        <f>100%-E26-E27</f>
+        <v>0.2</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="31">
-        <f>100%-E27-E28</f>
-        <v>0.2</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
@@ -11643,14 +11631,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11849,7 +11830,14 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11862,12 +11850,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11892,9 +11877,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680F03D4-84EC-4C66-BC5D-7A7510239EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C94625C-5EE8-4C1A-9F2C-2810468C30CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="555" windowWidth="35745" windowHeight="18900" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
@@ -275,6 +275,7 @@
     <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Variable">_xlfn.LAMBDA("MA_jk45")</definedName>
     <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProduction_Variation">_xlfn.LAMBDA("VARIATION ON SOURCE: Expanded equation to account for season after calving, rather than doing the same equation twice for both seasons")</definedName>
     <definedName name="EntericMethane_PastureBeef_Equations.VEERG_3_2_1_1__4_AdditionalIntakeForMilkProductionVariation">_xlfn.LAMBDA(_xlpm.LC_jk45calv,_xlpm.LC_jk45prev,_xlpm.FA_jk45calv,_xlpm.FA_jk45after, ((_xlpm.LC_jk45calv * _xlpm.FA_jk45calv) + (_xlpm.LC_jk45prev * _xlpm.FA_jk45after)) + (1 - (_xlpm.LC_jk45calv + _xlpm.LC_jk45prev)))</definedName>
+    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
     <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
@@ -579,7 +580,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="187">
   <si>
     <t>Home</t>
   </si>
@@ -663,9 +664,6 @@
   </si>
   <si>
     <t>Liveweight grown - method 2</t>
-  </si>
-  <si>
-    <t>Manure produced</t>
   </si>
   <si>
     <t>Percent manure sold</t>
@@ -1169,10 +1167,34 @@
     <t>Input - Enterprise</t>
   </si>
   <si>
-    <t>Liveweight sold - method 1</t>
-  </si>
-  <si>
     <t>percent</t>
+  </si>
+  <si>
+    <t>Manure produced - method 1</t>
+  </si>
+  <si>
+    <t>Manure produced - method 2</t>
+  </si>
+  <si>
+    <t>Percentage of income from liveweight sold</t>
+  </si>
+  <si>
+    <t>Percentage of income from manure sold</t>
+  </si>
+  <si>
+    <t>=SUM(Table_Input_LivestockSales348[Total liveweight sold])*10^-3</t>
+  </si>
+  <si>
+    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method1))*10^-3</t>
+  </si>
+  <si>
+    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method2))*10^-3</t>
+  </si>
+  <si>
+    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method1, Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method1, '4.2.1.1-2 Methane'!M1_Table_VS_j_k_l))*10^-3</t>
+  </si>
+  <si>
+    <t>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method2, M2_Table_VS_j_k_l))*10^-3</t>
   </si>
 </sst>
 </file>
@@ -2075,9 +2097,6 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="15">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="4" borderId="0" xfId="59">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="41">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2262,6 +2281,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="52" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="69">
     <cellStyle name="Alert" xfId="59" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -5078,7 +5100,7 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E7" s="19" t="e" cm="1">
         <f t="array" ref="E7">VEERG_3_2_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
@@ -5239,7 +5261,7 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12" s="19" t="e" cm="1">
         <f t="array" ref="E12">VEERG_5_1_1_1__1_InorganicFertiliserApplicationN2OEmissions_Result_Method1</f>
@@ -5272,7 +5294,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E13" s="19" t="e" cm="1">
         <f t="array" ref="E13">VEERG_5_1_1_3__1_InorganicFertiliserApplicationCO2Emissions_Result_Method1</f>
@@ -5283,7 +5305,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H13" s="19" t="e">
         <f>E13</f>
@@ -5305,7 +5327,7 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="19" t="e" cm="1">
         <f t="array" ref="E14">VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser_Result_Method1</f>
@@ -5335,7 +5357,7 @@
       <c r="A15" s="5"/>
       <c r="C15" s="9"/>
       <c r="D15" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E15" s="19" t="e" cm="1">
         <f t="array" ref="E15">VEERG_5_3_1_1__1_LimeApplicationCO2Emissions_Result_Method1</f>
@@ -5346,7 +5368,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H15" s="19" t="e">
         <f>E15</f>
@@ -5367,7 +5389,7 @@
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E16" s="19" t="e" cm="1">
         <f t="array" ref="E16">VEERG_5_4_1_3__1_OrganicFertiliserAtmosphericDepositionN2OEmissions_Result_Method1</f>
@@ -5400,7 +5422,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E17" s="19" t="e" cm="1">
         <f t="array" ref="E17">VEERG_5_5_1_1__1_FertiliserLeachingAndRunoffN2OEmissions_result_Method1</f>
@@ -5433,7 +5455,7 @@
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E18" s="19" t="e" cm="1">
         <f t="array" ref="E18">VEERG_6_2_1_1__1__NitrousOxideEmissionsFromPastureResidues_Result_Method1</f>
@@ -5466,7 +5488,7 @@
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" s="19" t="e" cm="1">
         <f t="array" ref="E19">VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_PastureOnly_Result_Method1</f>
@@ -5499,7 +5521,7 @@
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E20" s="19" t="e" cm="1">
         <f t="array" ref="E20">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CO2</f>
@@ -5510,7 +5532,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H20" s="19" t="e">
         <f>E20</f>
@@ -5528,7 +5550,7 @@
     <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="9"/>
       <c r="D21" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E21" s="19" t="e" cm="1">
         <f t="array" ref="E21">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_CH4</f>
@@ -5558,7 +5580,7 @@
       <c r="A22" s="5"/>
       <c r="C22" s="9"/>
       <c r="D22" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="19" t="e" cm="1">
         <f t="array" ref="E22">VEERG_8_1_1_1__1_FuelCombustionTransport_Result_N2O</f>
@@ -5588,7 +5610,7 @@
       <c r="A23" s="5"/>
       <c r="C23" s="9"/>
       <c r="D23" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E23" s="19" t="e" cm="1">
         <f t="array" ref="E23">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CO2</f>
@@ -5599,7 +5621,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H23" s="19" t="e">
         <f>E23</f>
@@ -5618,7 +5640,7 @@
       <c r="A24" s="5"/>
       <c r="C24" s="9"/>
       <c r="D24" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E24" s="19" t="e" cm="1">
         <f t="array" ref="E24">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_CH4</f>
@@ -5647,7 +5669,7 @@
     <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="9"/>
       <c r="D25" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E25" s="19" t="e" cm="1">
         <f t="array" ref="E25">VEERG_8_2_1_1__1_FuelCombustionStationary_Result_N2O</f>
@@ -5676,7 +5698,7 @@
     <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="9"/>
       <c r="D26" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E26" s="19" t="e" cm="1">
         <f t="array" ref="E26">VEERG_14_1_1__1_LocationBasedScopeElectricityEmissions_Result_Method1</f>
@@ -5705,7 +5727,7 @@
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="9"/>
       <c r="D27" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E27" s="19" t="e" cm="1">
         <f t="array" ref="E27">VEERG_14_1_2__1_MarketBasedScopeElectricityEmissionsVariation_Result_Method1</f>
@@ -5788,7 +5810,7 @@
     <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="9"/>
       <c r="D32" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -5800,7 +5822,7 @@
     </row>
     <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="9"/>
-      <c r="D33" s="90" t="str" cm="1">
+      <c r="D33" s="89" t="str" cm="1">
         <f t="array" ref="D33">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 3 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
@@ -5815,7 +5837,7 @@
     <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="9"/>
       <c r="D34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -5839,7 +5861,7 @@
     <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="9"/>
       <c r="D36" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E36" s="21" t="s">
         <v>11</v>
@@ -5859,11 +5881,11 @@
         <f t="array" ref="D37:D39">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
       </c>
-      <c r="E37" s="88" t="str">
+      <c r="E37" s="87" t="str">
         <f>IF(ISBLANK($D37), "", IF(ISNUMBER(SEARCH("reporting", $D37)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>Enter value</v>
       </c>
-      <c r="F37" s="88" t="str">
+      <c r="F37" s="87" t="str">
         <f>IF(ISBLANK($D37), "", IF(ISNUMBER(SEARCH("reporting", $D37)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>Enter value</v>
       </c>
@@ -5880,11 +5902,11 @@
       <c r="D38" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
-      <c r="E38" s="88" t="e">
+      <c r="E38" s="87" t="e">
         <f>IF(ISBLANK($D38), "", IF(ISNUMBER(SEARCH("reporting", $D38)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
-      <c r="F38" s="88" t="e">
+      <c r="F38" s="87" t="e">
         <f>IF(ISBLANK($D38), "", IF(ISNUMBER(SEARCH("reporting", $D38)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>#NAME?</v>
       </c>
@@ -5901,11 +5923,11 @@
       <c r="D39" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
-      <c r="E39" s="88" t="str">
+      <c r="E39" s="87" t="str">
         <f>IF(ISBLANK($D39), "", IF(ISNUMBER(SEARCH("reporting", $D39)), Result_Enterprise_Method1, "Enter value"))</f>
         <v>Enter value</v>
       </c>
-      <c r="F39" s="88" t="str">
+      <c r="F39" s="87" t="str">
         <f>IF(ISBLANK($D39), "", IF(ISNUMBER(SEARCH("reporting", $D39)), Result_Enterprise_Method2, "Enter value"))</f>
         <v>Enter value</v>
       </c>
@@ -5920,11 +5942,11 @@
     <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="9"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="88" t="str">
+      <c r="E40" s="87" t="str">
         <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method1, "Enter value"))</f>
         <v/>
       </c>
-      <c r="F40" s="88" t="str">
+      <c r="F40" s="87" t="str">
         <f>IF(ISBLANK($D40), "", IF(ISNUMBER(SEARCH("reporting", $D40)), Result_Enterprise_Method2, "Enter value"))</f>
         <v/>
       </c>
@@ -5938,12 +5960,12 @@
     </row>
     <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="9"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="88" t="str">
+      <c r="D41" s="89"/>
+      <c r="E41" s="87" t="str">
         <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method1, "Enter value"))</f>
         <v/>
       </c>
-      <c r="F41" s="88" t="str">
+      <c r="F41" s="87" t="str">
         <f>IF(ISBLANK($D41), "", IF(ISNUMBER(SEARCH("reporting", $D41)), Result_Enterprise_Method2, "Enter value"))</f>
         <v/>
       </c>
@@ -5958,7 +5980,7 @@
     <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="9"/>
       <c r="D42" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E42" s="20" t="e">
         <f>SUM(E37:E41)</f>
@@ -5999,7 +6021,7 @@
     <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="9"/>
       <c r="D45" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -6023,10 +6045,10 @@
     <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="9"/>
       <c r="D47" s="21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -6041,11 +6063,11 @@
         <f t="array" ref="D48:D50">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
       </c>
-      <c r="E48" s="88">
+      <c r="E48" s="87">
         <v>0.6</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -6058,11 +6080,11 @@
       <c r="D49" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
-      <c r="E49" s="88">
+      <c r="E49" s="87">
         <v>0.5</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -6075,11 +6097,11 @@
       <c r="D50" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
-      <c r="E50" s="88" t="s">
-        <v>176</v>
+      <c r="E50" s="87" t="s">
+        <v>175</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -6090,9 +6112,9 @@
     <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="9"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="88"/>
+      <c r="E51" s="87"/>
       <c r="F51" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -6103,9 +6125,9 @@
     <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="88"/>
+      <c r="E52" s="87"/>
       <c r="F52" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -6116,7 +6138,7 @@
     <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="9"/>
       <c r="D53" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E53" s="20">
         <f>SUM(E48:E51)</f>
@@ -6154,7 +6176,7 @@
     <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="9"/>
       <c r="D56" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -6179,10 +6201,10 @@
       <c r="C58" s="9"/>
       <c r="D58" s="21"/>
       <c r="E58" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F58" s="21" t="s">
         <v>153</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>154</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -6192,14 +6214,14 @@
     </row>
     <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="9"/>
-      <c r="D59" s="91" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" s="89" t="e">
+      <c r="D59" s="90" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" s="88" t="e">
         <f>E42-E53</f>
         <v>#NAME?</v>
       </c>
-      <c r="F59" s="89" t="e">
+      <c r="F59" s="88" t="e">
         <f>F42-E53</f>
         <v>#NAME?</v>
       </c>
@@ -6223,25 +6245,25 @@
     <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="9"/>
       <c r="D61" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E61" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F61" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="H61" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="I61" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J61" s="21" t="s">
         <v>133</v>
-      </c>
-      <c r="G61" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="I61" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="J61" s="21" t="s">
-        <v>134</v>
       </c>
       <c r="K61" s="9"/>
     </row>
@@ -6251,15 +6273,15 @@
         <v>25</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F62" s="19">
+        <v>141</v>
+      </c>
+      <c r="F62" s="19" t="str">
         <f>'Input - Enterprise'!E22</f>
-        <v>0</v>
+        <v>=SUM(Table_Input_LivestockSales348[Total liveweight sold])*10^-3</v>
       </c>
       <c r="G62" s="19" t="e">
         <f>F62/(F62+F63)</f>
-        <v>#DIV/0!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H62" s="19" t="e">
         <f>($E$42/F62)*G62</f>
@@ -6270,25 +6292,25 @@
         <v>#NAME?</v>
       </c>
       <c r="J62" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K62" s="9"/>
     </row>
     <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="9"/>
       <c r="D63" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F63" s="19">
+        <v>142</v>
+      </c>
+      <c r="F63" s="19" t="e">
         <f>'Input - Enterprise'!E25*'Input - Enterprise'!E26</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G63" s="19" t="e">
         <f>F63/(F62+F63)</f>
-        <v>#DIV/0!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H63" s="19" t="e">
         <f>($E$42/F63)*G63</f>
@@ -6299,30 +6321,30 @@
         <v>#NAME?</v>
       </c>
       <c r="J63" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K63" s="9"/>
     </row>
     <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="9"/>
       <c r="D64" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F64" s="19" t="e">
+        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E27</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G64" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F64" s="19">
-        <f>'Input - Enterprise'!E25*'Input - Enterprise'!E27</f>
-        <v>0</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="H64" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
@@ -6341,54 +6363,54 @@
     <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="9"/>
       <c r="D66" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F66" s="19">
+        <v>144</v>
+      </c>
+      <c r="F66" s="19" t="str">
         <f>'Input - Enterprise'!E23</f>
-        <v>0</v>
+        <v>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method1, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method1))*10^-3</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H66" s="19" t="e">
         <f>E59/F66</f>
         <v>#NAME?</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J66" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K66" s="9"/>
     </row>
     <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="9"/>
       <c r="D67" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F67" s="19">
+        <v>144</v>
+      </c>
+      <c r="F67" s="19" t="str">
         <f>'Input - Enterprise'!E24</f>
-        <v>0</v>
+        <v>=SUM(Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells('Input - Pasture Beef'!X_Table_PastureBeef_Head_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_Duration_Method2, 'Input - Pasture Beef'!X_Table_PastureBeef_LiveweightGain_Method2))*10^-3</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I67" s="19" t="e">
         <f>F59/F67</f>
         <v>#NAME?</v>
       </c>
       <c r="J67" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K67" s="9"/>
     </row>
@@ -6627,25 +6649,25 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" style="34" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" style="37" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" style="37" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" style="37" customWidth="1"/>
-    <col min="6" max="11" width="28.7109375" style="37" customWidth="1"/>
-    <col min="12" max="25" width="28.7109375" style="34" customWidth="1"/>
-    <col min="26" max="27" width="9.140625" style="34"/>
-    <col min="28" max="16384" width="9.140625" style="37"/>
+    <col min="2" max="2" width="4.7109375" style="33" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" style="36" customWidth="1"/>
+    <col min="4" max="4" width="60.7109375" style="36" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" style="36" customWidth="1"/>
+    <col min="6" max="11" width="28.7109375" style="36" customWidth="1"/>
+    <col min="12" max="25" width="28.7109375" style="33" customWidth="1"/>
+    <col min="26" max="27" width="9.140625" style="33"/>
+    <col min="28" max="16384" width="9.140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="34" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="40" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="39" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6661,100 +6683,100 @@
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="N5" s="43"/>
+        <v>107</v>
+      </c>
+      <c r="N5" s="42"/>
     </row>
     <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="45"/>
+      <c r="N6" s="44"/>
     </row>
     <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
-      <c r="D7" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="57"/>
+      <c r="D7" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="56"/>
     </row>
     <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
       </c>
-      <c r="D8" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="60"/>
+      <c r="D8" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="59"/>
     </row>
     <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="28"/>
-      <c r="N9" s="47"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="27"/>
+      <c r="N9" s="46"/>
     </row>
     <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="F10" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="N10" s="47"/>
+      <c r="N10" s="46"/>
     </row>
     <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
@@ -6762,16 +6784,16 @@
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>113</v>
+      <c r="F11" s="27" t="s">
+        <v>112</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="N11" s="52"/>
+      <c r="N11" s="51"/>
     </row>
     <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
@@ -6779,13 +6801,13 @@
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>113</v>
+      <c r="F12" s="27" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6794,16 +6816,16 @@
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="46">
+        <v>48</v>
+      </c>
+      <c r="E13" s="45">
         <v>307.7</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
+      <c r="F13" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
     </row>
     <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -6811,46 +6833,46 @@
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="45">
+        <v>18</v>
+      </c>
+      <c r="F14" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="46">
-        <v>18</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
     </row>
     <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="45">
+        <v>601</v>
+      </c>
+      <c r="F15" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="46">
-        <v>601</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
     </row>
     <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="46">
+        <v>122</v>
+      </c>
+      <c r="E16" s="45">
         <v>1326</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
+      <c r="F16" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
     </row>
     <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
@@ -6858,13 +6880,13 @@
         <v>Constants - Pasture Beef</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="45">
+        <v>7</v>
+      </c>
+      <c r="F17" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="E17" s="46">
-        <v>7</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6873,13 +6895,13 @@
         <v>Constants - Livestock</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="27">
+        <v>125</v>
+      </c>
+      <c r="E18" s="26">
         <f>E15/E16</f>
         <v>0.45324283559577677</v>
       </c>
-      <c r="F18" s="28"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
@@ -6887,14 +6909,14 @@
         <v>Constants - Common</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="27" t="str">
+        <v>76</v>
+      </c>
+      <c r="E19" s="26" t="str">
         <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E15,Table_SourceData_RainfallZones[Min rainfall],Table_SourceData_RainfallZones[Max rainfall],Table_SourceData_RainfallZones[Rainfall Zone])</f>
         <v>High rainfall</v>
       </c>
-      <c r="G19" s="62"/>
-      <c r="N19" s="43"/>
+      <c r="G19" s="61"/>
+      <c r="N19" s="42"/>
     </row>
     <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
@@ -6902,38 +6924,38 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="27" t="str">
+        <v>43</v>
+      </c>
+      <c r="E20" s="26" t="str">
         <f>Common_InputFunctions.Utility_GetClimateZone(E14,E15,E17,E13,E18,Table_SourceData_ClimateZones[Min temp],Table_SourceData_ClimateZones[Max temp],Table_SourceData_ClimateZones[Min rainfall],Table_SourceData_ClimateZones[Max rainfall],Table_SourceData_ClimateZones[Min frost days],Table_SourceData_ClimateZones[Max frost days],Table_SourceData_ClimateZones[Min elevation],Table_SourceData_ClimateZones[Max elevation],Table_SourceData_ClimateZones[Min MAP:PET],Table_SourceData_ClimateZones[Max MAP:PET],Table_SourceData_ClimateZones[Climate zone])</f>
         <v>Warm temperate dry</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="61"/>
-      <c r="N20" s="45"/>
+      <c r="G20" s="60"/>
+      <c r="N20" s="44"/>
     </row>
     <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" s="27" t="str">
+        <v>126</v>
+      </c>
+      <c r="E21" s="26" t="str">
         <f>Common_InputFunctions.Utility_LookupValueInTable($E$20,Table_SourceData_WetDryZones[Climate zone],Table_SourceData_WetDryZones[Wet or Dry Zone])</f>
         <v>Dry climate zone</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="61"/>
+      <c r="G21" s="60"/>
     </row>
     <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="27" t="str">
+        <v>80</v>
+      </c>
+      <c r="E22" s="26" t="str">
         <f>Common_InputFunctions.Utility_LookupItemFromMinMax(E14,Table_SourceData_TemperatureZones[Min MAT],Table_SourceData_TemperatureZones[Max MAT],Table_SourceData_TemperatureZones[Temperature Zone])</f>
         <v>Temperate</v>
       </c>
-      <c r="G22" s="65"/>
+      <c r="G22" s="64"/>
     </row>
     <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
@@ -6943,7 +6965,7 @@
     </row>
     <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="N25" s="45"/>
+      <c r="N25" s="44"/>
     </row>
     <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
@@ -6959,234 +6981,234 @@
     </row>
     <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
-      <c r="L30" s="63"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="63"/>
-      <c r="O30" s="63"/>
-      <c r="P30" s="63"/>
-      <c r="Q30" s="63"/>
-      <c r="R30" s="63"/>
-      <c r="S30" s="63"/>
-      <c r="T30" s="63"/>
-      <c r="U30" s="63"/>
-      <c r="V30" s="63"/>
-      <c r="W30" s="63"/>
-      <c r="X30" s="63"/>
-      <c r="Y30" s="63"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="62"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="62"/>
+      <c r="V30" s="62"/>
+      <c r="W30" s="62"/>
+      <c r="X30" s="62"/>
+      <c r="Y30" s="62"/>
     </row>
     <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
-      <c r="L31" s="64"/>
-      <c r="M31" s="64"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
-      <c r="Q31" s="64"/>
-      <c r="R31" s="64"/>
-      <c r="S31" s="64"/>
-      <c r="T31" s="64"/>
-      <c r="U31" s="64"/>
-      <c r="V31" s="64"/>
-      <c r="W31" s="64"/>
-      <c r="X31" s="64"/>
-      <c r="Y31" s="64"/>
+      <c r="L31" s="63"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="63"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="63"/>
+      <c r="R31" s="63"/>
+      <c r="S31" s="63"/>
+      <c r="T31" s="63"/>
+      <c r="U31" s="63"/>
+      <c r="V31" s="63"/>
+      <c r="W31" s="63"/>
+      <c r="X31" s="63"/>
+      <c r="Y31" s="63"/>
     </row>
     <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="64"/>
-      <c r="N32" s="64"/>
-      <c r="O32" s="64"/>
-      <c r="P32" s="64"/>
-      <c r="Q32" s="64"/>
-      <c r="R32" s="64"/>
-      <c r="S32" s="64"/>
-      <c r="T32" s="64"/>
-      <c r="U32" s="64"/>
-      <c r="V32" s="64"/>
-      <c r="W32" s="64"/>
-      <c r="X32" s="64"/>
-      <c r="Y32" s="64"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
+      <c r="O32" s="63"/>
+      <c r="P32" s="63"/>
+      <c r="Q32" s="63"/>
+      <c r="R32" s="63"/>
+      <c r="S32" s="63"/>
+      <c r="T32" s="63"/>
+      <c r="U32" s="63"/>
+      <c r="V32" s="63"/>
+      <c r="W32" s="63"/>
+      <c r="X32" s="63"/>
+      <c r="Y32" s="63"/>
     </row>
     <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="64"/>
-      <c r="S33" s="64"/>
-      <c r="T33" s="64"/>
-      <c r="U33" s="64"/>
-      <c r="V33" s="64"/>
-      <c r="W33" s="64"/>
-      <c r="X33" s="64"/>
-      <c r="Y33" s="64"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="63"/>
+      <c r="P33" s="63"/>
+      <c r="Q33" s="63"/>
+      <c r="R33" s="63"/>
+      <c r="S33" s="63"/>
+      <c r="T33" s="63"/>
+      <c r="U33" s="63"/>
+      <c r="V33" s="63"/>
+      <c r="W33" s="63"/>
+      <c r="X33" s="63"/>
+      <c r="Y33" s="63"/>
     </row>
     <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
-      <c r="J34" s="66"/>
-      <c r="K34" s="67"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="64"/>
-      <c r="S34" s="64"/>
-      <c r="T34" s="64"/>
-      <c r="U34" s="64"/>
-      <c r="V34" s="64"/>
-      <c r="W34" s="64"/>
-      <c r="X34" s="64"/>
-      <c r="Y34" s="64"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="63"/>
+      <c r="O34" s="63"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="63"/>
+      <c r="S34" s="63"/>
+      <c r="T34" s="63"/>
+      <c r="U34" s="63"/>
+      <c r="V34" s="63"/>
+      <c r="W34" s="63"/>
+      <c r="X34" s="63"/>
+      <c r="Y34" s="63"/>
     </row>
     <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="67"/>
-      <c r="L35" s="64"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="64"/>
-      <c r="Q35" s="64"/>
-      <c r="R35" s="64"/>
-      <c r="S35" s="64"/>
-      <c r="T35" s="64"/>
-      <c r="U35" s="64"/>
-      <c r="V35" s="64"/>
-      <c r="W35" s="64"/>
-      <c r="X35" s="64"/>
-      <c r="Y35" s="64"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="63"/>
+      <c r="R35" s="63"/>
+      <c r="S35" s="63"/>
+      <c r="T35" s="63"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="63"/>
+      <c r="W35" s="63"/>
+      <c r="X35" s="63"/>
+      <c r="Y35" s="63"/>
     </row>
     <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="64"/>
-      <c r="N36" s="64"/>
-      <c r="O36" s="64"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="64"/>
-      <c r="R36" s="64"/>
-      <c r="S36" s="64"/>
-      <c r="T36" s="64"/>
-      <c r="U36" s="64"/>
-      <c r="V36" s="64"/>
-      <c r="W36" s="64"/>
-      <c r="X36" s="64"/>
-      <c r="Y36" s="64"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="66"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="63"/>
+      <c r="O36" s="63"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="63"/>
+      <c r="S36" s="63"/>
+      <c r="T36" s="63"/>
+      <c r="U36" s="63"/>
+      <c r="V36" s="63"/>
+      <c r="W36" s="63"/>
+      <c r="X36" s="63"/>
+      <c r="Y36" s="63"/>
     </row>
     <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="66"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="64"/>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="64"/>
-      <c r="R37" s="64"/>
-      <c r="S37" s="64"/>
-      <c r="T37" s="64"/>
-      <c r="U37" s="64"/>
-      <c r="V37" s="64"/>
-      <c r="W37" s="64"/>
-      <c r="X37" s="64"/>
-      <c r="Y37" s="64"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="66"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="63"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="63"/>
+      <c r="R37" s="63"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="63"/>
+      <c r="U37" s="63"/>
+      <c r="V37" s="63"/>
+      <c r="W37" s="63"/>
+      <c r="X37" s="63"/>
+      <c r="Y37" s="63"/>
     </row>
     <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
-      <c r="N38" s="64"/>
-      <c r="O38" s="64"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="64"/>
-      <c r="R38" s="64"/>
-      <c r="S38" s="64"/>
-      <c r="T38" s="64"/>
-      <c r="U38" s="64"/>
-      <c r="V38" s="64"/>
-      <c r="W38" s="64"/>
-      <c r="X38" s="64"/>
-      <c r="Y38" s="64"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="63"/>
+      <c r="N38" s="63"/>
+      <c r="O38" s="63"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="63"/>
+      <c r="R38" s="63"/>
+      <c r="S38" s="63"/>
+      <c r="T38" s="63"/>
+      <c r="U38" s="63"/>
+      <c r="V38" s="63"/>
+      <c r="W38" s="63"/>
+      <c r="X38" s="63"/>
+      <c r="Y38" s="63"/>
     </row>
     <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="66"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="64"/>
-      <c r="R39" s="64"/>
-      <c r="S39" s="64"/>
-      <c r="T39" s="64"/>
-      <c r="U39" s="64"/>
-      <c r="V39" s="64"/>
-      <c r="W39" s="64"/>
-      <c r="X39" s="64"/>
-      <c r="Y39" s="64"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="66"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="63"/>
+      <c r="P39" s="63"/>
+      <c r="Q39" s="63"/>
+      <c r="R39" s="63"/>
+      <c r="S39" s="63"/>
+      <c r="T39" s="63"/>
+      <c r="U39" s="63"/>
+      <c r="V39" s="63"/>
+      <c r="W39" s="63"/>
+      <c r="X39" s="63"/>
+      <c r="Y39" s="63"/>
     </row>
     <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="74"/>
-      <c r="M40" s="74"/>
-      <c r="N40" s="74"/>
-      <c r="O40" s="74"/>
-      <c r="P40" s="74"/>
-      <c r="Q40" s="74"/>
-      <c r="R40" s="74"/>
-      <c r="S40" s="74"/>
-      <c r="T40" s="74"/>
-      <c r="U40" s="74"/>
-      <c r="V40" s="74"/>
-      <c r="W40" s="74"/>
-      <c r="X40" s="74"/>
-      <c r="Y40" s="74"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="73"/>
+      <c r="M40" s="73"/>
+      <c r="N40" s="73"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="73"/>
+      <c r="Q40" s="73"/>
+      <c r="R40" s="73"/>
+      <c r="S40" s="73"/>
+      <c r="T40" s="73"/>
+      <c r="U40" s="73"/>
+      <c r="V40" s="73"/>
+      <c r="W40" s="73"/>
+      <c r="X40" s="73"/>
+      <c r="Y40" s="73"/>
     </row>
     <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
@@ -7205,117 +7227,117 @@
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="74"/>
     </row>
     <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="76"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="75"/>
     </row>
     <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="76"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="75"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="75"/>
     </row>
     <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="76"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="75"/>
     </row>
     <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="78"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="80"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="78"/>
+      <c r="H51" s="79"/>
     </row>
     <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G54" s="81"/>
+      <c r="G54" s="80"/>
     </row>
     <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="82"/>
-      <c r="F57" s="83"/>
+      <c r="D57" s="81"/>
+      <c r="F57" s="82"/>
     </row>
     <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
-      <c r="E58" s="84"/>
+      <c r="E58" s="83"/>
     </row>
     <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
-      <c r="E59" s="84"/>
+      <c r="E59" s="83"/>
     </row>
     <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
-      <c r="E60" s="85"/>
+      <c r="E60" s="84"/>
     </row>
     <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
     </row>
     <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="82"/>
+      <c r="D63" s="81"/>
     </row>
     <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
-      <c r="E64" s="84"/>
+      <c r="E64" s="83"/>
     </row>
     <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
-      <c r="E65" s="84"/>
+      <c r="E65" s="83"/>
     </row>
     <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
-      <c r="E66" s="85"/>
+      <c r="E66" s="84"/>
     </row>
     <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="86"/>
-      <c r="E69" s="86"/>
-      <c r="F69" s="86"/>
-      <c r="G69" s="86"/>
-      <c r="H69" s="86"/>
-      <c r="I69" s="86"/>
+      <c r="D69" s="85"/>
+      <c r="E69" s="85"/>
+      <c r="F69" s="85"/>
+      <c r="G69" s="85"/>
+      <c r="H69" s="85"/>
+      <c r="I69" s="85"/>
     </row>
     <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="86"/>
-      <c r="E70" s="86"/>
-      <c r="F70" s="86"/>
-      <c r="G70" s="86"/>
-      <c r="H70" s="86"/>
-      <c r="I70" s="86"/>
+      <c r="D70" s="85"/>
+      <c r="E70" s="85"/>
+      <c r="F70" s="85"/>
+      <c r="G70" s="85"/>
+      <c r="H70" s="85"/>
+      <c r="I70" s="85"/>
     </row>
     <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="86"/>
-      <c r="E71" s="86"/>
-      <c r="F71" s="86"/>
-      <c r="G71" s="86"/>
-      <c r="H71" s="86"/>
-      <c r="I71" s="86"/>
+      <c r="D71" s="85"/>
+      <c r="E71" s="85"/>
+      <c r="F71" s="85"/>
+      <c r="G71" s="85"/>
+      <c r="H71" s="85"/>
+      <c r="I71" s="85"/>
     </row>
     <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="86"/>
-      <c r="E72" s="86"/>
-      <c r="F72" s="86"/>
-      <c r="G72" s="86"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="86"/>
+      <c r="D72" s="85"/>
+      <c r="E72" s="85"/>
+      <c r="F72" s="85"/>
+      <c r="G72" s="85"/>
+      <c r="H72" s="85"/>
+      <c r="I72" s="85"/>
     </row>
     <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7323,19 +7345,19 @@
     <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D78" s="87"/>
+      <c r="D78" s="86"/>
     </row>
     <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D79" s="87"/>
+      <c r="D79" s="86"/>
     </row>
     <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D80" s="87"/>
+      <c r="D80" s="86"/>
     </row>
     <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D81" s="87"/>
+      <c r="D81" s="86"/>
     </row>
     <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D82" s="87"/>
+      <c r="D82" s="86"/>
     </row>
     <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7404,16 +7426,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="C1" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="C1" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C2" s="3"/>
@@ -7426,212 +7448,247 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
+        <v>99</v>
+      </c>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D6" s="44"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="37"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D8" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D10" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D10" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="50"/>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D12" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="25">
         <v>45292</v>
       </c>
-      <c r="F12" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" s="37"/>
+      <c r="F12" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="36"/>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="52">
         <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
         <v>45657</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="37"/>
+      <c r="F13" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="25">
         <v>45231</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <v>45747</v>
       </c>
-      <c r="F19" s="28" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="26">
         <f>DATEDIF(E18,E19+1,"m")</f>
         <v>17</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="E22" s="91" t="s">
+        <v>182</v>
+      </c>
+      <c r="G22" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E23" s="91" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="E24" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D26" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="91" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="1" t="s">
+      <c r="E27" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D27" s="1" t="s">
+      <c r="E28" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="30">
-        <v>0.3</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="31">
-        <f>100%-E26-E27</f>
+      <c r="E29" s="30">
+        <f>100%-E27-E28</f>
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D31" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="29">
         <v>0.2</v>
       </c>
-      <c r="F28" s="28" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D32" s="25"/>
+      <c r="G32" s="27" t="s">
+        <v>177</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7643,8 +7700,8 @@
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" style="34" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="34" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="33" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="33" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="48" style="1" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" style="1" customWidth="1"/>
@@ -7659,49 +7716,49 @@
     <col min="18" max="18" width="31.140625" style="1" customWidth="1"/>
     <col min="19" max="20" width="20.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="4.7109375" style="1" customWidth="1"/>
-    <col min="22" max="33" width="20.7109375" style="34" customWidth="1"/>
-    <col min="34" max="39" width="21.85546875" style="34" customWidth="1"/>
-    <col min="40" max="44" width="20.7109375" style="34" customWidth="1"/>
-    <col min="45" max="65" width="9.140625" style="34"/>
-    <col min="66" max="16384" width="9.140625" style="37"/>
+    <col min="22" max="33" width="20.7109375" style="33" customWidth="1"/>
+    <col min="34" max="39" width="21.85546875" style="33" customWidth="1"/>
+    <col min="40" max="44" width="20.7109375" style="33" customWidth="1"/>
+    <col min="45" max="65" width="9.140625" style="33"/>
+    <col min="66" max="16384" width="9.140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="e" vm="1">
+    <row r="1" spans="1:65" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>33</v>
+      <c r="C1" s="32" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
     </row>
     <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
-      <c r="BM4" s="37"/>
+      <c r="BM4" s="36"/>
     </row>
     <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
@@ -7709,138 +7766,138 @@
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
         <v>Australian states and territories</v>
       </c>
-      <c r="BM5" s="37"/>
+      <c r="BM5" s="36"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="F6" s="31" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7"/>
-      <c r="D7" s="32" t="str" cm="1">
+      <c r="D7" s="31" t="str" cm="1">
         <f t="array" ref="D7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
       </c>
-      <c r="E7" s="32" t="str" cm="1">
+      <c r="E7" s="31" t="str" cm="1">
         <f t="array" ref="E7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>New South Wales</v>
       </c>
-      <c r="F7" s="32" t="str" cm="1">
+      <c r="F7" s="31" t="str" cm="1">
         <f t="array" ref="F7">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>NSW</v>
       </c>
     </row>
     <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8"/>
-      <c r="D8" s="32" t="str" cm="1">
+      <c r="D8" s="31" t="str" cm="1">
         <f t="array" ref="D8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Australian Capital Territory</v>
       </c>
-      <c r="E8" s="32" t="str" cm="1">
+      <c r="E8" s="31" t="str" cm="1">
         <f t="array" ref="E8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>ACT</v>
       </c>
-      <c r="F8" s="32" t="str" cm="1">
+      <c r="F8" s="31" t="str" cm="1">
         <f t="array" ref="F8">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>ACT</v>
       </c>
     </row>
     <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
-      <c r="D9" s="32" t="str" cm="1">
+      <c r="D9" s="31" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
       </c>
-      <c r="E9" s="32" t="str" cm="1">
+      <c r="E9" s="31" t="str" cm="1">
         <f t="array" ref="E9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Victoria</v>
       </c>
-      <c r="F9" s="32" t="str" cm="1">
+      <c r="F9" s="31" t="str" cm="1">
         <f t="array" ref="F9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>VIC</v>
       </c>
     </row>
     <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
-      <c r="D10" s="32" t="str" cm="1">
+      <c r="D10" s="31" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
       </c>
-      <c r="E10" s="32" t="str" cm="1">
+      <c r="E10" s="31" t="str" cm="1">
         <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Queensland</v>
       </c>
-      <c r="F10" s="32" t="str" cm="1">
+      <c r="F10" s="31" t="str" cm="1">
         <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>QLD</v>
       </c>
     </row>
     <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
-      <c r="D11" s="32" t="str" cm="1">
+      <c r="D11" s="31" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
       </c>
-      <c r="E11" s="32" t="str" cm="1">
+      <c r="E11" s="31" t="str" cm="1">
         <f t="array" ref="E11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>South Australia</v>
       </c>
-      <c r="F11" s="32" t="str" cm="1">
+      <c r="F11" s="31" t="str" cm="1">
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>SA</v>
       </c>
-      <c r="BM11" s="37"/>
+      <c r="BM11" s="36"/>
     </row>
     <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
-      <c r="D12" s="32" t="str" cm="1">
+      <c r="D12" s="31" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
       </c>
-      <c r="E12" s="32" t="str" cm="1">
+      <c r="E12" s="31" t="str" cm="1">
         <f t="array" ref="E12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Western Australia</v>
       </c>
-      <c r="F12" s="32" t="str" cm="1">
+      <c r="F12" s="31" t="str" cm="1">
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>WA</v>
       </c>
-      <c r="BM12" s="37"/>
+      <c r="BM12" s="36"/>
     </row>
     <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
-      <c r="D13" s="32" t="str" cm="1">
+      <c r="D13" s="31" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
       </c>
-      <c r="E13" s="32" t="str" cm="1">
+      <c r="E13" s="31" t="str" cm="1">
         <f t="array" ref="E13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Tasmania</v>
       </c>
-      <c r="F13" s="32" t="str" cm="1">
+      <c r="F13" s="31" t="str" cm="1">
         <f t="array" ref="F13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>TAS</v>
       </c>
     </row>
     <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
-      <c r="D14" s="32" t="str" cm="1">
+      <c r="D14" s="31" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
       </c>
-      <c r="E14" s="32" t="str" cm="1">
+      <c r="E14" s="31" t="str" cm="1">
         <f t="array" ref="E14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>Northern Territory</v>
       </c>
-      <c r="F14" s="32" t="str" cm="1">
+      <c r="F14" s="31" t="str" cm="1">
         <f t="array" ref="F14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
         <v>NT</v>
       </c>
@@ -7863,83 +7920,83 @@
     </row>
     <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
-      <c r="D19" s="29" t="str" cm="1">
+      <c r="D19" s="28" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
-      <c r="D20" s="32" t="s">
-        <v>37</v>
+      <c r="D20" s="31" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
-      <c r="D21" s="32" t="str" cm="1">
+      <c r="D21" s="31" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
-      <c r="D22" s="32" t="str" cm="1">
+      <c r="D22" s="31" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="D23" s="32" t="str" cm="1">
+      <c r="D23" s="31" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="D24" s="32" t="str" cm="1">
+      <c r="D24" s="31" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="D25" s="32" t="str" cm="1">
+      <c r="D25" s="31" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
-      <c r="D26" s="32" t="str" cm="1">
+      <c r="D26" s="31" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="D27" s="32" t="str" cm="1">
+      <c r="D27" s="31" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
-      <c r="D28" s="32" t="str" cm="1">
+      <c r="D28" s="31" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
-      <c r="D29" s="32" t="str" cm="1">
+      <c r="D29" s="31" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
-      <c r="D30" s="32" t="str" cm="1">
+      <c r="D30" s="31" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
@@ -7962,91 +8019,91 @@
     </row>
     <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
-      <c r="D35" s="29" t="str" cm="1">
+      <c r="D35" s="28" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="31" t="s">
         <v>38</v>
-      </c>
-      <c r="E36" s="32" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
-      <c r="D37" s="32" t="str" cm="1">
+      <c r="D37" s="31" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CO2</v>
       </c>
-      <c r="E37" s="32" cm="1">
+      <c r="E37" s="31" cm="1">
         <f t="array" ref="E37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
-      <c r="D38" s="32" t="str" cm="1">
+      <c r="D38" s="31" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CH4</v>
       </c>
-      <c r="E38" s="32" cm="1">
+      <c r="E38" s="31" cm="1">
         <f t="array" ref="E38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="32" t="str" cm="1">
+      <c r="D39" s="31" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>N2O</v>
       </c>
-      <c r="E39" s="32" cm="1">
+      <c r="E39" s="31" cm="1">
         <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="D40" s="32" t="str" cm="1">
+      <c r="D40" s="31" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>CF4</v>
       </c>
-      <c r="E40" s="32" cm="1">
+      <c r="E40" s="31" cm="1">
         <f t="array" ref="E40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>6630</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
-      <c r="D41" s="32" t="str" cm="1">
+      <c r="D41" s="31" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>C2F6</v>
       </c>
-      <c r="E41" s="32" cm="1">
+      <c r="E41" s="31" cm="1">
         <f t="array" ref="E41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>12200</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="32" t="str" cm="1">
+      <c r="D42" s="31" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>SF6</v>
       </c>
-      <c r="E42" s="32" cm="1">
+      <c r="E42" s="31" cm="1">
         <f t="array" ref="E42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>22800</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="32" t="str" cm="1">
+      <c r="D43" s="31" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>NF3</v>
       </c>
-      <c r="E43" s="32" cm="1">
+      <c r="E43" s="31" cm="1">
         <f t="array" ref="E43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
         <v>17200</v>
       </c>
@@ -8059,178 +8116,178 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D46" s="29" t="str" cm="1">
+      <c r="D46" s="28" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D47" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E47" s="32" t="s">
+      <c r="D47" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="32" t="s">
+      <c r="G47" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="G47" s="32" t="s">
+      <c r="H47" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="H47" s="32" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="32" t="str" cm="1">
+      <c r="D48" s="31" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO2</v>
       </c>
-      <c r="E48" s="32" t="str" cm="1">
+      <c r="E48" s="31" t="str" cm="1">
         <f t="array" ref="E48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/12</v>
       </c>
-      <c r="F48" s="32" cm="1">
+      <c r="F48" s="31" cm="1">
         <f t="array" ref="F48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G48" s="32" cm="1">
+      <c r="G48" s="31" cm="1">
         <f t="array" ref="G48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="32" t="str" cm="1">
+      <c r="D49" s="31" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CH4</v>
       </c>
-      <c r="E49" s="32" t="str" cm="1">
+      <c r="E49" s="31" t="str" cm="1">
         <f t="array" ref="E49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>16/12</v>
       </c>
-      <c r="F49" s="32" cm="1">
+      <c r="F49" s="31" cm="1">
         <f t="array" ref="F49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>16</v>
       </c>
-      <c r="G49" s="32" cm="1">
+      <c r="G49" s="31" cm="1">
         <f t="array" ref="G49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H49" s="32">
+      <c r="H49" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="32" t="str" cm="1">
+      <c r="D50" s="31" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>N2O</v>
       </c>
-      <c r="E50" s="32" t="str" cm="1">
+      <c r="E50" s="31" t="str" cm="1">
         <f t="array" ref="E50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/28</v>
       </c>
-      <c r="F50" s="32" cm="1">
+      <c r="F50" s="31" cm="1">
         <f t="array" ref="F50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G50" s="32" cm="1">
+      <c r="G50" s="31" cm="1">
         <f t="array" ref="G50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.5714285714285714</v>
       </c>
     </row>
     <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="32" t="str" cm="1">
+      <c r="D51" s="31" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>Nox</v>
       </c>
-      <c r="E51" s="32" t="str" cm="1">
+      <c r="E51" s="31" t="str" cm="1">
         <f t="array" ref="E51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>46/14</v>
       </c>
-      <c r="F51" s="32" cm="1">
+      <c r="F51" s="31" cm="1">
         <f t="array" ref="F51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>46</v>
       </c>
-      <c r="G51" s="32" cm="1">
+      <c r="G51" s="31" cm="1">
         <f t="array" ref="G51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.2857142857142856</v>
       </c>
     </row>
     <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D52" s="32" t="str" cm="1">
+      <c r="D52" s="31" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO</v>
       </c>
-      <c r="E52" s="32" t="str" cm="1">
+      <c r="E52" s="31" t="str" cm="1">
         <f t="array" ref="E52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28/12</v>
       </c>
-      <c r="F52" s="32" cm="1">
+      <c r="F52" s="31" cm="1">
         <f t="array" ref="F52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>28</v>
       </c>
-      <c r="G52" s="32" cm="1">
+      <c r="G52" s="31" cm="1">
         <f t="array" ref="G52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H52" s="32">
+      <c r="H52" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>2.3333333333333335</v>
       </c>
     </row>
     <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="32" t="str" cm="1">
+      <c r="D53" s="31" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>CO2 Lime</v>
       </c>
-      <c r="E53" s="32" t="str" cm="1">
+      <c r="E53" s="31" t="str" cm="1">
         <f t="array" ref="E53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44/12</v>
       </c>
-      <c r="F53" s="32" cm="1">
+      <c r="F53" s="31" cm="1">
         <f t="array" ref="F53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>44</v>
       </c>
-      <c r="G53" s="32" cm="1">
+      <c r="G53" s="31" cm="1">
         <f t="array" ref="G53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>3.6666666666666665</v>
       </c>
     </row>
     <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="32" t="str" cm="1">
+      <c r="D54" s="31" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>NMVOC</v>
       </c>
-      <c r="E54" s="32" t="str" cm="1">
+      <c r="E54" s="31" t="str" cm="1">
         <f t="array" ref="E54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14/12</v>
       </c>
-      <c r="F54" s="32" cm="1">
+      <c r="F54" s="31" cm="1">
         <f t="array" ref="F54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>14</v>
       </c>
-      <c r="G54" s="32" cm="1">
+      <c r="G54" s="31" cm="1">
         <f t="array" ref="G54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
         <v>12</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="31">
         <f>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</f>
         <v>1.1666666666666667</v>
       </c>
@@ -8244,172 +8301,172 @@
       </c>
     </row>
     <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D58" s="29" t="str" cm="1">
+      <c r="D58" s="28" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
     <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="38" t="str" cm="1">
+      <c r="D59" s="37" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D60" s="38" t="str">
+      <c r="D60" s="37" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
     <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="38" t="str">
+      <c r="D61" s="37" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
     <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E63" s="32" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D64" s="32" t="str" cm="1">
+      <c r="D64" s="31" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
       </c>
-      <c r="E64" s="32" t="str" cm="1">
+      <c r="E64" s="31" t="str" cm="1">
         <f t="array" ref="E64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D65" s="32" t="str" cm="1">
+      <c r="D65" s="31" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
       </c>
-      <c r="E65" s="32" t="str" cm="1">
+      <c r="E65" s="31" t="str" cm="1">
         <f t="array" ref="E65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D66" s="32" t="str" cm="1">
+      <c r="D66" s="31" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
       </c>
-      <c r="E66" s="32" t="str" cm="1">
+      <c r="E66" s="31" t="str" cm="1">
         <f t="array" ref="E66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="32" t="str" cm="1">
+      <c r="D67" s="31" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
       </c>
-      <c r="E67" s="32" t="str" cm="1">
+      <c r="E67" s="31" t="str" cm="1">
         <f t="array" ref="E67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D68" s="32" t="str" cm="1">
+      <c r="D68" s="31" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
       </c>
-      <c r="E68" s="32" t="str" cm="1">
+      <c r="E68" s="31" t="str" cm="1">
         <f t="array" ref="E68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="32" t="str" cm="1">
+      <c r="D69" s="31" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
       </c>
-      <c r="E69" s="32" t="str" cm="1">
+      <c r="E69" s="31" t="str" cm="1">
         <f t="array" ref="E69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="32" t="str" cm="1">
+      <c r="D70" s="31" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
       </c>
-      <c r="E70" s="32" t="str" cm="1">
+      <c r="E70" s="31" t="str" cm="1">
         <f t="array" ref="E70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="32" t="str" cm="1">
+      <c r="D71" s="31" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
       </c>
-      <c r="E71" s="32" t="str" cm="1">
+      <c r="E71" s="31" t="str" cm="1">
         <f t="array" ref="E71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="32" t="str" cm="1">
+      <c r="D72" s="31" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist - low frost</v>
       </c>
-      <c r="E72" s="32" t="str" cm="1">
+      <c r="E72" s="31" t="str" cm="1">
         <f t="array" ref="E72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="32" t="str" cm="1">
+      <c r="D73" s="31" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry - low frost</v>
       </c>
-      <c r="E73" s="32" t="str" cm="1">
+      <c r="E73" s="31" t="str" cm="1">
         <f t="array" ref="E73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="32" t="str" cm="1">
+      <c r="D74" s="31" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist - high temp</v>
       </c>
-      <c r="E74" s="32" t="str" cm="1">
+      <c r="E74" s="31" t="str" cm="1">
         <f t="array" ref="E74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D75" s="32" t="str" cm="1">
+      <c r="D75" s="31" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry - high temp</v>
       </c>
-      <c r="E75" s="32" t="str" cm="1">
+      <c r="E75" s="31" t="str" cm="1">
         <f t="array" ref="E75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
     </row>
     <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="32" t="str" cm="1">
+      <c r="D76" s="31" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist - low frost</v>
       </c>
-      <c r="E76" s="32" t="str" cm="1">
+      <c r="E76" s="31" t="str" cm="1">
         <f t="array" ref="E76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
     </row>
     <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D77" s="32" t="str" cm="1">
+      <c r="D77" s="31" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry - low frost</v>
       </c>
-      <c r="E77" s="32" t="str" cm="1">
+      <c r="E77" s="31" t="str" cm="1">
         <f t="array" ref="E77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
@@ -8424,624 +8481,624 @@
       </c>
     </row>
     <row r="82" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D82" s="29" t="str" cm="1">
+      <c r="D82" s="28" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
     <row r="83" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D83" s="38" t="str" cm="1">
+      <c r="D83" s="37" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="84" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D84" s="38" t="str">
+      <c r="D84" s="37" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
     <row r="85" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D85" s="38" t="str">
+      <c r="D85" s="37" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
     <row r="86" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D86" s="38" t="str">
+      <c r="D86" s="37" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
     <row r="87" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D87" s="38" t="str">
+      <c r="D87" s="37" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
     <row r="88" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D89" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E89" s="32" t="s">
+      <c r="D89" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F89" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F89" s="32" t="s">
+      <c r="G89" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="G89" s="32" t="s">
+      <c r="H89" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H89" s="32" t="s">
+      <c r="I89" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I89" s="32" t="s">
+      <c r="J89" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J89" s="32" t="s">
+      <c r="K89" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="K89" s="32" t="s">
+      <c r="L89" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L89" s="32" t="s">
+      <c r="M89" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="M89" s="32" t="s">
+      <c r="N89" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="N89" s="32" t="s">
+      <c r="O89" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="O89" s="32" t="s">
+      <c r="P89" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="P89" s="32" t="s">
+      <c r="Q89" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="Q89" s="32" t="s">
+      <c r="R89" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="R89" s="32" t="s">
+      <c r="S89" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="S89" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="T89" s="32"/>
+      <c r="T89" s="31"/>
     </row>
     <row r="90" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D90" s="32" t="str" cm="1">
+      <c r="D90" s="31" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical montane</v>
       </c>
-      <c r="E90" s="32" t="str" cm="1">
+      <c r="E90" s="31" t="str" cm="1">
         <f t="array" ref="E90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F90" s="32" t="str" cm="1">
+      <c r="F90" s="31" t="str" cm="1">
         <f t="array" ref="F90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G90" s="32" t="str" cm="1">
+      <c r="G90" s="31" t="str" cm="1">
         <f t="array" ref="G90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H90" s="32" t="str" cm="1">
+      <c r="H90" s="31" t="str" cm="1">
         <f t="array" ref="H90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1000 m</v>
       </c>
-      <c r="I90" s="32" t="str" cm="1">
+      <c r="I90" s="31" t="str" cm="1">
         <f t="array" ref="I90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J90" s="32" cm="1">
+      <c r="J90" s="31" cm="1">
         <f t="array" ref="J90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K90" s="32" cm="1">
+      <c r="K90" s="31" cm="1">
         <f t="array" ref="K90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L90" s="32" cm="1">
+      <c r="L90" s="31" cm="1">
         <f t="array" ref="L90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M90" s="32" cm="1">
+      <c r="M90" s="31" cm="1">
         <f t="array" ref="M90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N90" s="32" cm="1">
+      <c r="N90" s="31" cm="1">
         <f t="array" ref="N90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O90" s="32" cm="1">
+      <c r="O90" s="31" cm="1">
         <f t="array" ref="O90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P90" s="32" cm="1">
+      <c r="P90" s="31" cm="1">
         <f t="array" ref="P90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000</v>
       </c>
-      <c r="Q90" s="32" cm="1">
+      <c r="Q90" s="31" cm="1">
         <f t="array" ref="Q90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R90" s="32" cm="1">
+      <c r="R90" s="31" cm="1">
         <f t="array" ref="R90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S90" s="32" cm="1">
+      <c r="S90" s="31" cm="1">
         <f t="array" ref="S90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T90" s="32"/>
+      <c r="T90" s="31"/>
     </row>
     <row r="91" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D91" s="32" t="str" cm="1">
+      <c r="D91" s="31" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical wet</v>
       </c>
-      <c r="E91" s="32" t="str" cm="1">
+      <c r="E91" s="31" t="str" cm="1">
         <f t="array" ref="E91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F91" s="32" t="str" cm="1">
+      <c r="F91" s="31" t="str" cm="1">
         <f t="array" ref="F91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 2000 mm</v>
       </c>
-      <c r="G91" s="32" t="str" cm="1">
+      <c r="G91" s="31" t="str" cm="1">
         <f t="array" ref="G91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H91" s="32" t="str" cm="1">
+      <c r="H91" s="31" t="str" cm="1">
         <f t="array" ref="H91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I91" s="32" t="str" cm="1">
+      <c r="I91" s="31" t="str" cm="1">
         <f t="array" ref="I91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J91" s="32" cm="1">
+      <c r="J91" s="31" cm="1">
         <f t="array" ref="J91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K91" s="32" cm="1">
+      <c r="K91" s="31" cm="1">
         <f t="array" ref="K91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L91" s="32" cm="1">
+      <c r="L91" s="31" cm="1">
         <f t="array" ref="L91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>2000.001</v>
       </c>
-      <c r="M91" s="32" cm="1">
+      <c r="M91" s="31" cm="1">
         <f t="array" ref="M91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N91" s="32" cm="1">
+      <c r="N91" s="31" cm="1">
         <f t="array" ref="N91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O91" s="32" cm="1">
+      <c r="O91" s="31" cm="1">
         <f t="array" ref="O91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P91" s="32" cm="1">
+      <c r="P91" s="31" cm="1">
         <f t="array" ref="P91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q91" s="32" cm="1">
+      <c r="Q91" s="31" cm="1">
         <f t="array" ref="Q91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R91" s="32" cm="1">
+      <c r="R91" s="31" cm="1">
         <f t="array" ref="R91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S91" s="32" cm="1">
+      <c r="S91" s="31" cm="1">
         <f t="array" ref="S91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T91" s="32"/>
+      <c r="T91" s="31"/>
     </row>
     <row r="92" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D92" s="32" t="str" cm="1">
+      <c r="D92" s="31" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical moist</v>
       </c>
-      <c r="E92" s="32" t="str" cm="1">
+      <c r="E92" s="31" t="str" cm="1">
         <f t="array" ref="E92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F92" s="32" t="str" cm="1">
+      <c r="F92" s="31" t="str" cm="1">
         <f t="array" ref="F92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1000 mm - ≤ 2000 mm</v>
       </c>
-      <c r="G92" s="32" t="str" cm="1">
+      <c r="G92" s="31" t="str" cm="1">
         <f t="array" ref="G92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H92" s="32" t="str" cm="1">
+      <c r="H92" s="31" t="str" cm="1">
         <f t="array" ref="H92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I92" s="32" t="str" cm="1">
+      <c r="I92" s="31" t="str" cm="1">
         <f t="array" ref="I92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J92" s="32" cm="1">
+      <c r="J92" s="31" cm="1">
         <f t="array" ref="J92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K92" s="32" cm="1">
+      <c r="K92" s="31" cm="1">
         <f t="array" ref="K92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L92" s="32" cm="1">
+      <c r="L92" s="31" cm="1">
         <f t="array" ref="L92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000.001</v>
       </c>
-      <c r="M92" s="32" cm="1">
+      <c r="M92" s="31" cm="1">
         <f t="array" ref="M92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>2000</v>
       </c>
-      <c r="N92" s="32" cm="1">
+      <c r="N92" s="31" cm="1">
         <f t="array" ref="N92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O92" s="32" cm="1">
+      <c r="O92" s="31" cm="1">
         <f t="array" ref="O92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P92" s="32" cm="1">
+      <c r="P92" s="31" cm="1">
         <f t="array" ref="P92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q92" s="32" cm="1">
+      <c r="Q92" s="31" cm="1">
         <f t="array" ref="Q92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R92" s="32" cm="1">
+      <c r="R92" s="31" cm="1">
         <f t="array" ref="R92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S92" s="32" cm="1">
+      <c r="S92" s="31" cm="1">
         <f t="array" ref="S92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T92" s="32"/>
+      <c r="T92" s="31"/>
     </row>
     <row r="93" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D93" s="32" t="str" cm="1">
+      <c r="D93" s="31" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Tropical dry</v>
       </c>
-      <c r="E93" s="32" t="str" cm="1">
+      <c r="E93" s="31" t="str" cm="1">
         <f t="array" ref="E93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 18 C</v>
       </c>
-      <c r="F93" s="32" t="str" cm="1">
+      <c r="F93" s="31" t="str" cm="1">
         <f t="array" ref="F93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 mm</v>
       </c>
-      <c r="G93" s="32" t="str" cm="1">
+      <c r="G93" s="31" t="str" cm="1">
         <f t="array" ref="G93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 7</v>
       </c>
-      <c r="H93" s="32" t="str" cm="1">
+      <c r="H93" s="31" t="str" cm="1">
         <f t="array" ref="H93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1000 m</v>
       </c>
-      <c r="I93" s="32" t="str" cm="1">
+      <c r="I93" s="31" t="str" cm="1">
         <f t="array" ref="I93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="J93" s="32" cm="1">
+      <c r="J93" s="31" cm="1">
         <f t="array" ref="J93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>18.001000000000001</v>
       </c>
-      <c r="K93" s="32" cm="1">
+      <c r="K93" s="31" cm="1">
         <f t="array" ref="K93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L93" s="32" cm="1">
+      <c r="L93" s="31" cm="1">
         <f t="array" ref="L93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M93" s="32" cm="1">
+      <c r="M93" s="31" cm="1">
         <f t="array" ref="M93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1000</v>
       </c>
-      <c r="N93" s="32" cm="1">
+      <c r="N93" s="31" cm="1">
         <f t="array" ref="N93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O93" s="32" cm="1">
+      <c r="O93" s="31" cm="1">
         <f t="array" ref="O93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>7</v>
       </c>
-      <c r="P93" s="32" cm="1">
+      <c r="P93" s="31" cm="1">
         <f t="array" ref="P93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q93" s="32" cm="1">
+      <c r="Q93" s="31" cm="1">
         <f t="array" ref="Q93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999.99900000000002</v>
       </c>
-      <c r="R93" s="32" cm="1">
+      <c r="R93" s="31" cm="1">
         <f t="array" ref="R93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S93" s="32" cm="1">
+      <c r="S93" s="31" cm="1">
         <f t="array" ref="S93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T93" s="32"/>
+      <c r="T93" s="31"/>
     </row>
     <row r="94" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D94" s="32" t="str" cm="1">
+      <c r="D94" s="31" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate moist</v>
       </c>
-      <c r="E94" s="32" t="str" cm="1">
+      <c r="E94" s="31" t="str" cm="1">
         <f t="array" ref="E94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 10 C</v>
       </c>
-      <c r="F94" s="32" t="str" cm="1">
+      <c r="F94" s="31" t="str" cm="1">
         <f t="array" ref="F94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G94" s="32" t="str" cm="1">
+      <c r="G94" s="31" t="str" cm="1">
         <f t="array" ref="G94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H94" s="32" t="str" cm="1">
+      <c r="H94" s="31" t="str" cm="1">
         <f t="array" ref="H94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I94" s="32" t="str" cm="1">
+      <c r="I94" s="31" t="str" cm="1">
         <f t="array" ref="I94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1</v>
       </c>
-      <c r="J94" s="32" cm="1">
+      <c r="J94" s="31" cm="1">
         <f t="array" ref="J94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="K94" s="32" cm="1">
+      <c r="K94" s="31" cm="1">
         <f t="array" ref="K94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L94" s="32" cm="1">
+      <c r="L94" s="31" cm="1">
         <f t="array" ref="L94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M94" s="32" cm="1">
+      <c r="M94" s="31" cm="1">
         <f t="array" ref="M94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N94" s="32" cm="1">
+      <c r="N94" s="31" cm="1">
         <f t="array" ref="N94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O94" s="32" cm="1">
+      <c r="O94" s="31" cm="1">
         <f t="array" ref="O94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P94" s="32" cm="1">
+      <c r="P94" s="31" cm="1">
         <f t="array" ref="P94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q94" s="32" cm="1">
+      <c r="Q94" s="31" cm="1">
         <f t="array" ref="Q94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R94" s="32" cm="1">
+      <c r="R94" s="31" cm="1">
         <f t="array" ref="R94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1.0009999999999999</v>
       </c>
-      <c r="S94" s="32" cm="1">
+      <c r="S94" s="31" cm="1">
         <f t="array" ref="S94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T94" s="32"/>
+      <c r="T94" s="31"/>
     </row>
     <row r="95" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="32" t="str" cm="1">
+      <c r="D95" s="31" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Warm temperate dry</v>
       </c>
-      <c r="E95" s="32" t="str" cm="1">
+      <c r="E95" s="31" t="str" cm="1">
         <f t="array" ref="E95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 10 C</v>
       </c>
-      <c r="F95" s="32" t="str" cm="1">
+      <c r="F95" s="31" t="str" cm="1">
         <f t="array" ref="F95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G95" s="32" t="str" cm="1">
+      <c r="G95" s="31" t="str" cm="1">
         <f t="array" ref="G95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H95" s="32" t="str" cm="1">
+      <c r="H95" s="31" t="str" cm="1">
         <f t="array" ref="H95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I95" s="32" t="str" cm="1">
+      <c r="I95" s="31" t="str" cm="1">
         <f t="array" ref="I95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1</v>
       </c>
-      <c r="J95" s="32" cm="1">
+      <c r="J95" s="31" cm="1">
         <f t="array" ref="J95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="K95" s="32" cm="1">
+      <c r="K95" s="31" cm="1">
         <f t="array" ref="K95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="L95" s="32" cm="1">
+      <c r="L95" s="31" cm="1">
         <f t="array" ref="L95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M95" s="32" cm="1">
+      <c r="M95" s="31" cm="1">
         <f t="array" ref="M95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N95" s="32" cm="1">
+      <c r="N95" s="31" cm="1">
         <f t="array" ref="N95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O95" s="32" cm="1">
+      <c r="O95" s="31" cm="1">
         <f t="array" ref="O95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P95" s="32" cm="1">
+      <c r="P95" s="31" cm="1">
         <f t="array" ref="P95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q95" s="32" cm="1">
+      <c r="Q95" s="31" cm="1">
         <f t="array" ref="Q95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R95" s="32" cm="1">
+      <c r="R95" s="31" cm="1">
         <f t="array" ref="R95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S95" s="32" cm="1">
+      <c r="S95" s="31" cm="1">
         <f t="array" ref="S95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-      <c r="T95" s="32"/>
+      <c r="T95" s="31"/>
     </row>
     <row r="96" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="32" t="str" cm="1">
+      <c r="D96" s="31" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate moist</v>
       </c>
-      <c r="E96" s="32" t="str" cm="1">
+      <c r="E96" s="31" t="str" cm="1">
         <f t="array" ref="E96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 0 C - ≤ 10 C</v>
       </c>
-      <c r="F96" s="32" t="str" cm="1">
+      <c r="F96" s="31" t="str" cm="1">
         <f t="array" ref="F96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G96" s="32" t="str" cm="1">
+      <c r="G96" s="31" t="str" cm="1">
         <f t="array" ref="G96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H96" s="32" t="str" cm="1">
+      <c r="H96" s="31" t="str" cm="1">
         <f t="array" ref="H96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I96" s="32" t="str" cm="1">
+      <c r="I96" s="31" t="str" cm="1">
         <f t="array" ref="I96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 1</v>
       </c>
-      <c r="J96" s="32" cm="1">
+      <c r="J96" s="31" cm="1">
         <f t="array" ref="J96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="K96" s="32" cm="1">
+      <c r="K96" s="31" cm="1">
         <f t="array" ref="K96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10</v>
       </c>
-      <c r="L96" s="32" cm="1">
+      <c r="L96" s="31" cm="1">
         <f t="array" ref="L96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M96" s="32" cm="1">
+      <c r="M96" s="31" cm="1">
         <f t="array" ref="M96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N96" s="32" cm="1">
+      <c r="N96" s="31" cm="1">
         <f t="array" ref="N96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O96" s="32" cm="1">
+      <c r="O96" s="31" cm="1">
         <f t="array" ref="O96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P96" s="32" cm="1">
+      <c r="P96" s="31" cm="1">
         <f t="array" ref="P96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q96" s="32" cm="1">
+      <c r="Q96" s="31" cm="1">
         <f t="array" ref="Q96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R96" s="32" cm="1">
+      <c r="R96" s="31" cm="1">
         <f t="array" ref="R96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1.0009999999999999</v>
       </c>
-      <c r="S96" s="32" cm="1">
+      <c r="S96" s="31" cm="1">
         <f t="array" ref="S96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="T96" s="32"/>
+      <c r="T96" s="31"/>
     </row>
     <row r="97" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="32" t="str" cm="1">
+      <c r="D97" s="31" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Cool temperate dry</v>
       </c>
-      <c r="E97" s="32" t="str" cm="1">
+      <c r="E97" s="31" t="str" cm="1">
         <f t="array" ref="E97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>&gt; 0 C - ≤ 10 C</v>
       </c>
-      <c r="F97" s="32" t="str" cm="1">
+      <c r="F97" s="31" t="str" cm="1">
         <f t="array" ref="F97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="G97" s="32" t="str" cm="1">
+      <c r="G97" s="31" t="str" cm="1">
         <f t="array" ref="G97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H97" s="32" t="str" cm="1">
+      <c r="H97" s="31" t="str" cm="1">
         <f t="array" ref="H97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="I97" s="32" t="str" cm="1">
+      <c r="I97" s="31" t="str" cm="1">
         <f t="array" ref="I97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>≤ 1</v>
       </c>
-      <c r="J97" s="32" cm="1">
+      <c r="J97" s="31" cm="1">
         <f t="array" ref="J97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="K97" s="32" cm="1">
+      <c r="K97" s="31" cm="1">
         <f t="array" ref="K97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>10</v>
       </c>
-      <c r="L97" s="32" cm="1">
+      <c r="L97" s="31" cm="1">
         <f t="array" ref="L97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="M97" s="32" cm="1">
+      <c r="M97" s="31" cm="1">
         <f t="array" ref="M97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="N97" s="32" cm="1">
+      <c r="N97" s="31" cm="1">
         <f t="array" ref="N97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="O97" s="32" cm="1">
+      <c r="O97" s="31" cm="1">
         <f t="array" ref="O97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="P97" s="32" cm="1">
+      <c r="P97" s="31" cm="1">
         <f t="array" ref="P97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="Q97" s="32" cm="1">
+      <c r="Q97" s="31" cm="1">
         <f t="array" ref="Q97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>999999</v>
       </c>
-      <c r="R97" s="32" cm="1">
+      <c r="R97" s="31" cm="1">
         <f t="array" ref="R97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>-999999</v>
       </c>
-      <c r="S97" s="32" cm="1">
+      <c r="S97" s="31" cm="1">
         <f t="array" ref="S97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
         <v>1</v>
       </c>
-      <c r="T97" s="32"/>
+      <c r="T97" s="31"/>
     </row>
     <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9076,82 +9133,82 @@
       </c>
     </row>
     <row r="106" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D106" s="29" t="str" cm="1">
+      <c r="D106" s="28" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
     <row r="107" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D107" s="38" t="str" cm="1">
+      <c r="D107" s="37" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
     <row r="108" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="109" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D109" s="32" t="s">
+      <c r="D109" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E109" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F109" s="32" t="s">
+      <c r="G109" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="G109" s="32" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="110" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D110" s="32" t="str" cm="1">
+      <c r="D110" s="31" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E110" s="32" t="str" cm="1">
+      <c r="E110" s="31" t="str" cm="1">
         <f t="array" ref="E110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>≥ 26 C</v>
       </c>
-      <c r="F110" s="32" cm="1">
+      <c r="F110" s="31" cm="1">
         <f t="array" ref="F110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>26</v>
       </c>
-      <c r="G110" s="32" cm="1">
+      <c r="G110" s="31" cm="1">
         <f t="array" ref="G110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>999999</v>
       </c>
     </row>
     <row r="111" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D111" s="32" t="str" cm="1">
+      <c r="D111" s="31" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E111" s="32" t="str" cm="1">
+      <c r="E111" s="31" t="str" cm="1">
         <f t="array" ref="E111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>15 - 25 C</v>
       </c>
-      <c r="F111" s="32" cm="1">
+      <c r="F111" s="31" cm="1">
         <f t="array" ref="F111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>15</v>
       </c>
-      <c r="G111" s="32" cm="1">
+      <c r="G111" s="31" cm="1">
         <f t="array" ref="G111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>25.998999999999999</v>
       </c>
     </row>
     <row r="112" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D112" s="32" t="str" cm="1">
+      <c r="D112" s="31" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E112" s="32" t="str" cm="1">
+      <c r="E112" s="31" t="str" cm="1">
         <f t="array" ref="E112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>≤ 14 C</v>
       </c>
-      <c r="F112" s="32" cm="1">
+      <c r="F112" s="31" cm="1">
         <f t="array" ref="F112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>-999999</v>
       </c>
-      <c r="G112" s="32" cm="1">
+      <c r="G112" s="31" cm="1">
         <f t="array" ref="G112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
         <v>14.999000000000001</v>
       </c>
@@ -9163,80 +9220,80 @@
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
         <v>VEERG Australian rainfall zones</v>
       </c>
-      <c r="BN115" s="34"/>
+      <c r="BN115" s="33"/>
     </row>
     <row r="116" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D116" s="29" t="str" cm="1">
+      <c r="D116" s="28" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
-      <c r="BN116" s="34"/>
+      <c r="BN116" s="33"/>
     </row>
     <row r="117" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D117" s="38" t="str" cm="1">
+      <c r="D117" s="37" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
-      <c r="BN117" s="34"/>
+      <c r="BN117" s="33"/>
     </row>
     <row r="118" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN118" s="34"/>
+      <c r="BN118" s="33"/>
     </row>
     <row r="119" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D119" s="32" t="s">
+      <c r="D119" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E119" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E119" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="F119" s="32" t="s">
+      <c r="F119" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G119" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="G119" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="BN119" s="34"/>
+      <c r="BN119" s="33"/>
     </row>
     <row r="120" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D120" s="32" t="str" cm="1">
+      <c r="D120" s="31" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>High rainfall</v>
       </c>
-      <c r="E120" s="32" t="str" cm="1">
+      <c r="E120" s="31" t="str" cm="1">
         <f t="array" ref="E120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Annual rainfall &gt; 600mm</v>
       </c>
-      <c r="F120" s="32" cm="1">
+      <c r="F120" s="31" cm="1">
         <f t="array" ref="F120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600.00099999999998</v>
       </c>
-      <c r="G120" s="32" cm="1">
+      <c r="G120" s="31" cm="1">
         <f t="array" ref="G120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>999999</v>
       </c>
-      <c r="BN120" s="34"/>
+      <c r="BN120" s="33"/>
     </row>
     <row r="121" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D121" s="32" t="str" cm="1">
+      <c r="D121" s="31" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Low rainfall</v>
       </c>
-      <c r="E121" s="32" t="str" cm="1">
+      <c r="E121" s="31" t="str" cm="1">
         <f t="array" ref="E121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>Annual rainfall ≤ 600mm</v>
       </c>
-      <c r="F121" s="32" cm="1">
+      <c r="F121" s="31" cm="1">
         <f t="array" ref="F121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>-999999</v>
       </c>
-      <c r="G121" s="32" cm="1">
+      <c r="G121" s="31" cm="1">
         <f t="array" ref="G121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
         <v>600</v>
       </c>
-      <c r="BN121" s="34"/>
+      <c r="BN121" s="33"/>
     </row>
     <row r="122" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN122" s="34"/>
+      <c r="BN122" s="33"/>
     </row>
     <row r="123" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="124" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9246,36 +9303,36 @@
       </c>
     </row>
     <row r="125" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D125" s="29" t="str" cm="1">
+      <c r="D125" s="28" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
     <row r="126" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="127" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D127" s="32" t="s">
+      <c r="D127" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E127" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="E127" s="32" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="128" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D128" s="32" t="str" cm="1">
+      <c r="D128" s="31" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching occurs</v>
       </c>
-      <c r="E128" s="32" t="str" cm="1">
+      <c r="E128" s="31" t="str" cm="1">
         <f t="array" ref="E128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
     <row r="129" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D129" s="32" t="str" cm="1">
+      <c r="D129" s="31" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Leaching does not occur</v>
       </c>
-      <c r="E129" s="32" t="str" cm="1">
+      <c r="E129" s="31" t="str" cm="1">
         <f t="array" ref="E129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
@@ -9290,7 +9347,7 @@
       <c r="E132" s="9"/>
     </row>
     <row r="133" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D133" s="29" t="str" cm="1">
+      <c r="D133" s="28" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
@@ -9298,10 +9355,10 @@
     </row>
     <row r="134" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" t="s">
+        <v>67</v>
+      </c>
+      <c r="E134" t="s">
         <v>68</v>
-      </c>
-      <c r="E134" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="135" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9319,243 +9376,243 @@
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>No - not in leaching zone</v>
       </c>
-      <c r="E136" s="32" cm="1">
+      <c r="E136" s="31" cm="1">
         <f t="array" ref="E136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="138" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN138" s="34"/>
-      <c r="BO138" s="34"/>
-      <c r="BP138" s="34"/>
-      <c r="BQ138" s="34"/>
-      <c r="BR138" s="34"/>
-      <c r="BS138" s="34"/>
-      <c r="BT138" s="34"/>
-      <c r="BU138" s="34"/>
-      <c r="BV138" s="34"/>
-      <c r="BW138" s="34"/>
-      <c r="BX138" s="34"/>
-      <c r="BY138" s="34"/>
+      <c r="BN138" s="33"/>
+      <c r="BO138" s="33"/>
+      <c r="BP138" s="33"/>
+      <c r="BQ138" s="33"/>
+      <c r="BR138" s="33"/>
+      <c r="BS138" s="33"/>
+      <c r="BT138" s="33"/>
+      <c r="BU138" s="33"/>
+      <c r="BV138" s="33"/>
+      <c r="BW138" s="33"/>
+      <c r="BX138" s="33"/>
+      <c r="BY138" s="33"/>
     </row>
     <row r="139" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
         <v>FracWET for irrigation types</v>
       </c>
-      <c r="BN139" s="34"/>
-      <c r="BO139" s="34"/>
-      <c r="BP139" s="34"/>
-      <c r="BQ139" s="34"/>
-      <c r="BR139" s="34"/>
-      <c r="BS139" s="34"/>
-      <c r="BT139" s="34"/>
-      <c r="BU139" s="34"/>
-      <c r="BV139" s="34"/>
-      <c r="BW139" s="34"/>
-      <c r="BX139" s="34"/>
-      <c r="BY139" s="34"/>
+      <c r="BN139" s="33"/>
+      <c r="BO139" s="33"/>
+      <c r="BP139" s="33"/>
+      <c r="BQ139" s="33"/>
+      <c r="BR139" s="33"/>
+      <c r="BS139" s="33"/>
+      <c r="BT139" s="33"/>
+      <c r="BU139" s="33"/>
+      <c r="BV139" s="33"/>
+      <c r="BW139" s="33"/>
+      <c r="BX139" s="33"/>
+      <c r="BY139" s="33"/>
     </row>
     <row r="140" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D140" s="29" t="str" cm="1">
+      <c r="D140" s="28" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
         <v>VEERG 2026: Chapter 1, section 1.8.2 Leaching, climate and rainfall zones</v>
       </c>
-      <c r="BN140" s="34"/>
-      <c r="BO140" s="34"/>
-      <c r="BP140" s="34"/>
-      <c r="BQ140" s="34"/>
-      <c r="BR140" s="34"/>
-      <c r="BS140" s="34"/>
-      <c r="BT140" s="34"/>
-      <c r="BU140" s="34"/>
-      <c r="BV140" s="34"/>
-      <c r="BW140" s="34"/>
-      <c r="BX140" s="34"/>
-      <c r="BY140" s="34"/>
+      <c r="BN140" s="33"/>
+      <c r="BO140" s="33"/>
+      <c r="BP140" s="33"/>
+      <c r="BQ140" s="33"/>
+      <c r="BR140" s="33"/>
+      <c r="BS140" s="33"/>
+      <c r="BT140" s="33"/>
+      <c r="BU140" s="33"/>
+      <c r="BV140" s="33"/>
+      <c r="BW140" s="33"/>
+      <c r="BX140" s="33"/>
+      <c r="BY140" s="33"/>
     </row>
     <row r="141" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D141" s="38" t="str" cm="1">
+      <c r="D141" s="37" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
-      <c r="BN141" s="34"/>
+      <c r="BN141" s="33"/>
     </row>
     <row r="142" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D142" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="E142" s="32" t="s">
+      <c r="D142" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="BN142" s="34"/>
+      <c r="E142" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="BN142" s="33"/>
     </row>
     <row r="143" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D143" s="32" t="str" cm="1">
+      <c r="D143" s="31" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="E143" s="32" cm="1">
+      <c r="E143" s="31" cm="1">
         <f t="array" ref="E143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BN143" s="34"/>
+      <c r="BN143" s="33"/>
     </row>
     <row r="144" spans="4:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Drip irrigation</v>
       </c>
-      <c r="E144" s="32" cm="1">
+      <c r="E144" s="31" cm="1">
         <f t="array" ref="E144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>0</v>
       </c>
-      <c r="BN144" s="34"/>
+      <c r="BN144" s="33"/>
     </row>
     <row r="145" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Sprinkler irrigation</v>
       </c>
-      <c r="E145" s="32" cm="1">
+      <c r="E145" s="31" cm="1">
         <f t="array" ref="E145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BN145" s="34"/>
+      <c r="BN145" s="33"/>
     </row>
     <row r="146" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Surface irrigation</v>
       </c>
-      <c r="E146" s="32" cm="1">
+      <c r="E146" s="31" cm="1">
         <f t="array" ref="E146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BN146" s="34"/>
+      <c r="BN146" s="33"/>
     </row>
     <row r="147" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>Other irrigation</v>
       </c>
-      <c r="E147" s="32" cm="1">
+      <c r="E147" s="31" cm="1">
         <f t="array" ref="E147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BN147" s="34"/>
+      <c r="BN147" s="33"/>
     </row>
     <row r="148" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN148" s="34"/>
+      <c r="BN148" s="33"/>
     </row>
     <row r="149" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN149" s="34"/>
+      <c r="BN149" s="33"/>
     </row>
     <row r="150" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
         <v>Australian data scores for scope 3</v>
       </c>
-      <c r="BN150" s="34"/>
+      <c r="BN150" s="33"/>
     </row>
     <row r="151" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D151" s="29" t="str" cm="1">
+      <c r="D151" s="28" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
         <v>VEERG 2026: XXXXXXXX</v>
       </c>
-      <c r="BN151" s="34"/>
+      <c r="BN151" s="33"/>
     </row>
     <row r="152" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN152" s="34"/>
+      <c r="BN152" s="33"/>
     </row>
     <row r="153" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D153" s="32" t="s">
+      <c r="D153" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E153" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E153" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="BC153" s="37"/>
-      <c r="BD153" s="37"/>
-      <c r="BE153" s="37"/>
-      <c r="BF153" s="37"/>
-      <c r="BG153" s="37"/>
-      <c r="BH153" s="37"/>
-      <c r="BI153" s="37"/>
-      <c r="BJ153" s="37"/>
-      <c r="BK153" s="37"/>
-      <c r="BL153" s="37"/>
-      <c r="BM153" s="37"/>
+      <c r="BC153" s="36"/>
+      <c r="BD153" s="36"/>
+      <c r="BE153" s="36"/>
+      <c r="BF153" s="36"/>
+      <c r="BG153" s="36"/>
+      <c r="BH153" s="36"/>
+      <c r="BI153" s="36"/>
+      <c r="BJ153" s="36"/>
+      <c r="BK153" s="36"/>
+      <c r="BL153" s="36"/>
+      <c r="BM153" s="36"/>
     </row>
     <row r="154" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D154" s="32" t="str" cm="1">
+      <c r="D154" s="31" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>International scope 3 database</v>
       </c>
-      <c r="E154" s="32" cm="1">
+      <c r="E154" s="31" cm="1">
         <f t="array" ref="E154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>1</v>
       </c>
-      <c r="BC154" s="37"/>
-      <c r="BD154" s="37"/>
-      <c r="BE154" s="37"/>
-      <c r="BF154" s="37"/>
-      <c r="BG154" s="37"/>
-      <c r="BH154" s="37"/>
-      <c r="BI154" s="37"/>
-      <c r="BJ154" s="37"/>
-      <c r="BK154" s="37"/>
-      <c r="BL154" s="37"/>
-      <c r="BM154" s="37"/>
+      <c r="BC154" s="36"/>
+      <c r="BD154" s="36"/>
+      <c r="BE154" s="36"/>
+      <c r="BF154" s="36"/>
+      <c r="BG154" s="36"/>
+      <c r="BH154" s="36"/>
+      <c r="BI154" s="36"/>
+      <c r="BJ154" s="36"/>
+      <c r="BK154" s="36"/>
+      <c r="BL154" s="36"/>
+      <c r="BM154" s="36"/>
     </row>
     <row r="155" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D155" s="32" t="str" cm="1">
+      <c r="D155" s="31" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Australian scope 3 database</v>
       </c>
-      <c r="E155" s="32" cm="1">
+      <c r="E155" s="31" cm="1">
         <f t="array" ref="E155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>2</v>
       </c>
-      <c r="BC155" s="37"/>
-      <c r="BD155" s="37"/>
-      <c r="BE155" s="37"/>
-      <c r="BF155" s="37"/>
-      <c r="BG155" s="37"/>
-      <c r="BH155" s="37"/>
-      <c r="BI155" s="37"/>
-      <c r="BJ155" s="37"/>
-      <c r="BK155" s="37"/>
-      <c r="BL155" s="37"/>
-      <c r="BM155" s="37"/>
+      <c r="BC155" s="36"/>
+      <c r="BD155" s="36"/>
+      <c r="BE155" s="36"/>
+      <c r="BF155" s="36"/>
+      <c r="BG155" s="36"/>
+      <c r="BH155" s="36"/>
+      <c r="BI155" s="36"/>
+      <c r="BJ155" s="36"/>
+      <c r="BK155" s="36"/>
+      <c r="BL155" s="36"/>
+      <c r="BM155" s="36"/>
     </row>
     <row r="156" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D156" s="32" t="str" cm="1">
+      <c r="D156" s="31" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>State or regional scope 3 database</v>
       </c>
-      <c r="E156" s="32" cm="1">
+      <c r="E156" s="31" cm="1">
         <f t="array" ref="E156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="157" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D157" s="32" t="str" cm="1">
+      <c r="D157" s="31" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Emissions intensity calculated from approved method</v>
       </c>
-      <c r="E157" s="32" cm="1">
+      <c r="E157" s="31" cm="1">
         <f t="array" ref="E157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="158" spans="4:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D158" s="32" t="str" cm="1">
+      <c r="D158" s="31" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>Verified credential matching ISO14067</v>
       </c>
-      <c r="E158" s="32" cm="1">
+      <c r="E158" s="31" cm="1">
         <f t="array" ref="E158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
         <v>5</v>
       </c>
@@ -9570,14 +9627,14 @@
       <c r="E161" s="9"/>
     </row>
     <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D162" s="29" t="str" cm="1">
+      <c r="D162" s="28" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
     <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D163" s="29" t="str" cm="1">
+      <c r="D163" s="28" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
@@ -9593,41 +9650,41 @@
       </c>
     </row>
     <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN165" s="34"/>
-      <c r="BO165" s="34"/>
-      <c r="BP165" s="34"/>
+      <c r="BN165" s="33"/>
+      <c r="BO165" s="33"/>
+      <c r="BP165" s="33"/>
     </row>
     <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN166" s="34"/>
-      <c r="BO166" s="34"/>
-      <c r="BP166" s="34"/>
+      <c r="BN166" s="33"/>
+      <c r="BO166" s="33"/>
+      <c r="BP166" s="33"/>
     </row>
     <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
       </c>
-      <c r="BN167" s="34"/>
-      <c r="BO167" s="34"/>
-      <c r="BP167" s="34"/>
+      <c r="BN167" s="33"/>
+      <c r="BO167" s="33"/>
+      <c r="BP167" s="33"/>
     </row>
     <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D168" s="29" t="str" cm="1">
+      <c r="D168" s="28" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
-      <c r="BN168" s="34"/>
-      <c r="BO168" s="34"/>
-      <c r="BP168" s="34"/>
+      <c r="BN168" s="33"/>
+      <c r="BO168" s="33"/>
+      <c r="BP168" s="33"/>
     </row>
     <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D169" s="29" t="str" cm="1">
+      <c r="D169" s="28" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
       </c>
-      <c r="BN169" s="34"/>
-      <c r="BO169" s="34"/>
-      <c r="BP169" s="34"/>
+      <c r="BN169" s="33"/>
+      <c r="BO169" s="33"/>
+      <c r="BP169" s="33"/>
     </row>
     <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
@@ -9637,37 +9694,37 @@
       <c r="E170" s="1">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="BN170" s="34"/>
-      <c r="BO170" s="34"/>
-      <c r="BP170" s="34"/>
+      <c r="BN170" s="33"/>
+      <c r="BO170" s="33"/>
+      <c r="BP170" s="33"/>
     </row>
     <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN171" s="34"/>
-      <c r="BO171" s="34"/>
-      <c r="BP171" s="34"/>
+      <c r="BN171" s="33"/>
+      <c r="BO171" s="33"/>
+      <c r="BP171" s="33"/>
     </row>
     <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN172" s="34"/>
-      <c r="BO172" s="34"/>
-      <c r="BP172" s="34"/>
+      <c r="BN172" s="33"/>
+      <c r="BO172" s="33"/>
+      <c r="BP172" s="33"/>
     </row>
     <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
       </c>
-      <c r="BN173" s="34"/>
-      <c r="BO173" s="34"/>
-      <c r="BP173" s="34"/>
+      <c r="BN173" s="33"/>
+      <c r="BO173" s="33"/>
+      <c r="BP173" s="33"/>
     </row>
     <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D174" s="29" t="str" cm="1">
+      <c r="D174" s="28" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
       </c>
-      <c r="BN174" s="34"/>
-      <c r="BO174" s="34"/>
-      <c r="BP174" s="34"/>
+      <c r="BN174" s="33"/>
+      <c r="BO174" s="33"/>
+      <c r="BP174" s="33"/>
     </row>
     <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
@@ -9678,37 +9735,37 @@
         <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
         <v>kg/m3</v>
       </c>
-      <c r="BN175" s="34"/>
-      <c r="BO175" s="34"/>
-      <c r="BP175" s="34"/>
+      <c r="BN175" s="33"/>
+      <c r="BO175" s="33"/>
+      <c r="BP175" s="33"/>
     </row>
     <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN176" s="34"/>
-      <c r="BO176" s="34"/>
-      <c r="BP176" s="34"/>
+      <c r="BN176" s="33"/>
+      <c r="BO176" s="33"/>
+      <c r="BP176" s="33"/>
     </row>
     <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BN177" s="34"/>
-      <c r="BO177" s="34"/>
-      <c r="BP177" s="34"/>
+      <c r="BN177" s="33"/>
+      <c r="BO177" s="33"/>
+      <c r="BP177" s="33"/>
     </row>
     <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
       </c>
-      <c r="BN178" s="34"/>
-      <c r="BO178" s="34"/>
-      <c r="BP178" s="34"/>
+      <c r="BN178" s="33"/>
+      <c r="BO178" s="33"/>
+      <c r="BP178" s="33"/>
     </row>
     <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D179" s="29" t="str" cm="1">
+      <c r="D179" s="28" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
       </c>
-      <c r="BN179" s="34"/>
-      <c r="BO179" s="34"/>
-      <c r="BP179" s="34"/>
+      <c r="BN179" s="33"/>
+      <c r="BO179" s="33"/>
+      <c r="BP179" s="33"/>
     </row>
     <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="16" t="str" cm="1">
@@ -9717,330 +9774,330 @@
       </c>
     </row>
     <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D181" s="38" t="str" cm="1">
+      <c r="D181" s="37" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D182" s="38" t="str">
+      <c r="D182" s="37" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
     <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D183" s="38" t="str">
+      <c r="D183" s="37" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
     <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D184" s="38" t="str">
+      <c r="D184" s="37" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
     <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D185" s="38" t="str">
+      <c r="D185" s="37" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
     <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D186" s="32" t="s">
+      <c r="D186" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E186" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="E186" s="32" t="s">
+      <c r="F186" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F186" s="32" t="s">
+      <c r="G186" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="G186" s="32" t="s">
+      <c r="H186" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="H186" s="32" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D187" s="32" t="str" cm="1">
+      <c r="D187" s="31" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
       </c>
-      <c r="E187" s="32" cm="1">
+      <c r="E187" s="31" cm="1">
         <f t="array" ref="E187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="F187" s="32" t="str" cm="1">
+      <c r="F187" s="31" t="str" cm="1">
         <f t="array" ref="F187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G187" s="32" t="str" cm="1">
+      <c r="G187" s="31" t="str" cm="1">
         <f t="array" ref="G187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H187" s="32" t="str" cm="1">
+      <c r="H187" s="31" t="str" cm="1">
         <f t="array" ref="H187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D188" s="32" t="str" cm="1">
+      <c r="D188" s="31" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
       </c>
-      <c r="E188" s="32" cm="1">
+      <c r="E188" s="31" cm="1">
         <f t="array" ref="E188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F188" s="32" t="str" cm="1">
+      <c r="F188" s="31" t="str" cm="1">
         <f t="array" ref="F188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G188" s="32" t="str" cm="1">
+      <c r="G188" s="31" t="str" cm="1">
         <f t="array" ref="G188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H188" s="32" t="str" cm="1">
+      <c r="H188" s="31" t="str" cm="1">
         <f t="array" ref="H188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D189" s="32" t="str" cm="1">
+      <c r="D189" s="31" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
       </c>
-      <c r="E189" s="32" cm="1">
+      <c r="E189" s="31" cm="1">
         <f t="array" ref="E189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F189" s="32" t="str" cm="1">
+      <c r="F189" s="31" t="str" cm="1">
         <f t="array" ref="F189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G189" s="32" t="str" cm="1">
+      <c r="G189" s="31" t="str" cm="1">
         <f t="array" ref="G189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H189" s="32" t="str" cm="1">
+      <c r="H189" s="31" t="str" cm="1">
         <f t="array" ref="H189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Low rainfall</v>
       </c>
     </row>
     <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D190" s="32" t="str" cm="1">
+      <c r="D190" s="31" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
       </c>
-      <c r="E190" s="32" cm="1">
+      <c r="E190" s="31" cm="1">
         <f t="array" ref="E190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F190" s="32" t="str" cm="1">
+      <c r="F190" s="31" t="str" cm="1">
         <f t="array" ref="F190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Pasture</v>
       </c>
-      <c r="G190" s="32" t="str" cm="1">
+      <c r="G190" s="31" t="str" cm="1">
         <f t="array" ref="G190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H190" s="32" t="str" cm="1">
+      <c r="H190" s="31" t="str" cm="1">
         <f t="array" ref="H190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>High rainfall</v>
       </c>
     </row>
     <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D191" s="32" t="str" cm="1">
+      <c r="D191" s="31" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
       </c>
-      <c r="E191" s="32" cm="1">
+      <c r="E191" s="31" cm="1">
         <f t="array" ref="E191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>2.8999999999999998E-3</v>
       </c>
-      <c r="F191" s="32" t="str" cm="1">
+      <c r="F191" s="31" t="str" cm="1">
         <f t="array" ref="F191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G191" s="32" t="str" cm="1">
+      <c r="G191" s="31" t="str" cm="1">
         <f t="array" ref="G191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H191" s="32" t="str" cm="1">
+      <c r="H191" s="31" t="str" cm="1">
         <f t="array" ref="H191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Low rainfall</v>
       </c>
     </row>
     <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D192" s="32" t="str" cm="1">
+      <c r="D192" s="31" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
       </c>
-      <c r="E192" s="32" cm="1">
+      <c r="E192" s="31" cm="1">
         <f t="array" ref="E192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F192" s="32" t="str" cm="1">
+      <c r="F192" s="31" t="str" cm="1">
         <f t="array" ref="F192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Crop</v>
       </c>
-      <c r="G192" s="32" t="str" cm="1">
+      <c r="G192" s="31" t="str" cm="1">
         <f t="array" ref="G192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Not irrigated</v>
       </c>
-      <c r="H192" s="32" t="str" cm="1">
+      <c r="H192" s="31" t="str" cm="1">
         <f t="array" ref="H192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>High rainfall</v>
       </c>
     </row>
     <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D193" s="32" t="str" cm="1">
+      <c r="D193" s="31" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
       </c>
-      <c r="E193" s="32" cm="1">
+      <c r="E193" s="31" cm="1">
         <f t="array" ref="E193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="F193" s="32" t="str" cm="1">
+      <c r="F193" s="31" t="str" cm="1">
         <f t="array" ref="F193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
       </c>
-      <c r="G193" s="32" t="str" cm="1">
+      <c r="G193" s="31" t="str" cm="1">
         <f t="array" ref="G193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H193" s="32" t="str" cm="1">
+      <c r="H193" s="31" t="str" cm="1">
         <f t="array" ref="H193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D194" s="32" t="str" cm="1">
+      <c r="D194" s="31" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
       </c>
-      <c r="E194" s="32" cm="1">
+      <c r="E194" s="31" cm="1">
         <f t="array" ref="E194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.3E-3</v>
       </c>
-      <c r="F194" s="32" t="str" cm="1">
+      <c r="F194" s="31" t="str" cm="1">
         <f t="array" ref="F194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
       </c>
-      <c r="G194" s="32" t="str" cm="1">
+      <c r="G194" s="31" t="str" cm="1">
         <f t="array" ref="G194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H194" s="32" t="str" cm="1">
+      <c r="H194" s="31" t="str" cm="1">
         <f t="array" ref="H194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D195" s="32" t="str" cm="1">
+      <c r="D195" s="31" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
       </c>
-      <c r="E195" s="32" cm="1">
+      <c r="E195" s="31" cm="1">
         <f t="array" ref="E195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="F195" s="32" t="str" cm="1">
+      <c r="F195" s="31" t="str" cm="1">
         <f t="array" ref="F195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
       </c>
-      <c r="G195" s="32" t="str" cm="1">
+      <c r="G195" s="31" t="str" cm="1">
         <f t="array" ref="G195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H195" s="32" t="str" cm="1">
+      <c r="H195" s="31" t="str" cm="1">
         <f t="array" ref="H195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D196" s="32" t="str" cm="1">
+      <c r="D196" s="31" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
       </c>
-      <c r="E196" s="32" cm="1">
+      <c r="E196" s="31" cm="1">
         <f t="array" ref="E196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F196" s="32" t="str" cm="1">
+      <c r="F196" s="31" t="str" cm="1">
         <f t="array" ref="F196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice</v>
       </c>
-      <c r="G196" s="32" t="str" cm="1">
+      <c r="G196" s="31" t="str" cm="1">
         <f t="array" ref="G196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Continuous flooding</v>
       </c>
-      <c r="H196" s="32" t="str" cm="1">
+      <c r="H196" s="31" t="str" cm="1">
         <f t="array" ref="H196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="197" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D197" s="32" t="str" cm="1">
+      <c r="D197" s="31" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
       </c>
-      <c r="E197" s="32" cm="1">
+      <c r="E197" s="31" cm="1">
         <f t="array" ref="E197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F197" s="32" t="str" cm="1">
+      <c r="F197" s="31" t="str" cm="1">
         <f t="array" ref="F197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice</v>
       </c>
-      <c r="G197" s="32" t="str" cm="1">
+      <c r="G197" s="31" t="str" cm="1">
         <f t="array" ref="G197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Single and multiple drainage, or alternate wetting and drying</v>
       </c>
-      <c r="H197" s="32" t="str" cm="1">
+      <c r="H197" s="31" t="str" cm="1">
         <f t="array" ref="H197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="198" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D198" s="32" t="str" cm="1">
+      <c r="D198" s="31" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
       </c>
-      <c r="E198" s="32" cm="1">
+      <c r="E198" s="31" cm="1">
         <f t="array" ref="E198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F198" s="32" t="str" cm="1">
+      <c r="F198" s="31" t="str" cm="1">
         <f t="array" ref="F198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
       </c>
-      <c r="G198" s="32" t="str" cm="1">
+      <c r="G198" s="31" t="str" cm="1">
         <f t="array" ref="G198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H198" s="32" t="str" cm="1">
+      <c r="H198" s="31" t="str" cm="1">
         <f t="array" ref="H198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
     </row>
     <row r="199" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D199" s="32" t="str" cm="1">
+      <c r="D199" s="31" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
       </c>
-      <c r="E199" s="32" cm="1">
+      <c r="E199" s="31" cm="1">
         <f t="array" ref="E199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>1.8E-3</v>
       </c>
-      <c r="F199" s="32" t="str" cm="1">
+      <c r="F199" s="31" t="str" cm="1">
         <f t="array" ref="F199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
       </c>
-      <c r="G199" s="32" t="str" cm="1">
+      <c r="G199" s="31" t="str" cm="1">
         <f t="array" ref="G199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
-      <c r="H199" s="32" t="str" cm="1">
+      <c r="H199" s="31" t="str" cm="1">
         <f t="array" ref="H199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Any</v>
       </c>
@@ -10052,13 +10109,13 @@
       </c>
     </row>
     <row r="203" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D203" s="29" t="str" cm="1">
+      <c r="D203" s="28" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
     <row r="204" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D204" s="38" t="str" cm="1">
+      <c r="D204" s="37" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
@@ -10070,19 +10127,19 @@
       </c>
     </row>
     <row r="206" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D206" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E206" s="32" t="s">
-        <v>78</v>
+      <c r="D206" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E206" s="31" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D207" s="32" t="str" cm="1">
+      <c r="D207" s="31" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E207" s="32" cm="1">
+      <c r="E207" s="31" cm="1">
         <f t="array" ref="E207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -10092,7 +10149,7 @@
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
-      <c r="E208" s="32" cm="1">
+      <c r="E208" s="31" cm="1">
         <f t="array" ref="E208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>2E-3</v>
       </c>
@@ -10104,19 +10161,19 @@
       </c>
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D212" s="32" t="s">
+      <c r="D212" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E212" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="E212" s="32" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D213" s="32" t="str" cm="1">
+      <c r="D213" s="31" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
       </c>
-      <c r="E213" s="32" t="str" cm="1">
+      <c r="E213" s="31" t="str" cm="1">
         <f t="array" ref="E213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -10126,7 +10183,7 @@
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
       </c>
-      <c r="E214" s="32" t="str" cm="1">
+      <c r="E214" s="31" t="str" cm="1">
         <f t="array" ref="E214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -10136,7 +10193,7 @@
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
       </c>
-      <c r="E215" s="32" t="str" cm="1">
+      <c r="E215" s="31" t="str" cm="1">
         <f t="array" ref="E215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -10146,7 +10203,7 @@
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
       </c>
-      <c r="E216" s="32" t="str" cm="1">
+      <c r="E216" s="31" t="str" cm="1">
         <f t="array" ref="E216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -10156,7 +10213,7 @@
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
       </c>
-      <c r="E217" s="32" t="str" cm="1">
+      <c r="E217" s="31" t="str" cm="1">
         <f t="array" ref="E217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Autumn</v>
       </c>
@@ -10166,7 +10223,7 @@
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
       </c>
-      <c r="E218" s="32" t="str" cm="1">
+      <c r="E218" s="31" t="str" cm="1">
         <f t="array" ref="E218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -10176,7 +10233,7 @@
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
       </c>
-      <c r="E219" s="32" t="str" cm="1">
+      <c r="E219" s="31" t="str" cm="1">
         <f t="array" ref="E219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -10186,7 +10243,7 @@
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
       </c>
-      <c r="E220" s="32" t="str" cm="1">
+      <c r="E220" s="31" t="str" cm="1">
         <f t="array" ref="E220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Winter</v>
       </c>
@@ -10196,7 +10253,7 @@
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
       </c>
-      <c r="E221" s="32" t="str" cm="1">
+      <c r="E221" s="31" t="str" cm="1">
         <f t="array" ref="E221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -10206,7 +10263,7 @@
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
       </c>
-      <c r="E222" s="32" t="str" cm="1">
+      <c r="E222" s="31" t="str" cm="1">
         <f t="array" ref="E222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -10216,7 +10273,7 @@
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
       </c>
-      <c r="E223" s="32" t="str" cm="1">
+      <c r="E223" s="31" t="str" cm="1">
         <f t="array" ref="E223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Spring</v>
       </c>
@@ -10226,7 +10283,7 @@
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
       </c>
-      <c r="E224" s="32" t="str" cm="1">
+      <c r="E224" s="31" t="str" cm="1">
         <f t="array" ref="E224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>Summer</v>
       </c>
@@ -10238,129 +10295,129 @@
       </c>
     </row>
     <row r="228" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D228" s="29" t="str" cm="1">
+      <c r="D228" s="28" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
     <row r="229" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D229" s="38" t="str" cm="1">
+      <c r="D229" s="37" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
     <row r="231" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D231" s="32" t="s">
+      <c r="D231" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E231" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="E231" s="32" t="s">
+      <c r="F231" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="F231" s="39" t="s">
+      <c r="G231" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="G231" s="32" t="s">
+      <c r="H231" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="H231" s="32" t="s">
+      <c r="I231" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="I231" s="32" t="s">
+      <c r="J231" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="J231" s="32" t="s">
+      <c r="K231" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="K231" s="32" t="s">
+      <c r="L231" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="L231" s="32" t="s">
+      <c r="M231" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="M231" s="32" t="s">
+      <c r="N231" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="N231" s="32" t="s">
+      <c r="O231" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="O231" s="32" t="s">
+      <c r="P231" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="P231" s="32" t="s">
+      <c r="Q231" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="Q231" s="32" t="s">
+      <c r="R231" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="R231" s="32" t="s">
+      <c r="S231" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="S231" s="32" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D232" s="32" t="str" cm="1">
+      <c r="D232" s="31" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E232" s="32" t="str" cm="1">
+      <c r="E232" s="31" t="str" cm="1">
         <f t="array" ref="E232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≤10</v>
       </c>
-      <c r="F232" s="32" cm="1">
+      <c r="F232" s="31" cm="1">
         <f t="array" ref="F232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.66</v>
       </c>
-      <c r="G232" s="32" cm="1">
+      <c r="G232" s="31" cm="1">
         <f t="array" ref="G232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H232" s="32" cm="1">
+      <c r="H232" s="31" cm="1">
         <f t="array" ref="H232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="I232" s="32" cm="1">
+      <c r="I232" s="31" cm="1">
         <f t="array" ref="I232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J232" s="32" cm="1">
+      <c r="J232" s="31" cm="1">
         <f t="array" ref="J232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K232" s="32" cm="1">
+      <c r="K232" s="31" cm="1">
         <f t="array" ref="K232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L232" s="32" cm="1">
+      <c r="L232" s="31" cm="1">
         <f t="array" ref="L232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M232" s="32" cm="1">
+      <c r="M232" s="31" cm="1">
         <f t="array" ref="M232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N232" s="32" cm="1">
+      <c r="N232" s="31" cm="1">
         <f t="array" ref="N232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O232" s="32" cm="1">
+      <c r="O232" s="31" cm="1">
         <f t="array" ref="O232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P232" s="32" cm="1">
+      <c r="P232" s="31" cm="1">
         <f t="array" ref="P232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q232" s="32" cm="1">
+      <c r="Q232" s="31" cm="1">
         <f t="array" ref="Q232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R232" s="32" cm="1">
+      <c r="R232" s="31" cm="1">
         <f t="array" ref="R232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S232" s="32" cm="1">
+      <c r="S232" s="31" cm="1">
         <f t="array" ref="S232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>10</v>
       </c>
@@ -10370,63 +10427,63 @@
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E233" s="32" cm="1">
+      <c r="E233" s="31" cm="1">
         <f t="array" ref="E233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
-      <c r="F233" s="32" cm="1">
+      <c r="F233" s="31" cm="1">
         <f t="array" ref="F233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.68</v>
       </c>
-      <c r="G233" s="32" cm="1">
+      <c r="G233" s="31" cm="1">
         <f t="array" ref="G233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H233" s="32" cm="1">
+      <c r="H233" s="31" cm="1">
         <f t="array" ref="H233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.11</v>
       </c>
-      <c r="I233" s="32" cm="1">
+      <c r="I233" s="31" cm="1">
         <f t="array" ref="I233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J233" s="32" cm="1">
+      <c r="J233" s="31" cm="1">
         <f t="array" ref="J233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K233" s="32" cm="1">
+      <c r="K233" s="31" cm="1">
         <f t="array" ref="K233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L233" s="32" cm="1">
+      <c r="L233" s="31" cm="1">
         <f t="array" ref="L233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M233" s="32" cm="1">
+      <c r="M233" s="31" cm="1">
         <f t="array" ref="M233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N233" s="32" cm="1">
+      <c r="N233" s="31" cm="1">
         <f t="array" ref="N233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O233" s="32" cm="1">
+      <c r="O233" s="31" cm="1">
         <f t="array" ref="O233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P233" s="32" cm="1">
+      <c r="P233" s="31" cm="1">
         <f t="array" ref="P233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q233" s="32" cm="1">
+      <c r="Q233" s="31" cm="1">
         <f t="array" ref="Q233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R233" s="32" cm="1">
+      <c r="R233" s="31" cm="1">
         <f t="array" ref="R233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S233" s="32" cm="1">
+      <c r="S233" s="31" cm="1">
         <f t="array" ref="S233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>11</v>
       </c>
@@ -10436,63 +10493,63 @@
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E234" s="32" cm="1">
+      <c r="E234" s="31" cm="1">
         <f t="array" ref="E234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
-      <c r="F234" s="32" cm="1">
+      <c r="F234" s="31" cm="1">
         <f t="array" ref="F234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.7</v>
       </c>
-      <c r="G234" s="32" cm="1">
+      <c r="G234" s="31" cm="1">
         <f t="array" ref="G234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H234" s="32" cm="1">
+      <c r="H234" s="31" cm="1">
         <f t="array" ref="H234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.13</v>
       </c>
-      <c r="I234" s="32" cm="1">
+      <c r="I234" s="31" cm="1">
         <f t="array" ref="I234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J234" s="32" cm="1">
+      <c r="J234" s="31" cm="1">
         <f t="array" ref="J234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K234" s="32" cm="1">
+      <c r="K234" s="31" cm="1">
         <f t="array" ref="K234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L234" s="32" cm="1">
+      <c r="L234" s="31" cm="1">
         <f t="array" ref="L234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M234" s="32" cm="1">
+      <c r="M234" s="31" cm="1">
         <f t="array" ref="M234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N234" s="32" cm="1">
+      <c r="N234" s="31" cm="1">
         <f t="array" ref="N234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O234" s="32" cm="1">
+      <c r="O234" s="31" cm="1">
         <f t="array" ref="O234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P234" s="32" cm="1">
+      <c r="P234" s="31" cm="1">
         <f t="array" ref="P234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q234" s="32" cm="1">
+      <c r="Q234" s="31" cm="1">
         <f t="array" ref="Q234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R234" s="32" cm="1">
+      <c r="R234" s="31" cm="1">
         <f t="array" ref="R234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S234" s="32" cm="1">
+      <c r="S234" s="31" cm="1">
         <f t="array" ref="S234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>12</v>
       </c>
@@ -10502,63 +10559,63 @@
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E235" s="32" cm="1">
+      <c r="E235" s="31" cm="1">
         <f t="array" ref="E235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
-      <c r="F235" s="32" cm="1">
+      <c r="F235" s="31" cm="1">
         <f t="array" ref="F235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.71</v>
       </c>
-      <c r="G235" s="32" cm="1">
+      <c r="G235" s="31" cm="1">
         <f t="array" ref="G235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H235" s="32" cm="1">
+      <c r="H235" s="31" cm="1">
         <f t="array" ref="H235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="I235" s="32" cm="1">
+      <c r="I235" s="31" cm="1">
         <f t="array" ref="I235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J235" s="32" cm="1">
+      <c r="J235" s="31" cm="1">
         <f t="array" ref="J235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K235" s="32" cm="1">
+      <c r="K235" s="31" cm="1">
         <f t="array" ref="K235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L235" s="32" cm="1">
+      <c r="L235" s="31" cm="1">
         <f t="array" ref="L235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M235" s="32" cm="1">
+      <c r="M235" s="31" cm="1">
         <f t="array" ref="M235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N235" s="32" cm="1">
+      <c r="N235" s="31" cm="1">
         <f t="array" ref="N235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O235" s="32" cm="1">
+      <c r="O235" s="31" cm="1">
         <f t="array" ref="O235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P235" s="32" cm="1">
+      <c r="P235" s="31" cm="1">
         <f t="array" ref="P235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q235" s="32" cm="1">
+      <c r="Q235" s="31" cm="1">
         <f t="array" ref="Q235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R235" s="32" cm="1">
+      <c r="R235" s="31" cm="1">
         <f t="array" ref="R235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S235" s="32" cm="1">
+      <c r="S235" s="31" cm="1">
         <f t="array" ref="S235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>13</v>
       </c>
@@ -10568,63 +10625,63 @@
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
       </c>
-      <c r="E236" s="32" cm="1">
+      <c r="E236" s="31" cm="1">
         <f t="array" ref="E236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
-      <c r="F236" s="32" cm="1">
+      <c r="F236" s="31" cm="1">
         <f t="array" ref="F236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.73</v>
       </c>
-      <c r="G236" s="32" cm="1">
+      <c r="G236" s="31" cm="1">
         <f t="array" ref="G236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H236" s="32" cm="1">
+      <c r="H236" s="31" cm="1">
         <f t="array" ref="H236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.15</v>
       </c>
-      <c r="I236" s="32" cm="1">
+      <c r="I236" s="31" cm="1">
         <f t="array" ref="I236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1E-3</v>
       </c>
-      <c r="J236" s="32" cm="1">
+      <c r="J236" s="31" cm="1">
         <f t="array" ref="J236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K236" s="32" cm="1">
+      <c r="K236" s="31" cm="1">
         <f t="array" ref="K236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L236" s="32" cm="1">
+      <c r="L236" s="31" cm="1">
         <f t="array" ref="L236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M236" s="32" cm="1">
+      <c r="M236" s="31" cm="1">
         <f t="array" ref="M236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N236" s="32" cm="1">
+      <c r="N236" s="31" cm="1">
         <f t="array" ref="N236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O236" s="32" cm="1">
+      <c r="O236" s="31" cm="1">
         <f t="array" ref="O236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P236" s="32" cm="1">
+      <c r="P236" s="31" cm="1">
         <f t="array" ref="P236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q236" s="32" cm="1">
+      <c r="Q236" s="31" cm="1">
         <f t="array" ref="Q236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R236" s="32" cm="1">
+      <c r="R236" s="31" cm="1">
         <f t="array" ref="R236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S236" s="32" cm="1">
+      <c r="S236" s="31" cm="1">
         <f t="array" ref="S236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>14</v>
       </c>
@@ -10634,63 +10691,63 @@
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E237" s="32" cm="1">
+      <c r="E237" s="31" cm="1">
         <f t="array" ref="E237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
-      <c r="F237" s="32" cm="1">
+      <c r="F237" s="31" cm="1">
         <f t="array" ref="F237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.74</v>
       </c>
-      <c r="G237" s="32" cm="1">
+      <c r="G237" s="31" cm="1">
         <f t="array" ref="G237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H237" s="32" cm="1">
+      <c r="H237" s="31" cm="1">
         <f t="array" ref="H237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.17</v>
       </c>
-      <c r="I237" s="32" cm="1">
+      <c r="I237" s="31" cm="1">
         <f t="array" ref="I237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J237" s="32" cm="1">
+      <c r="J237" s="31" cm="1">
         <f t="array" ref="J237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K237" s="32" cm="1">
+      <c r="K237" s="31" cm="1">
         <f t="array" ref="K237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L237" s="32" cm="1">
+      <c r="L237" s="31" cm="1">
         <f t="array" ref="L237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M237" s="32" cm="1">
+      <c r="M237" s="31" cm="1">
         <f t="array" ref="M237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N237" s="32" cm="1">
+      <c r="N237" s="31" cm="1">
         <f t="array" ref="N237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O237" s="32" cm="1">
+      <c r="O237" s="31" cm="1">
         <f t="array" ref="O237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P237" s="32" cm="1">
+      <c r="P237" s="31" cm="1">
         <f t="array" ref="P237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q237" s="32" cm="1">
+      <c r="Q237" s="31" cm="1">
         <f t="array" ref="Q237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R237" s="32" cm="1">
+      <c r="R237" s="31" cm="1">
         <f t="array" ref="R237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S237" s="32" cm="1">
+      <c r="S237" s="31" cm="1">
         <f t="array" ref="S237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>15</v>
       </c>
@@ -10700,63 +10757,63 @@
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E238" s="32" cm="1">
+      <c r="E238" s="31" cm="1">
         <f t="array" ref="E238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
-      <c r="F238" s="32" cm="1">
+      <c r="F238" s="31" cm="1">
         <f t="array" ref="F238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.75</v>
       </c>
-      <c r="G238" s="32" cm="1">
+      <c r="G238" s="31" cm="1">
         <f t="array" ref="G238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H238" s="32" cm="1">
+      <c r="H238" s="31" cm="1">
         <f t="array" ref="H238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.18</v>
       </c>
-      <c r="I238" s="32" cm="1">
+      <c r="I238" s="31" cm="1">
         <f t="array" ref="I238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J238" s="32" cm="1">
+      <c r="J238" s="31" cm="1">
         <f t="array" ref="J238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K238" s="32" cm="1">
+      <c r="K238" s="31" cm="1">
         <f t="array" ref="K238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L238" s="32" cm="1">
+      <c r="L238" s="31" cm="1">
         <f t="array" ref="L238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M238" s="32" cm="1">
+      <c r="M238" s="31" cm="1">
         <f t="array" ref="M238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N238" s="32" cm="1">
+      <c r="N238" s="31" cm="1">
         <f t="array" ref="N238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O238" s="32" cm="1">
+      <c r="O238" s="31" cm="1">
         <f t="array" ref="O238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P238" s="32" cm="1">
+      <c r="P238" s="31" cm="1">
         <f t="array" ref="P238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q238" s="32" cm="1">
+      <c r="Q238" s="31" cm="1">
         <f t="array" ref="Q238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R238" s="32" cm="1">
+      <c r="R238" s="31" cm="1">
         <f t="array" ref="R238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S238" s="32" cm="1">
+      <c r="S238" s="31" cm="1">
         <f t="array" ref="S238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>16</v>
       </c>
@@ -10766,63 +10823,63 @@
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E239" s="32" cm="1">
+      <c r="E239" s="31" cm="1">
         <f t="array" ref="E239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
-      <c r="F239" s="32" cm="1">
+      <c r="F239" s="31" cm="1">
         <f t="array" ref="F239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.76</v>
       </c>
-      <c r="G239" s="32" cm="1">
+      <c r="G239" s="31" cm="1">
         <f t="array" ref="G239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H239" s="32" cm="1">
+      <c r="H239" s="31" cm="1">
         <f t="array" ref="H239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.2</v>
       </c>
-      <c r="I239" s="32" cm="1">
+      <c r="I239" s="31" cm="1">
         <f t="array" ref="I239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J239" s="32" cm="1">
+      <c r="J239" s="31" cm="1">
         <f t="array" ref="J239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K239" s="32" cm="1">
+      <c r="K239" s="31" cm="1">
         <f t="array" ref="K239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L239" s="32" cm="1">
+      <c r="L239" s="31" cm="1">
         <f t="array" ref="L239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M239" s="32" cm="1">
+      <c r="M239" s="31" cm="1">
         <f t="array" ref="M239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N239" s="32" cm="1">
+      <c r="N239" s="31" cm="1">
         <f t="array" ref="N239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O239" s="32" cm="1">
+      <c r="O239" s="31" cm="1">
         <f t="array" ref="O239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P239" s="32" cm="1">
+      <c r="P239" s="31" cm="1">
         <f t="array" ref="P239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q239" s="32" cm="1">
+      <c r="Q239" s="31" cm="1">
         <f t="array" ref="Q239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R239" s="32" cm="1">
+      <c r="R239" s="31" cm="1">
         <f t="array" ref="R239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S239" s="32" cm="1">
+      <c r="S239" s="31" cm="1">
         <f t="array" ref="S239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>17</v>
       </c>
@@ -10832,63 +10889,63 @@
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E240" s="32" cm="1">
+      <c r="E240" s="31" cm="1">
         <f t="array" ref="E240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
-      <c r="F240" s="32" cm="1">
+      <c r="F240" s="31" cm="1">
         <f t="array" ref="F240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.77</v>
       </c>
-      <c r="G240" s="32" cm="1">
+      <c r="G240" s="31" cm="1">
         <f t="array" ref="G240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H240" s="32" cm="1">
+      <c r="H240" s="31" cm="1">
         <f t="array" ref="H240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.22</v>
       </c>
-      <c r="I240" s="32" cm="1">
+      <c r="I240" s="31" cm="1">
         <f t="array" ref="I240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J240" s="32" cm="1">
+      <c r="J240" s="31" cm="1">
         <f t="array" ref="J240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K240" s="32" cm="1">
+      <c r="K240" s="31" cm="1">
         <f t="array" ref="K240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L240" s="32" cm="1">
+      <c r="L240" s="31" cm="1">
         <f t="array" ref="L240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M240" s="32" cm="1">
+      <c r="M240" s="31" cm="1">
         <f t="array" ref="M240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N240" s="32" cm="1">
+      <c r="N240" s="31" cm="1">
         <f t="array" ref="N240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O240" s="32" cm="1">
+      <c r="O240" s="31" cm="1">
         <f t="array" ref="O240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P240" s="32" cm="1">
+      <c r="P240" s="31" cm="1">
         <f t="array" ref="P240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q240" s="32" cm="1">
+      <c r="Q240" s="31" cm="1">
         <f t="array" ref="Q240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R240" s="32" cm="1">
+      <c r="R240" s="31" cm="1">
         <f t="array" ref="R240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S240" s="32" cm="1">
+      <c r="S240" s="31" cm="1">
         <f t="array" ref="S240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>18</v>
       </c>
@@ -10898,63 +10955,63 @@
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E241" s="32" cm="1">
+      <c r="E241" s="31" cm="1">
         <f t="array" ref="E241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
-      <c r="F241" s="32" cm="1">
+      <c r="F241" s="31" cm="1">
         <f t="array" ref="F241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.77</v>
       </c>
-      <c r="G241" s="32" cm="1">
+      <c r="G241" s="31" cm="1">
         <f t="array" ref="G241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H241" s="32" cm="1">
+      <c r="H241" s="31" cm="1">
         <f t="array" ref="H241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.24</v>
       </c>
-      <c r="I241" s="32" cm="1">
+      <c r="I241" s="31" cm="1">
         <f t="array" ref="I241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J241" s="32" cm="1">
+      <c r="J241" s="31" cm="1">
         <f t="array" ref="J241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K241" s="32" cm="1">
+      <c r="K241" s="31" cm="1">
         <f t="array" ref="K241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L241" s="32" cm="1">
+      <c r="L241" s="31" cm="1">
         <f t="array" ref="L241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M241" s="32" cm="1">
+      <c r="M241" s="31" cm="1">
         <f t="array" ref="M241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N241" s="32" cm="1">
+      <c r="N241" s="31" cm="1">
         <f t="array" ref="N241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O241" s="32" cm="1">
+      <c r="O241" s="31" cm="1">
         <f t="array" ref="O241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P241" s="32" cm="1">
+      <c r="P241" s="31" cm="1">
         <f t="array" ref="P241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q241" s="32" cm="1">
+      <c r="Q241" s="31" cm="1">
         <f t="array" ref="Q241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R241" s="32" cm="1">
+      <c r="R241" s="31" cm="1">
         <f t="array" ref="R241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S241" s="32" cm="1">
+      <c r="S241" s="31" cm="1">
         <f t="array" ref="S241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>19</v>
       </c>
@@ -10964,63 +11021,63 @@
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E242" s="32" cm="1">
+      <c r="E242" s="31" cm="1">
         <f t="array" ref="E242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
-      <c r="F242" s="32" cm="1">
+      <c r="F242" s="31" cm="1">
         <f t="array" ref="F242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G242" s="32" cm="1">
+      <c r="G242" s="31" cm="1">
         <f t="array" ref="G242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H242" s="32" cm="1">
+      <c r="H242" s="31" cm="1">
         <f t="array" ref="H242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.26</v>
       </c>
-      <c r="I242" s="32" cm="1">
+      <c r="I242" s="31" cm="1">
         <f t="array" ref="I242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J242" s="32" cm="1">
+      <c r="J242" s="31" cm="1">
         <f t="array" ref="J242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K242" s="32" cm="1">
+      <c r="K242" s="31" cm="1">
         <f t="array" ref="K242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L242" s="32" cm="1">
+      <c r="L242" s="31" cm="1">
         <f t="array" ref="L242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M242" s="32" cm="1">
+      <c r="M242" s="31" cm="1">
         <f t="array" ref="M242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N242" s="32" cm="1">
+      <c r="N242" s="31" cm="1">
         <f t="array" ref="N242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O242" s="32" cm="1">
+      <c r="O242" s="31" cm="1">
         <f t="array" ref="O242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P242" s="32" cm="1">
+      <c r="P242" s="31" cm="1">
         <f t="array" ref="P242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q242" s="32" cm="1">
+      <c r="Q242" s="31" cm="1">
         <f t="array" ref="Q242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R242" s="32" cm="1">
+      <c r="R242" s="31" cm="1">
         <f t="array" ref="R242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S242" s="32" cm="1">
+      <c r="S242" s="31" cm="1">
         <f t="array" ref="S242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>20</v>
       </c>
@@ -11030,63 +11087,63 @@
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E243" s="32" cm="1">
+      <c r="E243" s="31" cm="1">
         <f t="array" ref="E243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
-      <c r="F243" s="32" cm="1">
+      <c r="F243" s="31" cm="1">
         <f t="array" ref="F243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G243" s="32" cm="1">
+      <c r="G243" s="31" cm="1">
         <f t="array" ref="G243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H243" s="32" cm="1">
+      <c r="H243" s="31" cm="1">
         <f t="array" ref="H243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="I243" s="32" cm="1">
+      <c r="I243" s="31" cm="1">
         <f t="array" ref="I243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J243" s="32" cm="1">
+      <c r="J243" s="31" cm="1">
         <f t="array" ref="J243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K243" s="32" cm="1">
+      <c r="K243" s="31" cm="1">
         <f t="array" ref="K243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L243" s="32" cm="1">
+      <c r="L243" s="31" cm="1">
         <f t="array" ref="L243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M243" s="32" cm="1">
+      <c r="M243" s="31" cm="1">
         <f t="array" ref="M243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N243" s="32" cm="1">
+      <c r="N243" s="31" cm="1">
         <f t="array" ref="N243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O243" s="32" cm="1">
+      <c r="O243" s="31" cm="1">
         <f t="array" ref="O243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P243" s="32" cm="1">
+      <c r="P243" s="31" cm="1">
         <f t="array" ref="P243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q243" s="32" cm="1">
+      <c r="Q243" s="31" cm="1">
         <f t="array" ref="Q243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R243" s="32" cm="1">
+      <c r="R243" s="31" cm="1">
         <f t="array" ref="R243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S243" s="32" cm="1">
+      <c r="S243" s="31" cm="1">
         <f t="array" ref="S243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>21</v>
       </c>
@@ -11096,63 +11153,63 @@
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E244" s="32" cm="1">
+      <c r="E244" s="31" cm="1">
         <f t="array" ref="E244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
-      <c r="F244" s="32" cm="1">
+      <c r="F244" s="31" cm="1">
         <f t="array" ref="F244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.78</v>
       </c>
-      <c r="G244" s="32" cm="1">
+      <c r="G244" s="31" cm="1">
         <f t="array" ref="G244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H244" s="32" cm="1">
+      <c r="H244" s="31" cm="1">
         <f t="array" ref="H244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.31</v>
       </c>
-      <c r="I244" s="32" cm="1">
+      <c r="I244" s="31" cm="1">
         <f t="array" ref="I244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J244" s="32" cm="1">
+      <c r="J244" s="31" cm="1">
         <f t="array" ref="J244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K244" s="32" cm="1">
+      <c r="K244" s="31" cm="1">
         <f t="array" ref="K244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L244" s="32" cm="1">
+      <c r="L244" s="31" cm="1">
         <f t="array" ref="L244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M244" s="32" cm="1">
+      <c r="M244" s="31" cm="1">
         <f t="array" ref="M244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N244" s="32" cm="1">
+      <c r="N244" s="31" cm="1">
         <f t="array" ref="N244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O244" s="32" cm="1">
+      <c r="O244" s="31" cm="1">
         <f t="array" ref="O244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P244" s="32" cm="1">
+      <c r="P244" s="31" cm="1">
         <f t="array" ref="P244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q244" s="32" cm="1">
+      <c r="Q244" s="31" cm="1">
         <f t="array" ref="Q244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R244" s="32" cm="1">
+      <c r="R244" s="31" cm="1">
         <f t="array" ref="R244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S244" s="32" cm="1">
+      <c r="S244" s="31" cm="1">
         <f t="array" ref="S244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>22</v>
       </c>
@@ -11162,63 +11219,63 @@
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E245" s="32" cm="1">
+      <c r="E245" s="31" cm="1">
         <f t="array" ref="E245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
-      <c r="F245" s="32" cm="1">
+      <c r="F245" s="31" cm="1">
         <f t="array" ref="F245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G245" s="32" cm="1">
+      <c r="G245" s="31" cm="1">
         <f t="array" ref="G245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H245" s="32" cm="1">
+      <c r="H245" s="31" cm="1">
         <f t="array" ref="H245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.34</v>
       </c>
-      <c r="I245" s="32" cm="1">
+      <c r="I245" s="31" cm="1">
         <f t="array" ref="I245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J245" s="32" cm="1">
+      <c r="J245" s="31" cm="1">
         <f t="array" ref="J245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K245" s="32" cm="1">
+      <c r="K245" s="31" cm="1">
         <f t="array" ref="K245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L245" s="32" cm="1">
+      <c r="L245" s="31" cm="1">
         <f t="array" ref="L245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M245" s="32" cm="1">
+      <c r="M245" s="31" cm="1">
         <f t="array" ref="M245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N245" s="32" cm="1">
+      <c r="N245" s="31" cm="1">
         <f t="array" ref="N245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O245" s="32" cm="1">
+      <c r="O245" s="31" cm="1">
         <f t="array" ref="O245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P245" s="32" cm="1">
+      <c r="P245" s="31" cm="1">
         <f t="array" ref="P245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q245" s="32" cm="1">
+      <c r="Q245" s="31" cm="1">
         <f t="array" ref="Q245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R245" s="32" cm="1">
+      <c r="R245" s="31" cm="1">
         <f t="array" ref="R245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S245" s="32" cm="1">
+      <c r="S245" s="31" cm="1">
         <f t="array" ref="S245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>23</v>
       </c>
@@ -11228,63 +11285,63 @@
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E246" s="32" cm="1">
+      <c r="E246" s="31" cm="1">
         <f t="array" ref="E246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
-      <c r="F246" s="32" cm="1">
+      <c r="F246" s="31" cm="1">
         <f t="array" ref="F246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G246" s="32" cm="1">
+      <c r="G246" s="31" cm="1">
         <f t="array" ref="G246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H246" s="32" cm="1">
+      <c r="H246" s="31" cm="1">
         <f t="array" ref="H246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.37</v>
       </c>
-      <c r="I246" s="32" cm="1">
+      <c r="I246" s="31" cm="1">
         <f t="array" ref="I246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J246" s="32" cm="1">
+      <c r="J246" s="31" cm="1">
         <f t="array" ref="J246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K246" s="32" cm="1">
+      <c r="K246" s="31" cm="1">
         <f t="array" ref="K246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L246" s="32" cm="1">
+      <c r="L246" s="31" cm="1">
         <f t="array" ref="L246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M246" s="32" cm="1">
+      <c r="M246" s="31" cm="1">
         <f t="array" ref="M246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N246" s="32" cm="1">
+      <c r="N246" s="31" cm="1">
         <f t="array" ref="N246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O246" s="32" cm="1">
+      <c r="O246" s="31" cm="1">
         <f t="array" ref="O246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P246" s="32" cm="1">
+      <c r="P246" s="31" cm="1">
         <f t="array" ref="P246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q246" s="32" cm="1">
+      <c r="Q246" s="31" cm="1">
         <f t="array" ref="Q246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R246" s="32" cm="1">
+      <c r="R246" s="31" cm="1">
         <f t="array" ref="R246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S246" s="32" cm="1">
+      <c r="S246" s="31" cm="1">
         <f t="array" ref="S246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>24</v>
       </c>
@@ -11294,63 +11351,63 @@
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
       </c>
-      <c r="E247" s="32" cm="1">
+      <c r="E247" s="31" cm="1">
         <f t="array" ref="E247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
-      <c r="F247" s="32" cm="1">
+      <c r="F247" s="31" cm="1">
         <f t="array" ref="F247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G247" s="32" cm="1">
+      <c r="G247" s="31" cm="1">
         <f t="array" ref="G247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H247" s="32" cm="1">
+      <c r="H247" s="31" cm="1">
         <f t="array" ref="H247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.41</v>
       </c>
-      <c r="I247" s="32" cm="1">
+      <c r="I247" s="31" cm="1">
         <f t="array" ref="I247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J247" s="32" cm="1">
+      <c r="J247" s="31" cm="1">
         <f t="array" ref="J247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="K247" s="32" cm="1">
+      <c r="K247" s="31" cm="1">
         <f t="array" ref="K247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L247" s="32" cm="1">
+      <c r="L247" s="31" cm="1">
         <f t="array" ref="L247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M247" s="32" cm="1">
+      <c r="M247" s="31" cm="1">
         <f t="array" ref="M247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N247" s="32" cm="1">
+      <c r="N247" s="31" cm="1">
         <f t="array" ref="N247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O247" s="32" cm="1">
+      <c r="O247" s="31" cm="1">
         <f t="array" ref="O247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P247" s="32" cm="1">
+      <c r="P247" s="31" cm="1">
         <f t="array" ref="P247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q247" s="32" cm="1">
+      <c r="Q247" s="31" cm="1">
         <f t="array" ref="Q247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R247" s="32" cm="1">
+      <c r="R247" s="31" cm="1">
         <f t="array" ref="R247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S247" s="32" cm="1">
+      <c r="S247" s="31" cm="1">
         <f t="array" ref="S247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>25</v>
       </c>
@@ -11360,63 +11417,63 @@
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E248" s="32" cm="1">
+      <c r="E248" s="31" cm="1">
         <f t="array" ref="E248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
-      <c r="F248" s="32" cm="1">
+      <c r="F248" s="31" cm="1">
         <f t="array" ref="F248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.79</v>
       </c>
-      <c r="G248" s="32" cm="1">
+      <c r="G248" s="31" cm="1">
         <f t="array" ref="G248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H248" s="32" cm="1">
+      <c r="H248" s="31" cm="1">
         <f t="array" ref="H248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.44</v>
       </c>
-      <c r="I248" s="32" cm="1">
+      <c r="I248" s="31" cm="1">
         <f t="array" ref="I248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J248" s="32" cm="1">
+      <c r="J248" s="31" cm="1">
         <f t="array" ref="J248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K248" s="32" cm="1">
+      <c r="K248" s="31" cm="1">
         <f t="array" ref="K248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L248" s="32" cm="1">
+      <c r="L248" s="31" cm="1">
         <f t="array" ref="L248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M248" s="32" cm="1">
+      <c r="M248" s="31" cm="1">
         <f t="array" ref="M248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N248" s="32" cm="1">
+      <c r="N248" s="31" cm="1">
         <f t="array" ref="N248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O248" s="32" cm="1">
+      <c r="O248" s="31" cm="1">
         <f t="array" ref="O248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P248" s="32" cm="1">
+      <c r="P248" s="31" cm="1">
         <f t="array" ref="P248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q248" s="32" cm="1">
+      <c r="Q248" s="31" cm="1">
         <f t="array" ref="Q248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R248" s="32" cm="1">
+      <c r="R248" s="31" cm="1">
         <f t="array" ref="R248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S248" s="32" cm="1">
+      <c r="S248" s="31" cm="1">
         <f t="array" ref="S248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>26</v>
       </c>
@@ -11426,63 +11483,63 @@
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E249" s="32" cm="1">
+      <c r="E249" s="31" cm="1">
         <f t="array" ref="E249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
-      <c r="F249" s="32" cm="1">
+      <c r="F249" s="31" cm="1">
         <f t="array" ref="F249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.8</v>
       </c>
-      <c r="G249" s="32" cm="1">
+      <c r="G249" s="31" cm="1">
         <f t="array" ref="G249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H249" s="32" cm="1">
+      <c r="H249" s="31" cm="1">
         <f t="array" ref="H249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.48</v>
       </c>
-      <c r="I249" s="32" cm="1">
+      <c r="I249" s="31" cm="1">
         <f t="array" ref="I249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J249" s="32" cm="1">
+      <c r="J249" s="31" cm="1">
         <f t="array" ref="J249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K249" s="32" cm="1">
+      <c r="K249" s="31" cm="1">
         <f t="array" ref="K249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L249" s="32" cm="1">
+      <c r="L249" s="31" cm="1">
         <f t="array" ref="L249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M249" s="32" cm="1">
+      <c r="M249" s="31" cm="1">
         <f t="array" ref="M249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N249" s="32" cm="1">
+      <c r="N249" s="31" cm="1">
         <f t="array" ref="N249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O249" s="32" cm="1">
+      <c r="O249" s="31" cm="1">
         <f t="array" ref="O249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P249" s="32" cm="1">
+      <c r="P249" s="31" cm="1">
         <f t="array" ref="P249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q249" s="32" cm="1">
+      <c r="Q249" s="31" cm="1">
         <f t="array" ref="Q249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R249" s="32" cm="1">
+      <c r="R249" s="31" cm="1">
         <f t="array" ref="R249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S249" s="32" cm="1">
+      <c r="S249" s="31" cm="1">
         <f t="array" ref="S249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>27</v>
       </c>
@@ -11492,63 +11549,63 @@
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
       </c>
-      <c r="E250" s="32" t="str" cm="1">
+      <c r="E250" s="31" t="str" cm="1">
         <f t="array" ref="E250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>≥28</v>
       </c>
-      <c r="F250" s="32" cm="1">
+      <c r="F250" s="31" cm="1">
         <f t="array" ref="F250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.8</v>
       </c>
-      <c r="G250" s="32" cm="1">
+      <c r="G250" s="31" cm="1">
         <f t="array" ref="G250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.1</v>
       </c>
-      <c r="H250" s="32" cm="1">
+      <c r="H250" s="31" cm="1">
         <f t="array" ref="H250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.5</v>
       </c>
-      <c r="I250" s="32" cm="1">
+      <c r="I250" s="31" cm="1">
         <f t="array" ref="I250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.01</v>
       </c>
-      <c r="J250" s="32" cm="1">
+      <c r="J250" s="31" cm="1">
         <f t="array" ref="J250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="K250" s="32" cm="1">
+      <c r="K250" s="31" cm="1">
         <f t="array" ref="K250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.02</v>
       </c>
-      <c r="L250" s="32" cm="1">
+      <c r="L250" s="31" cm="1">
         <f t="array" ref="L250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.03</v>
       </c>
-      <c r="M250" s="32" cm="1">
+      <c r="M250" s="31" cm="1">
         <f t="array" ref="M250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0.04</v>
       </c>
-      <c r="N250" s="32" cm="1">
+      <c r="N250" s="31" cm="1">
         <f t="array" ref="N250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="O250" s="32" cm="1">
+      <c r="O250" s="31" cm="1">
         <f t="array" ref="O250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="P250" s="32" cm="1">
+      <c r="P250" s="31" cm="1">
         <f t="array" ref="P250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="Q250" s="32" cm="1">
+      <c r="Q250" s="31" cm="1">
         <f t="array" ref="Q250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>0</v>
       </c>
-      <c r="R250" s="32" cm="1">
+      <c r="R250" s="31" cm="1">
         <f t="array" ref="R250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="S250" s="32" cm="1">
+      <c r="S250" s="31" cm="1">
         <f t="array" ref="S250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>28</v>
       </c>
@@ -11560,7 +11617,7 @@
       </c>
     </row>
     <row r="254" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D254" s="29" t="str" cm="1">
+      <c r="D254" s="28" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
@@ -11578,19 +11635,19 @@
       </c>
     </row>
     <row r="257" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D257" s="32" t="s">
+      <c r="D257" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E257" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="E257" s="32" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="258" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D258" s="32" t="str" cm="1">
+      <c r="D258" s="31" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
       </c>
-      <c r="E258" s="32" cm="1">
+      <c r="E258" s="31" cm="1">
         <f t="array" ref="E258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>6.0000000000000001E-3</v>
       </c>
@@ -11600,7 +11657,7 @@
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
       </c>
-      <c r="E259" s="32" cm="1">
+      <c r="E259" s="31" cm="1">
         <f t="array" ref="E259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>5.0000000000000001E-3</v>
       </c>
@@ -11631,7 +11688,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11830,14 +11894,7 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11850,9 +11907,12 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11877,12 +11937,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C94625C-5EE8-4C1A-9F2C-2810468C30CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14DB445-5E0C-4BC9-BF83-D183E73330EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="555" windowWidth="35745" windowHeight="18900" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1215" yWindow="705" windowWidth="35745" windowHeight="18900" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -417,8 +417,13 @@
     <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Unit">_xlfn.LAMBDA("ratio")</definedName>
     <definedName name="MMS_PastureBeef_Soil_N2ODirect_Equations.VEERG_4_2_1_3__7_RelativeSize_Variable">_xlfn.LAMBDA("Z_jkl")</definedName>
     <definedName name="Range_LivestockStartingValues">#REF!</definedName>
+    <definedName name="Result_CarbonRemovalsFromPlantings">Results!$E$53</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method1">Results!$E$42</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Method2">Results!$F$42</definedName>
     <definedName name="Result_Enterprise_Method1">Results!$H$28</definedName>
     <definedName name="Result_Enterprise_Method2">Results!$I$28</definedName>
+    <definedName name="Result_NetEmissions_Method1">Results!$E$59</definedName>
+    <definedName name="Result_NetEmissions_Method2">Results!$F$59</definedName>
     <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Data">_xlfn.LAMBDA(0.08)</definedName>
     <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Source">_xlfn.LAMBDA("VEERG 2026: 4.2.2.3 CONSTANTS")</definedName>
     <definedName name="SourceData_PastureBeef.SourceData_PastureBeef_AshContentOfFeedIntake_Title">_xlfn.LAMBDA("Ash content of feed intake")</definedName>
@@ -521,6 +526,8 @@
     <definedName name="X_Cell_Site_TemperatureZone">'Input - Site'!$E$22</definedName>
     <definedName name="X_Cell_Site_TotalRainfall">'Input - Site'!$E$15</definedName>
     <definedName name="X_Cell_Site_WetOrDryClimateZone">'Input - Site'!$E$21</definedName>
+    <definedName name="X_Table_Result_ActivityPeriodEmissions_RowsToCols">Results!$D$36:$F$41</definedName>
+    <definedName name="X_Table_Result_CarbonRemovalsFromPlantings_RowsToCols">Results!$D$47:$E$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -6636,7 +6643,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11688,17 +11696,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIAAnAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAnACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAAnAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAJwAsACAAJwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACcAIABhAG4AZAAgACcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkACcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQAnACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgACcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AJwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAJwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAJwAgAHQAbwAgAHMAaQBuAGcAdQBsAGEAcgAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAnACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAPAAxACAAbQBvAG4AdABoAFwAIgAsACAAXAAiAEQAZQBlAHAAIABMAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAIAAoAHcAaQB0AGgALwB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAIABpAG4AdABvACAAcABlAGwAbABlAHQAaQB6AGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUALAAgAFIAYQBuAGcAZQAgAGEAbgBkACAAUABhAGQAZABvAGMAawAgACgAYwApACgAZAApAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIxADAAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAxACwAIAAwAC4ANgA4ACwAIAAwAC4AMQAsACAAMAAuADEAMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADIALAAgADAALgA3ACwAIAAwAC4AMQAsACAAMAAuADEAMwAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADMALAAgADAALgA3ADEALAAgADAALgAxACwAIAAwAC4AMQA0ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEANAAsACAAMAAuADcAMwAsACAAMAAuADEALAAgADAALgAxADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANQAsACAAMAAuADcANAAsACAAMAAuADEALAAgADAALgAxADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADYALAAgADAALgA3ADUALAAgADAALgAxACwAIAAwAC4AMQA4ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA3ACwAIAAwAC4ANwA2ACwAIAAwAC4AMQAsACAAMAAuADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADgALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA5ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMAAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADYALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADEALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA5ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAyACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADMAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMwAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADQALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA1ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA2ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADQANAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAMgA3ACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA0ADgALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIjIAOABcACIALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADUALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAE0AQQBUACAAcgBhAHcAXAAiACAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIAByAG8AdwAgAG8AZgAgAE4ASQBSACAATQBNAEEAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABEAHUAcABsAGkAYwBhAHQAZQBkACAAJwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgACcATQBBAFQAIAByAGEAdwAnACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgACYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -11893,31 +11903,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwAsAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgACYAIABcACIAIAB0AG8AIABcACIAIAAmACAAZQBuAGQAcwBUAGUAeAB0ACAAJgAgAHQAYQBnACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcgBvAHcAcwBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAA+ADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjACcAXAAiACAAJgAgAHMAaAAgACYAIABcACIAJwAhAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgACYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgACYAIABcACIAIABcACIAIAAmACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGUAbgB0AGUAcgBwAHIAaQBzAGUAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAFwAbgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAKAAwAC4ANgA3ADgANAAgAGsAZwAvAG0AMwApAFwAbgBUAGEAawBlAG4AIABmAHIAbwBtACAAdABoAGUAIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAYQBuAGQAIABFAG4AZQByAGcAeQAgAFIAZQBwAG8AcgB0AGkAbgBnACAAXABuACgATQBlAGEAcwB1AHIAZQBtAGUAbgB0ACkAIABEAGUAdABlAHIAbQBpAG4AYQB0AGkAbwBuACAAMgAwADAAOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AbQAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AcwAgADMALgBCAC4AMQBhAF8AMgAsACAAMwAuAEIALgAxAGMAXwAyACwAIAAzAC4AQgAuADMAXwAxACwAIAAzAC4AQgAuADQAZwBfADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA2ADcAOAA0ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBcAG4AQwBnACAAPQAgADQANAAvADIAOAAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQANAAvADIAOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBcAG4ARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMQBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAyAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgAFwAIgAxADYALwAxADIAXAAiACwAIAAxADYALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgAFwAIgA0ADQALwAyADgAXAAiACwAIAA0ADQALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AeABcACIALAAgAFwAIgA0ADYALwAxADQAXAAiACwAIAA0ADYALAAgADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AXAAiACwAIABcACIAMgA4AC8AMQAyAFwAIgAsACAAMgA4ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAIABMAGkAbQBlAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ATQBWAE8AQwBcACIALAAgAFwAIgAxADQALwAxADIAXAAiACwAIAAxADQALAAgADEAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAATgAyAE8AXABuAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAVwBQAE4AMgBPAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAGEAcwBcACIALAAgAFwAIgBDAE8AMgAtAGUAIABmAGEAYwB0AG8AcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAMgA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAMgBGADYAXAAiACwAIAAxADIAMgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGADYAXAAiACwAIAAyADIAOAAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBGADMAXAAiACwAIAAxADcAMgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAdABhAHQAZQBzACAAYQBuAGQAIAB0AGUAcgByAGkAdABvAHIAaQBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAC8AVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQwBvAG0AbQBvAG4AIABOAGEAbQBlAFwAIgAsACAAXAAiAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEMAYQBwAGkAdABhAGwAIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAQQBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBOAFQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAQgBTACAAUwB0AGEAdABpAHMAdABjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADQAIAAtACAAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABCAHUAcgBlAGEAdQAgAG8AZgAgAFMAdABhAHQAaQBzAHQAaQBjAHMAIAAoAEEAQgBTACkAIAAtACAAUwB0AGEAdABpAHMAdABpAGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAAMgAgAC0AIAAyADAAMgAxACAALQAgAFMAaABhAHAAZQBmAGkAbABlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAIAA0ACAATgBhAG0AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AG4AYgB1AHIAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZAB1AHIAYQBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAASQBuAG4AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAFcAaABlAGEAdAAgAEIAZQBsAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABOAG8AcgB0AGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAFMAbwB1AHQAaAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMgA6ACAAVAByAGEAbgBzAGwAYQB0AGkAbgBnACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwAgAHQAbwAgAHcAZQB0ACAAYQBuAGQAIABkAHIAeQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAC0AIABDAGgAYQBuAGcAZQBkACAAJwBGAHIAeQAnACAAdABvACAAJwBEAHIAeQAnAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgADEAMAAwADAALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAD4AIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAPgAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAPgAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAPgAgADAAIABDACAALQAgAGQiIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAPgAgADYAMAAwAG0AbQBcACIALAAgADYAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZCIgADYAMAAwAG0AbQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADYAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAWgBvAG4AZQBcACIALAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABjAHIAaQB0AGUAcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAG8AYwBjAHUAcgBzAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQA+AKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAA